--- a/research/traditional_assets/database/data/france/france_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/france/france_cable_tv.xlsx
@@ -647,10 +647,10 @@
         <v>-0.1022136017979742</v>
       </c>
       <c r="X2">
-        <v>0.150141623654476</v>
+        <v>0.1500928950875312</v>
       </c>
       <c r="Y2">
-        <v>-0.2523552254524502</v>
+        <v>-0.2523064968855053</v>
       </c>
       <c r="Z2">
         <v>0.2662228594838181</v>
@@ -659,10 +659,10 @@
         <v>0.0002642359688652192</v>
       </c>
       <c r="AB2">
-        <v>0.09036993518783519</v>
+        <v>0.09035845716405685</v>
       </c>
       <c r="AC2">
-        <v>-0.09010569921896996</v>
+        <v>-0.09009422119519163</v>
       </c>
       <c r="AD2">
         <v>3617.3</v>
@@ -781,10 +781,10 @@
         <v>-0.1022136017979742</v>
       </c>
       <c r="X3">
-        <v>0.150141623654476</v>
+        <v>0.1500928950875312</v>
       </c>
       <c r="Y3">
-        <v>-0.2523552254524502</v>
+        <v>-0.2523064968855053</v>
       </c>
       <c r="Z3">
         <v>0.2662228594838181</v>
@@ -793,10 +793,10 @@
         <v>0.0002642359688652192</v>
       </c>
       <c r="AB3">
-        <v>0.09036993518783519</v>
+        <v>0.09035845716405685</v>
       </c>
       <c r="AC3">
-        <v>-0.09010569921896996</v>
+        <v>-0.09009422119519163</v>
       </c>
       <c r="AD3">
         <v>3617.3</v>
@@ -1133,49 +1133,49 @@
         <v>0.151209677419355</v>
       </c>
       <c r="F2">
-        <v>4.55080630509635</v>
+        <v>4.51071287332841</v>
       </c>
       <c r="G2">
         <v>4.66868869385648</v>
       </c>
       <c r="H2">
-        <v>3.54220702116675</v>
+        <v>3.72542462570986</v>
       </c>
       <c r="I2">
         <v>0.764449798178322</v>
       </c>
       <c r="J2">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="K2">
         <v>1114.6</v>
       </c>
       <c r="L2">
-        <v>3198.50840410376</v>
+        <v>3183.96208962696</v>
       </c>
       <c r="M2">
         <v>3834.7</v>
       </c>
       <c r="N2">
-        <v>5045.81040410376</v>
+        <v>5173.22108962696</v>
       </c>
       <c r="O2">
         <v>3617.3</v>
       </c>
       <c r="P2">
-        <v>2744.502</v>
+        <v>2886.459</v>
       </c>
       <c r="Q2">
-        <v>0.0903699351878352</v>
+        <v>0.0903584571640569</v>
       </c>
       <c r="R2">
-        <v>0.0729837251457454</v>
+        <v>0.0716166389072263</v>
       </c>
       <c r="S2">
         <v>0.0719524624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.150141623654476</v>
+        <v>0.150092895087531</v>
       </c>
       <c r="X2">
-        <v>0.107654278327484</v>
+        <v>0.1117971456003</v>
       </c>
       <c r="Y2">
         <v>2.03286264551953</v>
       </c>
       <c r="Z2">
-        <v>1.20509196113238</v>
+        <v>1.28640720817235</v>
       </c>
       <c r="AA2">
         <v>3617.3</v>
@@ -1230,7 +1230,7 @@
         <v>1114.6</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0761845577749042</v>
+        <v>0.07617036788686367</v>
       </c>
       <c r="C2">
-        <v>5665.744645999526</v>
+        <v>5665.978885845398</v>
       </c>
       <c r="D2">
-        <v>4768.544645999526</v>
+        <v>4768.778885845398</v>
       </c>
       <c r="E2">
         <v>-3617.3</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0761845577749042</v>
+        <v>0.07617036788686367</v>
       </c>
       <c r="T2">
         <v>0.5919749984509941</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07608287100543594</v>
+        <v>0.07605821659211551</v>
       </c>
       <c r="C3">
-        <v>5626.764597607047</v>
+        <v>5627.859651101419</v>
       </c>
       <c r="D3">
-        <v>4776.883597607048</v>
+        <v>4777.97865110142</v>
       </c>
       <c r="E3">
         <v>-3569.981</v>
@@ -1533,37 +1533,37 @@
         <v>797.3</v>
       </c>
       <c r="M3">
-        <v>2.727307063854451</v>
+        <v>2.661060463854451</v>
       </c>
       <c r="N3">
-        <v>794.5726929361455</v>
+        <v>794.6389395361455</v>
       </c>
       <c r="O3">
-        <v>198.6431732340364</v>
+        <v>198.6597348840364</v>
       </c>
       <c r="P3">
-        <v>595.9295197021091</v>
+        <v>595.979204652109</v>
       </c>
       <c r="Q3">
-        <v>1348.229519702109</v>
+        <v>1348.279204652109</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07641474381865347</v>
+        <v>0.07640044643146111</v>
       </c>
       <c r="T3">
         <v>0.5964596575301683</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>292.3396527537281</v>
+        <v>299.6173934526611</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07598118423596768</v>
+        <v>0.07594606529736736</v>
       </c>
       <c r="C4">
-        <v>5587.813765646957</v>
+        <v>5589.77598071245</v>
       </c>
       <c r="D4">
-        <v>4785.251765646957</v>
+        <v>4787.21398071245</v>
       </c>
       <c r="E4">
         <v>-3522.662</v>
@@ -1615,37 +1615,37 @@
         <v>797.3</v>
       </c>
       <c r="M4">
-        <v>5.454614127708902</v>
+        <v>5.322120927708902</v>
       </c>
       <c r="N4">
-        <v>791.8453858722911</v>
+        <v>791.9778790722911</v>
       </c>
       <c r="O4">
-        <v>197.9613464680728</v>
+        <v>197.9944697680728</v>
       </c>
       <c r="P4">
-        <v>593.8840394042184</v>
+        <v>593.9834093042183</v>
       </c>
       <c r="Q4">
-        <v>1346.184039404218</v>
+        <v>1346.283409304218</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07664962753676498</v>
+        <v>0.07663522045656056</v>
       </c>
       <c r="T4">
         <v>0.6010358402640196</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>146.1698263768641</v>
+        <v>149.8086967263306</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07587949746649943</v>
+        <v>0.0758339140026192</v>
       </c>
       <c r="C5">
-        <v>5548.892303933173</v>
+        <v>5551.728081304334</v>
       </c>
       <c r="D5">
-        <v>4793.649303933174</v>
+        <v>4796.485081304334</v>
       </c>
       <c r="E5">
         <v>-3475.343</v>
@@ -1697,37 +1697,37 @@
         <v>797.3</v>
       </c>
       <c r="M5">
-        <v>8.181921191563353</v>
+        <v>7.983181391563352</v>
       </c>
       <c r="N5">
-        <v>789.1180788084366</v>
+        <v>789.3168186084366</v>
       </c>
       <c r="O5">
-        <v>197.2795197021092</v>
+        <v>197.3292046521092</v>
       </c>
       <c r="P5">
-        <v>591.8385591063275</v>
+        <v>591.9876139563274</v>
       </c>
       <c r="Q5">
-        <v>1344.138559106327</v>
+        <v>1344.287613956327</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07688935421813652</v>
+        <v>0.07687483518320844</v>
       </c>
       <c r="T5">
         <v>0.6057063772810429</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>97.44655091790938</v>
+        <v>99.87246448422039</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07577781069703118</v>
+        <v>0.07572176270787105</v>
       </c>
       <c r="C6">
-        <v>5510.000367361213</v>
+        <v>5513.716161106659</v>
       </c>
       <c r="D6">
-        <v>4802.076367361213</v>
+        <v>4805.792161106659</v>
       </c>
       <c r="E6">
         <v>-3428.024</v>
@@ -1779,37 +1779,37 @@
         <v>797.3</v>
       </c>
       <c r="M6">
-        <v>10.9092282554178</v>
+        <v>10.6442418554178</v>
       </c>
       <c r="N6">
-        <v>786.3907717445821</v>
+        <v>786.6557581445821</v>
       </c>
       <c r="O6">
-        <v>196.5976929361455</v>
+        <v>196.6639395361455</v>
       </c>
       <c r="P6">
-        <v>589.7930788084366</v>
+        <v>589.9918186084366</v>
       </c>
       <c r="Q6">
-        <v>1342.093078808437</v>
+        <v>1342.291818608437</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07713407520536995</v>
+        <v>0.07711944188332816</v>
       </c>
       <c r="T6">
         <v>0.6104742171525877</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.08491318843203</v>
+        <v>74.90434836316528</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07567612392756293</v>
+        <v>0.0756096114131229</v>
       </c>
       <c r="C7">
-        <v>5471.138111917717</v>
+        <v>5475.740429968352</v>
       </c>
       <c r="D7">
-        <v>4810.533111917717</v>
+        <v>4815.135429968353</v>
       </c>
       <c r="E7">
         <v>-3380.705</v>
@@ -1861,37 +1861,37 @@
         <v>797.3</v>
       </c>
       <c r="M7">
-        <v>13.63653531927226</v>
+        <v>13.30530231927226</v>
       </c>
       <c r="N7">
-        <v>783.6634646807277</v>
+        <v>783.9946976807277</v>
       </c>
       <c r="O7">
-        <v>195.9158661701819</v>
+        <v>195.9986744201819</v>
       </c>
       <c r="P7">
-        <v>587.7475985105457</v>
+        <v>587.9960232605457</v>
       </c>
       <c r="Q7">
-        <v>1340.047598510546</v>
+        <v>1340.296023260546</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07738394821338726</v>
+        <v>0.07736919819818723</v>
       </c>
       <c r="T7">
         <v>0.6153424326003755</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.46793055074561</v>
+        <v>59.92347869053221</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07557443715809466</v>
+        <v>0.07549746011837474</v>
       </c>
       <c r="C8">
-        <v>5432.305694690067</v>
+        <v>5437.801099373441</v>
       </c>
       <c r="D8">
-        <v>4819.019694690067</v>
+        <v>4824.515099373441</v>
       </c>
       <c r="E8">
         <v>-3333.386</v>
@@ -1943,37 +1943,37 @@
         <v>797.3</v>
       </c>
       <c r="M8">
-        <v>16.36384238312671</v>
+        <v>15.9663627831267</v>
       </c>
       <c r="N8">
-        <v>780.9361576168733</v>
+        <v>781.3336372168733</v>
       </c>
       <c r="O8">
-        <v>195.2340394042183</v>
+        <v>195.3334093042183</v>
       </c>
       <c r="P8">
-        <v>585.702118212655</v>
+        <v>586.000227912655</v>
       </c>
       <c r="Q8">
-        <v>1338.002118212655</v>
+        <v>1338.300227912655</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07763913766838365</v>
+        <v>0.07762426847719225</v>
       </c>
       <c r="T8">
         <v>0.6203142271002439</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.72327545895469</v>
+        <v>49.93623224211019</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07547275038862641</v>
+        <v>0.07538530882362658</v>
       </c>
       <c r="C9">
-        <v>5393.503273876117</v>
+        <v>5399.898382457014</v>
       </c>
       <c r="D9">
-        <v>4827.536273876118</v>
+        <v>4833.931382457014</v>
       </c>
       <c r="E9">
         <v>-3286.067</v>
@@ -2025,37 +2025,37 @@
         <v>797.3</v>
       </c>
       <c r="M9">
-        <v>19.09114944698116</v>
+        <v>18.62742324698116</v>
       </c>
       <c r="N9">
-        <v>778.2088505530188</v>
+        <v>778.6725767530188</v>
       </c>
       <c r="O9">
-        <v>194.5522126382547</v>
+        <v>194.6681441882547</v>
       </c>
       <c r="P9">
-        <v>583.6566379147641</v>
+        <v>584.0044325647641</v>
       </c>
       <c r="Q9">
-        <v>1335.956637914764</v>
+        <v>1336.304432564764</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07789981506864879</v>
+        <v>0.07788482413854145</v>
       </c>
       <c r="T9">
         <v>0.6253929419119373</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.76280753624687</v>
+        <v>42.80248477895158</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07537106361915816</v>
+        <v>0.07527315752887845</v>
       </c>
       <c r="C10">
-        <v>5354.731008794029</v>
+        <v>5362.03249402137</v>
       </c>
       <c r="D10">
-        <v>4836.083008794029</v>
+        <v>4843.384494021369</v>
       </c>
       <c r="E10">
         <v>-3238.748</v>
@@ -2107,37 +2107,37 @@
         <v>797.3</v>
       </c>
       <c r="M10">
-        <v>21.81845651083561</v>
+        <v>21.28848371083561</v>
       </c>
       <c r="N10">
-        <v>775.4815434891643</v>
+        <v>776.0115162891643</v>
       </c>
       <c r="O10">
-        <v>193.8703858722911</v>
+        <v>194.0028790722911</v>
       </c>
       <c r="P10">
-        <v>581.6111576168732</v>
+        <v>582.0086372168732</v>
       </c>
       <c r="Q10">
-        <v>1333.911157616873</v>
+        <v>1334.308637216873</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07816615936891969</v>
+        <v>0.07815104405339826</v>
       </c>
       <c r="T10">
         <v>0.6305820635673633</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.54245659421601</v>
+        <v>37.45217418158264</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07526937684968989</v>
+        <v>0.07516100623413029</v>
       </c>
       <c r="C11">
-        <v>5315.989059892196</v>
+        <v>5324.203650552344</v>
       </c>
       <c r="D11">
-        <v>4844.660059892196</v>
+        <v>4852.874650552344</v>
       </c>
       <c r="E11">
         <v>-3191.429</v>
@@ -2189,37 +2189,37 @@
         <v>797.3</v>
       </c>
       <c r="M11">
-        <v>24.54576357469006</v>
+        <v>23.94954417469005</v>
       </c>
       <c r="N11">
-        <v>772.75423642531</v>
+        <v>773.35045582531</v>
       </c>
       <c r="O11">
-        <v>193.1885591063275</v>
+        <v>193.3376139563275</v>
       </c>
       <c r="P11">
-        <v>579.5656773189825</v>
+        <v>580.0128418689825</v>
       </c>
       <c r="Q11">
-        <v>1331.865677318982</v>
+        <v>1332.312841868983</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07843835739007565</v>
+        <v>0.07842311495539477</v>
       </c>
       <c r="T11">
         <v>0.6358852318525788</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.48218363930313</v>
+        <v>33.29082149474014</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07516769008022166</v>
+        <v>0.07504885493938213</v>
       </c>
       <c r="C12">
-        <v>5277.277588759291</v>
+        <v>5286.41207023584</v>
       </c>
       <c r="D12">
-        <v>4853.26758875929</v>
+        <v>4862.402070235839</v>
       </c>
       <c r="E12">
         <v>-3144.11</v>
@@ -2271,37 +2271,37 @@
         <v>797.3</v>
       </c>
       <c r="M12">
-        <v>27.27307063854451</v>
+        <v>26.61060463854451</v>
       </c>
       <c r="N12">
-        <v>770.0269293614555</v>
+        <v>770.6893953614555</v>
       </c>
       <c r="O12">
-        <v>192.5067323403639</v>
+        <v>192.6723488403639</v>
       </c>
       <c r="P12">
-        <v>577.5201970210916</v>
+        <v>578.0170465210916</v>
       </c>
       <c r="Q12">
-        <v>1329.820197021092</v>
+        <v>1330.317046521091</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07871660425614621</v>
+        <v>0.07870123187743563</v>
       </c>
       <c r="T12">
         <v>0.6413062483219102</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.23396527537281</v>
+        <v>29.96173934526611</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0750660033107534</v>
+        <v>0.07493670364463398</v>
       </c>
       <c r="C13">
-        <v>5238.596758134413</v>
+        <v>5248.657972974542</v>
       </c>
       <c r="D13">
-        <v>4861.905758134413</v>
+        <v>4871.966972974542</v>
       </c>
       <c r="E13">
         <v>-3096.791</v>
@@ -2353,37 +2353,37 @@
         <v>797.3</v>
       </c>
       <c r="M13">
-        <v>30.00037770239896</v>
+        <v>29.27166510239896</v>
       </c>
       <c r="N13">
-        <v>767.299622297601</v>
+        <v>768.028334897601</v>
       </c>
       <c r="O13">
-        <v>191.8249055744002</v>
+        <v>192.0070837244002</v>
       </c>
       <c r="P13">
-        <v>575.4747167232008</v>
+        <v>576.0212511732008</v>
       </c>
       <c r="Q13">
-        <v>1327.774716723201</v>
+        <v>1328.321251173201</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07900110386078016</v>
+        <v>0.07898559861794935</v>
       </c>
       <c r="T13">
         <v>0.6468490853860582</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.57633206852074</v>
+        <v>27.23794485933283</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07496431654128514</v>
+        <v>0.07482455234988583</v>
       </c>
       <c r="C14">
-        <v>5199.946731917344</v>
+        <v>5210.941580404848</v>
       </c>
       <c r="D14">
-        <v>4870.574731917343</v>
+        <v>4881.569580404848</v>
       </c>
       <c r="E14">
         <v>-3049.472</v>
@@ -2435,37 +2435,37 @@
         <v>797.3</v>
       </c>
       <c r="M14">
-        <v>32.72768476625341</v>
+        <v>31.93272556625341</v>
       </c>
       <c r="N14">
-        <v>764.5723152337465</v>
+        <v>765.3672744337465</v>
       </c>
       <c r="O14">
-        <v>191.1430788084366</v>
+        <v>191.3418186084366</v>
       </c>
       <c r="P14">
-        <v>573.4292364253099</v>
+        <v>574.0254558253099</v>
       </c>
       <c r="Q14">
-        <v>1325.72923642531</v>
+        <v>1326.32545582531</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0792920693655194</v>
+        <v>0.07927642823892928</v>
       </c>
       <c r="T14">
         <v>0.6525178960198458</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.36163772947734</v>
+        <v>24.96811612105509</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07486262977181687</v>
+        <v>0.07471240105513767</v>
       </c>
       <c r="C15">
-        <v>5161.327675178908</v>
+        <v>5173.263115913978</v>
       </c>
       <c r="D15">
-        <v>4879.274675178908</v>
+        <v>4891.210115913978</v>
       </c>
       <c r="E15">
         <v>-3002.153</v>
@@ -2517,37 +2517,37 @@
         <v>797.3</v>
       </c>
       <c r="M15">
-        <v>35.45499183010786</v>
+        <v>34.59378603010786</v>
       </c>
       <c r="N15">
-        <v>761.8450081698921</v>
+        <v>762.7062139698921</v>
       </c>
       <c r="O15">
-        <v>190.461252042473</v>
+        <v>190.676553492473</v>
       </c>
       <c r="P15">
-        <v>571.3837561274191</v>
+        <v>572.0296604774192</v>
       </c>
       <c r="Q15">
-        <v>1323.683756127419</v>
+        <v>1324.329660477419</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07958972373243656</v>
+        <v>0.07957394359832252</v>
       </c>
       <c r="T15">
         <v>0.6583170241394676</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.48766559644063</v>
+        <v>23.04749180405086</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07476094300234863</v>
+        <v>0.07460024976038952</v>
       </c>
       <c r="C16">
-        <v>5122.739754171455</v>
+        <v>5135.622804657296</v>
       </c>
       <c r="D16">
-        <v>4888.005754171456</v>
+        <v>4900.888804657297</v>
       </c>
       <c r="E16">
         <v>-2954.834</v>
@@ -2599,37 +2599,37 @@
         <v>797.3</v>
       </c>
       <c r="M16">
-        <v>38.18229889396231</v>
+        <v>37.25484649396232</v>
       </c>
       <c r="N16">
-        <v>759.1177011060377</v>
+        <v>760.0451535060377</v>
       </c>
       <c r="O16">
-        <v>189.7794252765094</v>
+        <v>190.0112883765094</v>
       </c>
       <c r="P16">
-        <v>569.3382758295282</v>
+        <v>570.0338651295283</v>
       </c>
       <c r="Q16">
-        <v>1321.638275829528</v>
+        <v>1322.333865129528</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0798943002939332</v>
+        <v>0.07987837791956215</v>
       </c>
       <c r="T16">
         <v>0.6642510157037318</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.88140376812344</v>
+        <v>21.40124238947579</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07465925623288036</v>
+        <v>0.07448809846564136</v>
       </c>
       <c r="C17">
-        <v>5084.183136339462</v>
+        <v>5098.020873575849</v>
       </c>
       <c r="D17">
-        <v>4896.768136339462</v>
+        <v>4910.605873575849</v>
       </c>
       <c r="E17">
         <v>-2907.515</v>
@@ -2681,37 +2681,37 @@
         <v>797.3</v>
       </c>
       <c r="M17">
-        <v>40.90960595781677</v>
+        <v>39.91590695781677</v>
       </c>
       <c r="N17">
-        <v>756.3903940421832</v>
+        <v>757.3840930421832</v>
       </c>
       <c r="O17">
-        <v>189.0975985105458</v>
+        <v>189.3460232605458</v>
       </c>
       <c r="P17">
-        <v>567.2927955316374</v>
+        <v>568.0380697816374</v>
       </c>
       <c r="Q17">
-        <v>1319.592795531637</v>
+        <v>1320.338069781637</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08020604336275916</v>
+        <v>0.0801899754013015</v>
       </c>
       <c r="T17">
         <v>0.6703246305989198</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.48931018358187</v>
+        <v>19.97449289684407</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07455756946341213</v>
+        <v>0.07437594717089321</v>
       </c>
       <c r="C18">
-        <v>5045.657990330204</v>
+        <v>5060.457551414091</v>
       </c>
       <c r="D18">
-        <v>4905.561990330205</v>
+        <v>4920.361551414091</v>
       </c>
       <c r="E18">
         <v>-2860.196</v>
@@ -2763,37 +2763,37 @@
         <v>797.3</v>
       </c>
       <c r="M18">
-        <v>43.63691302167121</v>
+        <v>42.57696742167121</v>
       </c>
       <c r="N18">
-        <v>753.6630869783287</v>
+        <v>754.7230325783287</v>
       </c>
       <c r="O18">
-        <v>188.4157717445822</v>
+        <v>188.6807581445822</v>
       </c>
       <c r="P18">
-        <v>565.2473152337466</v>
+        <v>566.0422744337466</v>
       </c>
       <c r="Q18">
-        <v>1317.547315233747</v>
+        <v>1318.342274433747</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0805252088856048</v>
+        <v>0.08050899187070133</v>
       </c>
       <c r="T18">
         <v>0.6765428553725646</v>
       </c>
       <c r="U18">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.27122829710801</v>
+        <v>18.72608709079132</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07445588269394388</v>
+        <v>0.07426379587614507</v>
       </c>
       <c r="C19">
-        <v>5007.164486004618</v>
+        <v>5022.933068737843</v>
       </c>
       <c r="D19">
-        <v>4914.387486004618</v>
+        <v>4930.156068737843</v>
       </c>
       <c r="E19">
         <v>-2812.877</v>
@@ -2845,37 +2845,37 @@
         <v>797.3</v>
       </c>
       <c r="M19">
-        <v>46.36422008552567</v>
+        <v>45.23802788552567</v>
       </c>
       <c r="N19">
-        <v>750.9357799144743</v>
+        <v>752.0619721144743</v>
       </c>
       <c r="O19">
-        <v>187.7339449786186</v>
+        <v>188.0154930286186</v>
       </c>
       <c r="P19">
-        <v>563.2018349358557</v>
+        <v>564.0464790858557</v>
       </c>
       <c r="Q19">
-        <v>1315.501834935856</v>
+        <v>1316.346479085856</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08085206514394069</v>
+        <v>0.08083569548394212</v>
       </c>
       <c r="T19">
         <v>0.6829109168877433</v>
       </c>
       <c r="U19">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.19645016198401</v>
+        <v>17.62455255603889</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07435419592447562</v>
+        <v>0.07415164458139692</v>
       </c>
       <c r="C20">
-        <v>4968.702794448203</v>
+        <v>4985.447657952454</v>
       </c>
       <c r="D20">
-        <v>4923.244794448204</v>
+        <v>4939.989657952455</v>
       </c>
       <c r="E20">
         <v>-2765.558</v>
@@ -2927,37 +2927,37 @@
         <v>797.3</v>
       </c>
       <c r="M20">
-        <v>49.09152714938011</v>
+        <v>47.89908834938011</v>
       </c>
       <c r="N20">
-        <v>748.2084728506198</v>
+        <v>749.4009116506198</v>
       </c>
       <c r="O20">
-        <v>187.052118212655</v>
+        <v>187.350227912655</v>
       </c>
       <c r="P20">
-        <v>561.1563546379649</v>
+        <v>562.0506837379648</v>
       </c>
       <c r="Q20">
-        <v>1313.456354637965</v>
+        <v>1314.350683737965</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08118689350613842</v>
+        <v>0.08117036747799367</v>
       </c>
       <c r="T20">
         <v>0.6894342969764626</v>
       </c>
       <c r="U20">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.24109181965157</v>
+        <v>16.64541074737006</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07425250915500736</v>
+        <v>0.07403949328664874</v>
       </c>
       <c r="C21">
-        <v>4930.273087982096</v>
+        <v>4948.001553321185</v>
       </c>
       <c r="D21">
-        <v>4932.134087982095</v>
+        <v>4949.862553321185</v>
       </c>
       <c r="E21">
         <v>-2718.239</v>
@@ -3009,37 +3009,37 @@
         <v>797.3</v>
       </c>
       <c r="M21">
-        <v>51.81883421323457</v>
+        <v>50.56014881323457</v>
       </c>
       <c r="N21">
-        <v>745.4811657867654</v>
+        <v>746.7398511867653</v>
       </c>
       <c r="O21">
-        <v>186.3702914466913</v>
+        <v>186.6849627966913</v>
       </c>
       <c r="P21">
-        <v>559.110874340074</v>
+        <v>560.054888390074</v>
       </c>
       <c r="Q21">
-        <v>1311.410874340074</v>
+        <v>1312.354888390074</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08152998923530401</v>
+        <v>0.08151330297807116</v>
       </c>
       <c r="T21">
         <v>0.6961187481784838</v>
       </c>
       <c r="U21">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.38629751335411</v>
+        <v>15.76933649750848</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07415082238553909</v>
+        <v>0.0739273419919006</v>
       </c>
       <c r="C22">
-        <v>4891.875540174236</v>
+        <v>4910.594990983799</v>
       </c>
       <c r="D22">
-        <v>4941.055540174237</v>
+        <v>4959.774990983799</v>
       </c>
       <c r="E22">
         <v>-2670.92</v>
@@ -3091,37 +3091,37 @@
         <v>797.3</v>
       </c>
       <c r="M22">
-        <v>54.54614127708902</v>
+        <v>53.22120927708902</v>
       </c>
       <c r="N22">
-        <v>742.753858722911</v>
+        <v>744.078790722911</v>
       </c>
       <c r="O22">
-        <v>185.6884646807277</v>
+        <v>186.0196976807277</v>
       </c>
       <c r="P22">
-        <v>557.0653940421832</v>
+        <v>558.0590930421832</v>
       </c>
       <c r="Q22">
-        <v>1309.365394042183</v>
+        <v>1310.359093042183</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08188166235769873</v>
+        <v>0.0818648118656506</v>
       </c>
       <c r="T22">
         <v>0.7029703106605555</v>
       </c>
       <c r="U22">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.61698263768641</v>
+        <v>14.98086967263306</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07404913561607084</v>
+        <v>0.07381519069715245</v>
       </c>
       <c r="C23">
-        <v>4853.51032585067</v>
+        <v>4873.228208975412</v>
       </c>
       <c r="D23">
-        <v>4950.009325850669</v>
+        <v>4969.727208975411</v>
       </c>
       <c r="E23">
         <v>-2623.601000000001</v>
@@ -3173,37 +3173,37 @@
         <v>797.3</v>
       </c>
       <c r="M23">
-        <v>57.27344834094346</v>
+        <v>55.88226974094346</v>
       </c>
       <c r="N23">
-        <v>740.0265516590565</v>
+        <v>741.4177302590565</v>
       </c>
       <c r="O23">
-        <v>185.0066379147641</v>
+        <v>185.3544325647641</v>
       </c>
       <c r="P23">
-        <v>555.0199137442924</v>
+        <v>556.0632976942924</v>
       </c>
       <c r="Q23">
-        <v>1307.319913744292</v>
+        <v>1308.363297694292</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0822422385971161</v>
+        <v>0.08222521971240927</v>
       </c>
       <c r="T23">
         <v>0.7099953304206543</v>
       </c>
       <c r="U23">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.92093584541563</v>
+        <v>14.2674949263172</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07394744884660259</v>
+        <v>0.07370303940240429</v>
       </c>
       <c r="C24">
-        <v>4815.177621106964</v>
+        <v>4835.901447245526</v>
       </c>
       <c r="D24">
-        <v>4958.995621106964</v>
+        <v>4979.719447245526</v>
       </c>
       <c r="E24">
         <v>-2576.282</v>
@@ -3255,37 +3255,37 @@
         <v>797.3</v>
       </c>
       <c r="M24">
-        <v>60.00075540479792</v>
+        <v>58.54333020479793</v>
       </c>
       <c r="N24">
-        <v>737.299244595202</v>
+        <v>738.756669795202</v>
       </c>
       <c r="O24">
-        <v>184.3248111488005</v>
+        <v>184.6891674488005</v>
       </c>
       <c r="P24">
-        <v>552.9744334464015</v>
+        <v>554.0675023464015</v>
       </c>
       <c r="Q24">
-        <v>1305.274433446401</v>
+        <v>1306.367502346402</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08261206038113392</v>
+        <v>0.0825948687860079</v>
       </c>
       <c r="T24">
         <v>0.7172004788925505</v>
       </c>
       <c r="U24">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.28816603426037</v>
+        <v>13.61897242966641</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07403551207713435</v>
+        <v>0.07359088810765614</v>
       </c>
       <c r="C25">
-        <v>4760.07437967334</v>
+        <v>4798.614947677321</v>
       </c>
       <c r="D25">
-        <v>4951.21137967334</v>
+        <v>4989.75194767732</v>
       </c>
       <c r="E25">
         <v>-2528.963</v>
@@ -3337,45 +3337,45 @@
         <v>797.3</v>
       </c>
       <c r="M25">
-        <v>63.92523316865237</v>
+        <v>61.20439066865237</v>
       </c>
       <c r="N25">
-        <v>733.3747668313476</v>
+        <v>736.0956093313475</v>
       </c>
       <c r="O25">
-        <v>183.3436917078369</v>
+        <v>184.0239023328369</v>
       </c>
       <c r="P25">
-        <v>550.0310751235107</v>
+        <v>552.0717069985106</v>
       </c>
       <c r="Q25">
-        <v>1302.331075123511</v>
+        <v>1304.37170699851</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0829914879257756</v>
+        <v>0.08297411913424546</v>
       </c>
       <c r="T25">
         <v>0.7245927740780025</v>
       </c>
       <c r="U25">
-        <v>0.0587366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04405246249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>12.47238313384799</v>
+        <v>13.02684319359396</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07394207530766608</v>
+        <v>0.073748736812908</v>
       </c>
       <c r="C26">
-        <v>4721.015400914959</v>
+        <v>4737.187141465646</v>
       </c>
       <c r="D26">
-        <v>4959.471400914959</v>
+        <v>4975.643141465646</v>
       </c>
       <c r="E26">
         <v>-2481.644</v>
@@ -3419,37 +3419,37 @@
         <v>797.3</v>
       </c>
       <c r="M26">
-        <v>66.70459113250682</v>
+        <v>65.56893513250682</v>
       </c>
       <c r="N26">
-        <v>730.5954088674931</v>
+        <v>731.7310648674932</v>
       </c>
       <c r="O26">
-        <v>182.6488522168733</v>
+        <v>182.9327662168733</v>
       </c>
       <c r="P26">
-        <v>547.9465566506199</v>
+        <v>548.7982986506199</v>
       </c>
       <c r="Q26">
-        <v>1300.24655665062</v>
+        <v>1301.09829865062</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08338090040580257</v>
+        <v>0.08336334975480507</v>
       </c>
       <c r="T26">
         <v>0.7321796033472823</v>
       </c>
       <c r="U26">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.95270050327099</v>
+        <v>12.15972164850251</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07384863853819783</v>
+        <v>0.07364783551815983</v>
       </c>
       <c r="C27">
-        <v>4681.984028315717</v>
+        <v>4698.877667176215</v>
       </c>
       <c r="D27">
-        <v>4967.759028315718</v>
+        <v>4984.652667176216</v>
       </c>
       <c r="E27">
         <v>-2434.325</v>
@@ -3501,37 +3501,37 @@
         <v>797.3</v>
       </c>
       <c r="M27">
-        <v>69.48394909636127</v>
+        <v>68.30097409636126</v>
       </c>
       <c r="N27">
-        <v>727.8160509036387</v>
+        <v>728.9990259036387</v>
       </c>
       <c r="O27">
-        <v>181.9540127259097</v>
+        <v>182.2497564759097</v>
       </c>
       <c r="P27">
-        <v>545.862038177729</v>
+        <v>546.749269427729</v>
       </c>
       <c r="Q27">
-        <v>1298.162038177729</v>
+        <v>1299.049269427729</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08378069721863024</v>
+        <v>0.08376295985857959</v>
       </c>
       <c r="T27">
         <v>0.7399687480637427</v>
       </c>
       <c r="U27">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.47459248314015</v>
+        <v>11.67333278256241</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07375520176872957</v>
+        <v>0.07354693422341167</v>
       </c>
       <c r="C28">
-        <v>4642.980400502805</v>
+        <v>4660.600879635923</v>
       </c>
       <c r="D28">
-        <v>4976.074400502805</v>
+        <v>4993.694879635923</v>
       </c>
       <c r="E28">
         <v>-2387.006</v>
@@ -3583,37 +3583,37 @@
         <v>797.3</v>
       </c>
       <c r="M28">
-        <v>72.26330706021571</v>
+        <v>71.03301306021571</v>
       </c>
       <c r="N28">
-        <v>725.0366929397842</v>
+        <v>726.2669869397843</v>
       </c>
       <c r="O28">
-        <v>181.259173234946</v>
+        <v>181.5667467349461</v>
       </c>
       <c r="P28">
-        <v>543.7775197048381</v>
+        <v>544.7002402048382</v>
       </c>
       <c r="Q28">
-        <v>1296.077519704838</v>
+        <v>1297.000240204838</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08419129935072354</v>
+        <v>0.08417337023542909</v>
       </c>
       <c r="T28">
         <v>0.7479684102049723</v>
       </c>
       <c r="U28">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.03326200301938</v>
+        <v>11.22435844477155</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07366176499926132</v>
+        <v>0.07344603292866353</v>
       </c>
       <c r="C29">
-        <v>4604.004657033136</v>
+        <v>4622.356957050354</v>
       </c>
       <c r="D29">
-        <v>4984.417657033136</v>
+        <v>5002.769957050355</v>
       </c>
       <c r="E29">
         <v>-2339.687</v>
@@ -3665,37 +3665,37 @@
         <v>797.3</v>
       </c>
       <c r="M29">
-        <v>75.04266502407017</v>
+        <v>73.76505202407017</v>
       </c>
       <c r="N29">
-        <v>722.2573349759298</v>
+        <v>723.5349479759298</v>
       </c>
       <c r="O29">
-        <v>180.5643337439824</v>
+        <v>180.8837369939824</v>
       </c>
       <c r="P29">
-        <v>541.6930012319474</v>
+        <v>542.6512109819473</v>
       </c>
       <c r="Q29">
-        <v>1293.993001231947</v>
+        <v>1294.951210981947</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08461315085629886</v>
+        <v>0.0845950247321923</v>
       </c>
       <c r="T29">
         <v>0.7561872411719891</v>
       </c>
       <c r="U29">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.62462266957421</v>
+        <v>10.80864146533556</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07356832822979308</v>
+        <v>0.07334513163391537</v>
       </c>
       <c r="C30">
-        <v>4565.056938401171</v>
+        <v>4584.146078922879</v>
       </c>
       <c r="D30">
-        <v>4992.788938401171</v>
+        <v>5011.878078922879</v>
       </c>
       <c r="E30">
         <v>-2292.368</v>
@@ -3747,37 +3747,37 @@
         <v>797.3</v>
       </c>
       <c r="M30">
-        <v>77.82202298792463</v>
+        <v>76.49709098792462</v>
       </c>
       <c r="N30">
-        <v>719.4779770120754</v>
+        <v>720.8029090120754</v>
       </c>
       <c r="O30">
-        <v>179.8694942530188</v>
+        <v>180.2007272530188</v>
       </c>
       <c r="P30">
-        <v>539.6084827590565</v>
+        <v>540.6021817590565</v>
       </c>
       <c r="Q30">
-        <v>1291.908482759056</v>
+        <v>1292.902181759056</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08504672045925127</v>
+        <v>0.08502839185386557</v>
       </c>
       <c r="T30">
         <v>0.7646343729992008</v>
       </c>
       <c r="U30">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.24517185994656</v>
+        <v>10.42261855585929</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07347489146032479</v>
+        <v>0.07324423033916722</v>
       </c>
       <c r="C31">
-        <v>4526.137386046794</v>
+        <v>4545.968426066471</v>
       </c>
       <c r="D31">
-        <v>5001.188386046793</v>
+        <v>5021.01942606647</v>
       </c>
       <c r="E31">
         <v>-2245.049</v>
@@ -3829,37 +3829,37 @@
         <v>797.3</v>
       </c>
       <c r="M31">
-        <v>80.60138095177906</v>
+        <v>79.22912995177906</v>
       </c>
       <c r="N31">
-        <v>716.6986190482208</v>
+        <v>718.0708700482209</v>
       </c>
       <c r="O31">
-        <v>179.1746547620552</v>
+        <v>179.5177175120552</v>
       </c>
       <c r="P31">
-        <v>537.5239642861657</v>
+        <v>538.5531525361656</v>
       </c>
       <c r="Q31">
-        <v>1289.823964286166</v>
+        <v>1290.853152536165</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08549250329045582</v>
+        <v>0.08547396650009303</v>
       </c>
       <c r="T31">
         <v>0.7733194522018267</v>
       </c>
       <c r="U31">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.891890071672545</v>
+        <v>10.06321791600208</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07387645469085655</v>
+        <v>0.07352582904441905</v>
       </c>
       <c r="C32">
-        <v>4442.918905216256</v>
+        <v>4473.220358406777</v>
       </c>
       <c r="D32">
-        <v>4965.288905216255</v>
+        <v>4995.590358406777</v>
       </c>
       <c r="E32">
         <v>-2197.73</v>
@@ -3911,37 +3911,37 @@
         <v>797.3</v>
       </c>
       <c r="M32">
-        <v>86.50379291563353</v>
+        <v>84.37443791563352</v>
       </c>
       <c r="N32">
-        <v>710.7962070843664</v>
+        <v>712.9255620843664</v>
       </c>
       <c r="O32">
-        <v>177.6990517710916</v>
+        <v>178.2313905210916</v>
       </c>
       <c r="P32">
-        <v>533.0971553132748</v>
+        <v>534.6941715632748</v>
       </c>
       <c r="Q32">
-        <v>1285.397155313275</v>
+        <v>1286.994171563275</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08595102277398055</v>
+        <v>0.08593227185049841</v>
       </c>
       <c r="T32">
         <v>0.7822526765245279</v>
       </c>
       <c r="U32">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.216936889433281</v>
+        <v>9.449544431895649</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07379951792138829</v>
+        <v>0.0734376777496709</v>
       </c>
       <c r="C33">
-        <v>4402.438032446197</v>
+        <v>4433.83390203812</v>
       </c>
       <c r="D33">
-        <v>4972.127032446198</v>
+        <v>5003.52290203812</v>
       </c>
       <c r="E33">
         <v>-2150.411</v>
@@ -3993,37 +3993,37 @@
         <v>797.3</v>
       </c>
       <c r="M33">
-        <v>89.38725267948797</v>
+        <v>87.18691917948797</v>
       </c>
       <c r="N33">
-        <v>707.9127473205119</v>
+        <v>710.113080820512</v>
       </c>
       <c r="O33">
-        <v>176.978186830128</v>
+        <v>177.528270205128</v>
       </c>
       <c r="P33">
-        <v>530.934560490384</v>
+        <v>532.584810615384</v>
       </c>
       <c r="Q33">
-        <v>1283.234560490384</v>
+        <v>1284.884810615384</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08642283267731757</v>
+        <v>0.08640386141395903</v>
       </c>
       <c r="T33">
         <v>0.7914448348855682</v>
       </c>
       <c r="U33">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.919616344612852</v>
+        <v>9.144720417963532</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07372258115192004</v>
+        <v>0.07334952645492275</v>
       </c>
       <c r="C34">
-        <v>4361.976020399419</v>
+        <v>4394.472678053399</v>
       </c>
       <c r="D34">
-        <v>4978.984020399419</v>
+        <v>5011.480678053399</v>
       </c>
       <c r="E34">
         <v>-2103.092000000001</v>
@@ -4075,37 +4075,37 @@
         <v>797.3</v>
       </c>
       <c r="M34">
-        <v>92.27071244334242</v>
+        <v>89.99940044334242</v>
       </c>
       <c r="N34">
-        <v>705.0292875566576</v>
+        <v>707.3005995566575</v>
       </c>
       <c r="O34">
-        <v>176.2573218891644</v>
+        <v>176.8251498891644</v>
       </c>
       <c r="P34">
-        <v>528.7719656674932</v>
+        <v>530.4754496674932</v>
       </c>
       <c r="Q34">
-        <v>1281.071965667493</v>
+        <v>1282.775449667493</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08690851934251745</v>
+        <v>0.0868893212586979</v>
       </c>
       <c r="T34">
         <v>0.8009073508454626</v>
       </c>
       <c r="U34">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.640878333843702</v>
+        <v>8.858947904902172</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0736456443824518</v>
+        <v>0.0732613751601746</v>
       </c>
       <c r="C35">
-        <v>4321.532947215329</v>
+        <v>4355.136807035764</v>
       </c>
       <c r="D35">
-        <v>4985.859947215329</v>
+        <v>5019.463807035764</v>
       </c>
       <c r="E35">
         <v>-2055.773</v>
@@ -4157,37 +4157,37 @@
         <v>797.3</v>
       </c>
       <c r="M35">
-        <v>95.15417220719688</v>
+        <v>92.81188170719687</v>
       </c>
       <c r="N35">
-        <v>702.1458277928031</v>
+        <v>704.4881182928031</v>
       </c>
       <c r="O35">
-        <v>175.5364569482008</v>
+        <v>176.1220295732008</v>
       </c>
       <c r="P35">
-        <v>526.6093708446023</v>
+        <v>528.3660887196023</v>
       </c>
       <c r="Q35">
-        <v>1278.909370844602</v>
+        <v>1280.666088719602</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08740870411712628</v>
+        <v>0.08738927244208569</v>
       </c>
       <c r="T35">
         <v>0.810652329968339</v>
       </c>
       <c r="U35">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.379033535848437</v>
+        <v>8.590494938086955</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07356870761298354</v>
+        <v>0.07317322386542643</v>
       </c>
       <c r="C36">
-        <v>4281.108891465572</v>
+        <v>4315.826410337935</v>
       </c>
       <c r="D36">
-        <v>4992.754891465572</v>
+        <v>5027.472410337935</v>
       </c>
       <c r="E36">
         <v>-2008.454</v>
@@ -4239,37 +4239,37 @@
         <v>797.3</v>
       </c>
       <c r="M36">
-        <v>98.03763197105133</v>
+        <v>95.62436297105133</v>
       </c>
       <c r="N36">
-        <v>699.2623680289487</v>
+        <v>701.6756370289486</v>
       </c>
       <c r="O36">
-        <v>174.8155920072372</v>
+        <v>175.4189092572371</v>
       </c>
       <c r="P36">
-        <v>524.4467760217115</v>
+        <v>526.2567277717114</v>
       </c>
       <c r="Q36">
-        <v>1276.746776021711</v>
+        <v>1278.556727771711</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.0879240460061172</v>
+        <v>0.08790437366133372</v>
       </c>
       <c r="T36">
         <v>0.8206926114888783</v>
       </c>
       <c r="U36">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.132591373029367</v>
+        <v>8.337833322260867</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07349177084351527</v>
+        <v>0.0730850725706783</v>
       </c>
       <c r="C37">
-        <v>4240.703932157016</v>
+        <v>4276.541610088336</v>
       </c>
       <c r="D37">
-        <v>4999.668932157017</v>
+        <v>5035.506610088336</v>
       </c>
       <c r="E37">
         <v>-1961.135</v>
@@ -4321,37 +4321,37 @@
         <v>797.3</v>
       </c>
       <c r="M37">
-        <v>100.9210917349058</v>
+        <v>98.43684423490578</v>
       </c>
       <c r="N37">
-        <v>696.3789082650942</v>
+        <v>698.8631557650942</v>
       </c>
       <c r="O37">
-        <v>174.0947270662735</v>
+        <v>174.7157889412736</v>
       </c>
       <c r="P37">
-        <v>522.2841811988206</v>
+        <v>524.1473668238207</v>
       </c>
       <c r="Q37">
-        <v>1274.584181198821</v>
+        <v>1276.447366823821</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0884552445686155</v>
+        <v>0.0884353241488663</v>
       </c>
       <c r="T37">
         <v>0.8310418247485111</v>
       </c>
       <c r="U37">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.900231619514241</v>
+        <v>8.099609513053416</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07381983407404702</v>
+        <v>0.07299692127593015</v>
       </c>
       <c r="C38">
-        <v>4164.035506740464</v>
+        <v>4237.282529197329</v>
       </c>
       <c r="D38">
-        <v>4970.319506740464</v>
+        <v>5043.566529197329</v>
       </c>
       <c r="E38">
         <v>-1913.816</v>
@@ -4403,45 +4403,45 @@
         <v>797.3</v>
       </c>
       <c r="M38">
-        <v>106.3597774987602</v>
+        <v>101.2493254987602</v>
       </c>
       <c r="N38">
-        <v>690.9402225012398</v>
+        <v>696.0506745012398</v>
       </c>
       <c r="O38">
-        <v>172.7350556253099</v>
+        <v>174.0126686253099</v>
       </c>
       <c r="P38">
-        <v>518.2051668759298</v>
+        <v>522.0380058759298</v>
       </c>
       <c r="Q38">
-        <v>1270.50516687593</v>
+        <v>1274.33800587593</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.0890030430861919</v>
+        <v>0.08898286683913428</v>
       </c>
       <c r="T38">
         <v>0.8417144509225073</v>
       </c>
       <c r="U38">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.496254869556245</v>
+        <v>7.874620359913043</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07375414730457877</v>
+        <v>0.07290876998118198</v>
       </c>
       <c r="C39">
-        <v>4122.565401020455</v>
+        <v>4198.049291363461</v>
       </c>
       <c r="D39">
-        <v>4976.168401020455</v>
+        <v>5051.652291363461</v>
       </c>
       <c r="E39">
         <v>-1866.497</v>
@@ -4485,45 +4485,45 @@
         <v>797.3</v>
       </c>
       <c r="M39">
-        <v>109.3142157626147</v>
+        <v>104.0618067626147</v>
       </c>
       <c r="N39">
-        <v>687.9857842373852</v>
+        <v>693.2381932373853</v>
       </c>
       <c r="O39">
-        <v>171.9964460593463</v>
+        <v>173.3095483093463</v>
       </c>
       <c r="P39">
-        <v>515.9893381780389</v>
+        <v>519.9286449280389</v>
       </c>
       <c r="Q39">
-        <v>1268.289338178039</v>
+        <v>1272.228644928039</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08956823203289771</v>
+        <v>0.08954779183702979</v>
       </c>
       <c r="T39">
         <v>0.8527258906258367</v>
       </c>
       <c r="U39">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.293653386595264</v>
+        <v>7.661792782618095</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07368846053511052</v>
+        <v>0.07304861868643384</v>
       </c>
       <c r="C40">
-        <v>4081.109077057644</v>
+        <v>4137.914564716175</v>
       </c>
       <c r="D40">
-        <v>4982.031077057644</v>
+        <v>5038.836564716175</v>
       </c>
       <c r="E40">
         <v>-1819.178</v>
@@ -4567,37 +4567,37 @@
         <v>797.3</v>
       </c>
       <c r="M40">
-        <v>112.2686540264691</v>
+        <v>108.3127856264691</v>
       </c>
       <c r="N40">
-        <v>685.0313459735308</v>
+        <v>688.9872143735308</v>
       </c>
       <c r="O40">
-        <v>171.2578364933827</v>
+        <v>172.2468035933827</v>
       </c>
       <c r="P40">
-        <v>513.7735094801482</v>
+        <v>516.7404107801481</v>
       </c>
       <c r="Q40">
-        <v>1266.073509480148</v>
+        <v>1269.040410780148</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09015165288111016</v>
+        <v>0.09013094022195423</v>
       </c>
       <c r="T40">
         <v>0.8640925380615317</v>
       </c>
       <c r="U40">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.1017151395796</v>
+        <v>7.361088493740654</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07362277376564226</v>
+        <v>0.07296646739168568</v>
       </c>
       <c r="C41">
-        <v>4039.666583620447</v>
+        <v>4098.116012846031</v>
       </c>
       <c r="D41">
-        <v>4987.907583620447</v>
+        <v>5046.357012846031</v>
       </c>
       <c r="E41">
         <v>-1771.859</v>
@@ -4649,37 +4649,37 @@
         <v>797.3</v>
       </c>
       <c r="M41">
-        <v>115.2230922903236</v>
+        <v>111.1631220903236</v>
       </c>
       <c r="N41">
-        <v>682.0769077096763</v>
+        <v>686.1368779096764</v>
       </c>
       <c r="O41">
-        <v>170.5192269274191</v>
+        <v>171.5342194774191</v>
       </c>
       <c r="P41">
-        <v>511.5576807822573</v>
+        <v>514.6026584322573</v>
       </c>
       <c r="Q41">
-        <v>1263.857680782257</v>
+        <v>1266.902658432257</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09075420228172301</v>
+        <v>0.09073320822605649</v>
       </c>
       <c r="T41">
         <v>0.8758318624623315</v>
       </c>
       <c r="U41">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.919619879590377</v>
+        <v>7.172342634926791</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07355708699617401</v>
+        <v>0.07288431609693753</v>
       </c>
       <c r="C42">
-        <v>3998.237969707646</v>
+        <v>4058.339943021841</v>
       </c>
       <c r="D42">
-        <v>4993.797969707646</v>
+        <v>5053.899943021841</v>
       </c>
       <c r="E42">
         <v>-1724.54</v>
@@ -4731,37 +4731,37 @@
         <v>797.3</v>
       </c>
       <c r="M42">
-        <v>118.177530554178</v>
+        <v>114.013458554178</v>
       </c>
       <c r="N42">
-        <v>679.1224694458219</v>
+        <v>683.286541445822</v>
       </c>
       <c r="O42">
-        <v>169.7806173614555</v>
+        <v>170.8216353614555</v>
       </c>
       <c r="P42">
-        <v>509.3418520843665</v>
+        <v>512.4649060843665</v>
       </c>
       <c r="Q42">
-        <v>1261.641852084366</v>
+        <v>1264.764906084366</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.0913768366623563</v>
+        <v>0.09135555183029551</v>
       </c>
       <c r="T42">
         <v>0.8879624976764912</v>
       </c>
       <c r="U42">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.746629382600619</v>
+        <v>6.993034069053621</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07349140022670575</v>
+        <v>0.07280216480218937</v>
       </c>
       <c r="C43">
-        <v>3956.82328454976</v>
+        <v>4018.586456208139</v>
       </c>
       <c r="D43">
-        <v>4999.702284549759</v>
+        <v>5061.465456208139</v>
       </c>
       <c r="E43">
         <v>-1677.221</v>
@@ -4813,37 +4813,37 @@
         <v>797.3</v>
       </c>
       <c r="M43">
-        <v>121.1319688180325</v>
+        <v>116.8637950180325</v>
       </c>
       <c r="N43">
-        <v>676.1680311819674</v>
+        <v>680.4362049819674</v>
       </c>
       <c r="O43">
-        <v>169.0420077954919</v>
+        <v>170.1090512454919</v>
       </c>
       <c r="P43">
-        <v>507.1260233864756</v>
+        <v>510.3271537364756</v>
       </c>
       <c r="Q43">
-        <v>1259.426023386476</v>
+        <v>1262.627153736476</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09202057729318054</v>
+        <v>0.09199899182789856</v>
       </c>
       <c r="T43">
         <v>0.9005043408640123</v>
       </c>
       <c r="U43">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.582077446439627</v>
+        <v>6.822472262491337</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0734257134572375</v>
+        <v>0.07272001350744123</v>
       </c>
       <c r="C44">
-        <v>3915.4225776104</v>
+        <v>3978.855653974926</v>
       </c>
       <c r="D44">
-        <v>5005.6205776104</v>
+        <v>5069.053653974926</v>
       </c>
       <c r="E44">
         <v>-1629.902</v>
@@ -4895,37 +4895,37 @@
         <v>797.3</v>
       </c>
       <c r="M44">
-        <v>124.0864070818869</v>
+        <v>119.7141314818869</v>
       </c>
       <c r="N44">
-        <v>673.213592918113</v>
+        <v>677.585868518113</v>
       </c>
       <c r="O44">
-        <v>168.3033982295283</v>
+        <v>169.3964671295282</v>
       </c>
       <c r="P44">
-        <v>504.9101946885847</v>
+        <v>508.1894013885848</v>
       </c>
       <c r="Q44">
-        <v>1257.210194688585</v>
+        <v>1260.489401388585</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.09268651587679182</v>
+        <v>0.09266461941162582</v>
       </c>
       <c r="T44">
         <v>0.9134786614028271</v>
       </c>
       <c r="U44">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.425361316762495</v>
+        <v>6.660032446717734</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07336002668776925</v>
+        <v>0.07263786221269307</v>
       </c>
       <c r="C45">
-        <v>3874.035898587671</v>
+        <v>3939.147638502214</v>
       </c>
       <c r="D45">
-        <v>5011.552898587671</v>
+        <v>5076.664638502214</v>
       </c>
       <c r="E45">
         <v>-1582.583</v>
@@ -4977,37 +4977,37 @@
         <v>797.3</v>
       </c>
       <c r="M45">
-        <v>127.0408453457414</v>
+        <v>122.5644679457414</v>
       </c>
       <c r="N45">
-        <v>670.2591546542585</v>
+        <v>674.7355320542586</v>
       </c>
       <c r="O45">
-        <v>167.5647886635646</v>
+        <v>168.6838830135646</v>
       </c>
       <c r="P45">
-        <v>502.6943659906939</v>
+        <v>506.0516490406939</v>
       </c>
       <c r="Q45">
-        <v>1254.994365990694</v>
+        <v>1258.351649040694</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09337582072649472</v>
+        <v>0.0933536023491681</v>
       </c>
       <c r="T45">
         <v>0.9269082212587934</v>
       </c>
       <c r="U45">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.275934309395924</v>
+        <v>6.50514797121267</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07375633991830099</v>
+        <v>0.07255571091794492</v>
       </c>
       <c r="C46">
-        <v>3791.136943808894</v>
+        <v>3899.462512584618</v>
       </c>
       <c r="D46">
-        <v>4975.972943808894</v>
+        <v>5084.298512584618</v>
       </c>
       <c r="E46">
         <v>-1535.264</v>
@@ -5059,45 +5059,45 @@
         <v>797.3</v>
       </c>
       <c r="M46">
-        <v>132.9101340095959</v>
+        <v>125.4148044095958</v>
       </c>
       <c r="N46">
-        <v>664.3898659904041</v>
+        <v>671.8851955904041</v>
       </c>
       <c r="O46">
-        <v>166.097466497601</v>
+        <v>167.971298897601</v>
       </c>
       <c r="P46">
-        <v>498.2923994928031</v>
+        <v>503.9138966928031</v>
       </c>
       <c r="Q46">
-        <v>1250.592399492803</v>
+        <v>1256.213896692803</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09408974360654418</v>
+        <v>0.09406719182019405</v>
       </c>
       <c r="T46">
         <v>0.9408174082524728</v>
       </c>
       <c r="U46">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>5.998790129445182</v>
+        <v>6.357303699139655</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07370115314883273</v>
+        <v>0.07247355962319676</v>
       </c>
       <c r="C47">
-        <v>3748.74215928578</v>
+        <v>3859.800379635979</v>
       </c>
       <c r="D47">
-        <v>4980.897159285781</v>
+        <v>5091.95537963598</v>
       </c>
       <c r="E47">
         <v>-1487.945</v>
@@ -5141,45 +5141,45 @@
         <v>797.3</v>
       </c>
       <c r="M47">
-        <v>135.9308188734503</v>
+        <v>128.2651408734503</v>
       </c>
       <c r="N47">
-        <v>661.3691811265496</v>
+        <v>669.0348591265497</v>
       </c>
       <c r="O47">
-        <v>165.3422952816374</v>
+        <v>167.2587147816374</v>
       </c>
       <c r="P47">
-        <v>496.0268858449122</v>
+        <v>501.7761443449123</v>
       </c>
       <c r="Q47">
-        <v>1248.326885844912</v>
+        <v>1254.076144344912</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.0948296273185954</v>
+        <v>0.09480672999925727</v>
       </c>
       <c r="T47">
         <v>0.955232383864104</v>
       </c>
       <c r="U47">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y47">
-        <v>5.865483682124179</v>
+        <v>6.216030283603218</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07364596637936448</v>
+        <v>0.0727364083284486</v>
       </c>
       <c r="C48">
-        <v>3706.357130409568</v>
+        <v>3788.063471055946</v>
       </c>
       <c r="D48">
-        <v>4985.831130409568</v>
+        <v>5067.537471055946</v>
       </c>
       <c r="E48">
         <v>-1440.626</v>
@@ -5223,37 +5223,37 @@
         <v>797.3</v>
       </c>
       <c r="M48">
-        <v>138.9515037373047</v>
+        <v>133.2921513373047</v>
       </c>
       <c r="N48">
-        <v>658.3484962626952</v>
+        <v>664.0078486626952</v>
       </c>
       <c r="O48">
-        <v>164.5871240656738</v>
+        <v>166.0019621656738</v>
       </c>
       <c r="P48">
-        <v>493.7613721970214</v>
+        <v>498.0058864970214</v>
       </c>
       <c r="Q48">
-        <v>1246.061372197021</v>
+        <v>1250.305886497021</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09559691413109299</v>
+        <v>0.09557365848124878</v>
       </c>
       <c r="T48">
         <v>0.9701812474613514</v>
       </c>
       <c r="U48">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.737973167295392</v>
+        <v>5.981597505935505</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07359077960989623</v>
+        <v>0.07266175703370047</v>
       </c>
       <c r="C49">
-        <v>3663.981886200213</v>
+        <v>3747.655524124437</v>
       </c>
       <c r="D49">
-        <v>4990.774886200214</v>
+        <v>5074.448524124437</v>
       </c>
       <c r="E49">
         <v>-1393.307</v>
@@ -5305,37 +5305,37 @@
         <v>797.3</v>
       </c>
       <c r="M49">
-        <v>141.9721886011592</v>
+        <v>136.1898068011592</v>
       </c>
       <c r="N49">
-        <v>655.3278113988408</v>
+        <v>661.1101931988408</v>
       </c>
       <c r="O49">
-        <v>163.8319528497102</v>
+        <v>165.2775482997102</v>
       </c>
       <c r="P49">
-        <v>491.4958585491306</v>
+        <v>495.8326448991306</v>
       </c>
       <c r="Q49">
-        <v>1243.795858549131</v>
+        <v>1248.132644899131</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09639315516293009</v>
+        <v>0.09636952766067394</v>
       </c>
       <c r="T49">
         <v>0.9856942191188722</v>
       </c>
       <c r="U49">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.615888631821022</v>
+        <v>5.854329473894325</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07353559284042796</v>
+        <v>0.07258710573895229</v>
       </c>
       <c r="C50">
-        <v>3621.616455792892</v>
+        <v>3707.266453375668</v>
       </c>
       <c r="D50">
-        <v>4995.728455792892</v>
+        <v>5081.378453375668</v>
       </c>
       <c r="E50">
         <v>-1345.988</v>
@@ -5387,37 +5387,37 @@
         <v>797.3</v>
       </c>
       <c r="M50">
-        <v>144.9928734650136</v>
+        <v>139.0874622650136</v>
       </c>
       <c r="N50">
-        <v>652.3071265349863</v>
+        <v>658.2125377349863</v>
       </c>
       <c r="O50">
-        <v>163.0767816337466</v>
+        <v>164.5531344337466</v>
       </c>
       <c r="P50">
-        <v>489.2303449012397</v>
+        <v>493.6594033012398</v>
       </c>
       <c r="Q50">
-        <v>1241.53034490124</v>
+        <v>1245.95940330124</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09722002084983786</v>
+        <v>0.09719600719315388</v>
       </c>
       <c r="T50">
         <v>1.001803843532451</v>
       </c>
       <c r="U50">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.498890951991417</v>
+        <v>5.732364276521526</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07348040607095971</v>
+        <v>0.07251245444420415</v>
       </c>
       <c r="C51">
-        <v>3579.26086843856</v>
+        <v>3666.896336250263</v>
       </c>
       <c r="D51">
-        <v>5000.69186843856</v>
+        <v>5088.327336250263</v>
       </c>
       <c r="E51">
         <v>-1298.669</v>
@@ -5469,37 +5469,37 @@
         <v>797.3</v>
       </c>
       <c r="M51">
-        <v>148.0135583288681</v>
+        <v>141.9851177288681</v>
       </c>
       <c r="N51">
-        <v>649.2864416711319</v>
+        <v>655.3148822711319</v>
       </c>
       <c r="O51">
-        <v>162.321610417783</v>
+        <v>163.828720567783</v>
       </c>
       <c r="P51">
-        <v>486.964831253349</v>
+        <v>491.4861617033489</v>
       </c>
       <c r="Q51">
-        <v>1239.264831253349</v>
+        <v>1243.786161703349</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09807931264211457</v>
+        <v>0.09805489768769189</v>
       </c>
       <c r="T51">
         <v>1.018545217923034</v>
       </c>
       <c r="U51">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.386668687665063</v>
+        <v>5.615377250470067</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07342521930149146</v>
+        <v>0.072437803149456</v>
       </c>
       <c r="C52">
-        <v>3536.91515350454</v>
+        <v>3626.545250613044</v>
       </c>
       <c r="D52">
-        <v>5005.66515350454</v>
+        <v>5095.295250613044</v>
       </c>
       <c r="E52">
         <v>-1251.35</v>
@@ -5551,37 +5551,37 @@
         <v>797.3</v>
       </c>
       <c r="M52">
-        <v>151.0342431927225</v>
+        <v>144.8827731927225</v>
       </c>
       <c r="N52">
-        <v>646.2657568072774</v>
+        <v>652.4172268072774</v>
       </c>
       <c r="O52">
-        <v>161.5664392018193</v>
+        <v>163.1043067018194</v>
       </c>
       <c r="P52">
-        <v>484.6993176054581</v>
+        <v>489.312920105458</v>
       </c>
       <c r="Q52">
-        <v>1236.999317605458</v>
+        <v>1241.612920105458</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09897297610608234</v>
+        <v>0.09894814380201142</v>
       </c>
       <c r="T52">
         <v>1.03595624728924</v>
       </c>
       <c r="U52">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.278935313911761</v>
+        <v>5.503069705460665</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.0733700325320232</v>
+        <v>0.07236315185470785</v>
       </c>
       <c r="C53">
-        <v>3494.579340475094</v>
+        <v>3586.213274755919</v>
       </c>
       <c r="D53">
-        <v>5010.648340475094</v>
+        <v>5102.282274755918</v>
       </c>
       <c r="E53">
         <v>-1204.031</v>
@@ -5633,37 +5633,37 @@
         <v>797.3</v>
       </c>
       <c r="M53">
-        <v>154.054928056577</v>
+        <v>147.780428656577</v>
       </c>
       <c r="N53">
-        <v>643.245071943423</v>
+        <v>649.519571343423</v>
       </c>
       <c r="O53">
-        <v>160.8112679858557</v>
+        <v>162.3798928358557</v>
       </c>
       <c r="P53">
-        <v>482.4338039575672</v>
+        <v>487.1396785075672</v>
       </c>
       <c r="Q53">
-        <v>1234.733803957567</v>
+        <v>1239.439678507567</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.0999031156298039</v>
+        <v>0.0998778489414052</v>
       </c>
       <c r="T53">
         <v>1.054077930915291</v>
       </c>
       <c r="U53">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.175426778344864</v>
+        <v>5.395166377902613</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07331484576255494</v>
+        <v>0.07228850055995968</v>
       </c>
       <c r="C54">
-        <v>3452.253458952012</v>
+        <v>3545.900487400828</v>
       </c>
       <c r="D54">
-        <v>5015.641458952012</v>
+        <v>5109.288487400828</v>
       </c>
       <c r="E54">
         <v>-1156.712</v>
@@ -5715,37 +5715,37 @@
         <v>797.3</v>
       </c>
       <c r="M54">
-        <v>157.0756129204314</v>
+        <v>150.6780841204314</v>
       </c>
       <c r="N54">
-        <v>640.2243870795685</v>
+        <v>646.6219158795685</v>
       </c>
       <c r="O54">
-        <v>160.0560967698921</v>
+        <v>161.6554789698921</v>
       </c>
       <c r="P54">
-        <v>480.1682903096764</v>
+        <v>484.9664369096764</v>
       </c>
       <c r="Q54">
-        <v>1232.468290309676</v>
+        <v>1237.266436909676</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1008720109670138</v>
+        <v>0.1008462917949404</v>
       </c>
       <c r="T54">
         <v>1.072954684692427</v>
       </c>
       <c r="U54">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.075899340299769</v>
+        <v>5.291413178327563</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.0732596589930867</v>
+        <v>0.07221384926521153</v>
       </c>
       <c r="C55">
-        <v>3409.937538655187</v>
+        <v>3505.606967702688</v>
       </c>
       <c r="D55">
-        <v>5020.644538655188</v>
+        <v>5116.313967702688</v>
       </c>
       <c r="E55">
         <v>-1109.393</v>
@@ -5797,37 +5797,37 @@
         <v>797.3</v>
       </c>
       <c r="M55">
-        <v>160.0962977842859</v>
+        <v>153.5757395842859</v>
       </c>
       <c r="N55">
-        <v>637.2037022157141</v>
+        <v>643.7242604157141</v>
       </c>
       <c r="O55">
-        <v>159.3009255539285</v>
+        <v>160.9310651039285</v>
       </c>
       <c r="P55">
-        <v>477.9027766617855</v>
+        <v>482.7931953117856</v>
       </c>
       <c r="Q55">
-        <v>1230.202776661785</v>
+        <v>1235.093195311786</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1018821358930413</v>
+        <v>0.1018559449826686</v>
       </c>
       <c r="T55">
         <v>1.092634704587739</v>
       </c>
       <c r="U55">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.980127654633737</v>
+        <v>5.191575193830816</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07320447222361844</v>
+        <v>0.07213919797046338</v>
       </c>
       <c r="C56">
-        <v>3367.631609423225</v>
+        <v>3465.33279525239</v>
       </c>
       <c r="D56">
-        <v>5025.657609423225</v>
+        <v>5123.35879525239</v>
       </c>
       <c r="E56">
         <v>-1062.074</v>
@@ -5879,37 +5879,37 @@
         <v>797.3</v>
       </c>
       <c r="M56">
-        <v>163.1169826481404</v>
+        <v>156.4733950481404</v>
       </c>
       <c r="N56">
-        <v>634.1830173518596</v>
+        <v>640.8266049518596</v>
       </c>
       <c r="O56">
-        <v>158.5457543379649</v>
+        <v>160.2066512379649</v>
       </c>
       <c r="P56">
-        <v>475.6372630138947</v>
+        <v>480.6199537138947</v>
       </c>
       <c r="Q56">
-        <v>1227.937263013895</v>
+        <v>1232.919953713895</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1029361792941133</v>
+        <v>0.1029094961350806</v>
       </c>
       <c r="T56">
         <v>1.113170377521978</v>
       </c>
       <c r="U56">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.887903068436815</v>
+        <v>5.095434912463578</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07314928545415018</v>
+        <v>0.07206454667571524</v>
       </c>
       <c r="C57">
-        <v>3325.335701214012</v>
+        <v>3425.078050079786</v>
       </c>
       <c r="D57">
-        <v>5030.680701214013</v>
+        <v>5130.423050079787</v>
       </c>
       <c r="E57">
         <v>-1014.755</v>
@@ -5961,37 +5961,37 @@
         <v>797.3</v>
       </c>
       <c r="M57">
-        <v>166.1376675119948</v>
+        <v>159.3710505119948</v>
       </c>
       <c r="N57">
-        <v>631.1623324880052</v>
+        <v>637.9289494880052</v>
       </c>
       <c r="O57">
-        <v>157.7905831220013</v>
+        <v>159.4822373720013</v>
       </c>
       <c r="P57">
-        <v>473.3717493660039</v>
+        <v>478.4467121160039</v>
       </c>
       <c r="Q57">
-        <v>1225.671749366004</v>
+        <v>1230.746712116004</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1040370690685664</v>
+        <v>0.1040098717831554</v>
       </c>
       <c r="T57">
         <v>1.134618747031072</v>
       </c>
       <c r="U57">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.799032103556145</v>
+        <v>5.002790641327877</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07309409868468192</v>
+        <v>0.07198989538096708</v>
       </c>
       <c r="C58">
-        <v>3283.049844105335</v>
+        <v>3384.842812656738</v>
       </c>
       <c r="D58">
-        <v>5035.713844105335</v>
+        <v>5137.506812656738</v>
       </c>
       <c r="E58">
         <v>-967.4360000000001</v>
@@ -6043,37 +6043,37 @@
         <v>797.3</v>
       </c>
       <c r="M58">
-        <v>169.1583523758493</v>
+        <v>162.2687059758493</v>
       </c>
       <c r="N58">
-        <v>628.1416476241507</v>
+        <v>635.0312940241507</v>
       </c>
       <c r="O58">
-        <v>157.0354119060377</v>
+        <v>158.7578235060377</v>
       </c>
       <c r="P58">
-        <v>471.106235718113</v>
+        <v>476.2734705181131</v>
       </c>
       <c r="Q58">
-        <v>1223.406235718113</v>
+        <v>1228.573470518113</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1051879992873127</v>
+        <v>0.1051602645061426</v>
       </c>
       <c r="T58">
         <v>1.157042042426943</v>
       </c>
       <c r="U58">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.713335101706928</v>
+        <v>4.913455094161308</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07303891191521367</v>
+        <v>0.07191524408621891</v>
       </c>
       <c r="C59">
-        <v>3240.774068295461</v>
+        <v>3344.627163900156</v>
       </c>
       <c r="D59">
-        <v>5040.757068295461</v>
+        <v>5144.610163900156</v>
       </c>
       <c r="E59">
         <v>-920.1170000000002</v>
@@ -6125,37 +6125,37 @@
         <v>797.3</v>
       </c>
       <c r="M59">
-        <v>172.1790372397037</v>
+        <v>165.1663614397037</v>
       </c>
       <c r="N59">
-        <v>625.1209627602963</v>
+        <v>632.1336385602963</v>
       </c>
       <c r="O59">
-        <v>156.2802406900741</v>
+        <v>158.0334096400741</v>
       </c>
       <c r="P59">
-        <v>468.8407220702222</v>
+        <v>474.1002289202222</v>
       </c>
       <c r="Q59">
-        <v>1221.140722070222</v>
+        <v>1226.400228920222</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1063924611441403</v>
+        <v>0.1063641638674084</v>
       </c>
       <c r="T59">
         <v>1.180508281794715</v>
       </c>
       <c r="U59">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.630645012203299</v>
+        <v>4.827254127597074</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07298372514574542</v>
+        <v>0.07184059279147077</v>
       </c>
       <c r="C60">
-        <v>3198.508404103762</v>
+        <v>3304.431185175087</v>
       </c>
       <c r="D60">
-        <v>5045.810404103761</v>
+        <v>5151.733185175087</v>
       </c>
       <c r="E60">
         <v>-872.7980000000007</v>
@@ -6207,37 +6207,37 @@
         <v>797.3</v>
       </c>
       <c r="M60">
-        <v>175.1997221035581</v>
+        <v>168.0640169035581</v>
       </c>
       <c r="N60">
-        <v>622.1002778964419</v>
+        <v>629.2359830964418</v>
       </c>
       <c r="O60">
-        <v>155.5250694741105</v>
+        <v>157.3089957741105</v>
       </c>
       <c r="P60">
-        <v>466.5752084223314</v>
+        <v>471.9269873223313</v>
       </c>
       <c r="Q60">
-        <v>1218.875208422331</v>
+        <v>1224.226987322331</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1076542783274835</v>
+        <v>0.1076253917696867</v>
       </c>
       <c r="T60">
         <v>1.205091961132381</v>
       </c>
       <c r="U60">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.550806305096346</v>
+        <v>4.744025608155747</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07407903837627716</v>
+        <v>0.07176594149672261</v>
       </c>
       <c r="C61">
-        <v>3052.751943251336</v>
+        <v>3264.25495829783</v>
       </c>
       <c r="D61">
-        <v>4947.372943251336</v>
+        <v>5158.87595829783</v>
       </c>
       <c r="E61">
         <v>-825.4790000000007</v>
@@ -6289,45 +6289,45 @@
         <v>797.3</v>
       </c>
       <c r="M61">
-        <v>185.4791415674125</v>
+        <v>170.9616723674126</v>
       </c>
       <c r="N61">
-        <v>611.8208584325874</v>
+        <v>626.3383276325874</v>
       </c>
       <c r="O61">
-        <v>152.9552146081469</v>
+        <v>156.5845819081468</v>
       </c>
       <c r="P61">
-        <v>458.8656438244406</v>
+        <v>469.7537457244405</v>
       </c>
       <c r="Q61">
-        <v>1211.16564382444</v>
+        <v>1222.05374572444</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1089776475685508</v>
+        <v>0.1089481429842714</v>
       </c>
       <c r="T61">
         <v>1.230874844340177</v>
       </c>
       <c r="U61">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.298596560574552</v>
+        <v>4.663618394458191</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07404335160680892</v>
+        <v>0.07169129020197446</v>
       </c>
       <c r="C62">
-        <v>3008.579598478732</v>
+        <v>3224.098565539052</v>
       </c>
       <c r="D62">
-        <v>4950.519598478732</v>
+        <v>5166.038565539052</v>
       </c>
       <c r="E62">
         <v>-778.1600000000003</v>
@@ -6371,45 +6371,45 @@
         <v>797.3</v>
       </c>
       <c r="M62">
-        <v>188.622855831267</v>
+        <v>173.8593278312671</v>
       </c>
       <c r="N62">
-        <v>608.6771441687329</v>
+        <v>623.4406721687329</v>
       </c>
       <c r="O62">
-        <v>152.1692860421832</v>
+        <v>155.8601680421832</v>
       </c>
       <c r="P62">
-        <v>456.5078581265496</v>
+        <v>467.5805041265497</v>
       </c>
       <c r="Q62">
-        <v>1208.807858126549</v>
+        <v>1219.88050412655</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1103671852716714</v>
+        <v>0.1103370317595853</v>
       </c>
       <c r="T62">
         <v>1.257946871708362</v>
       </c>
       <c r="U62">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.226953284564974</v>
+        <v>4.585891421217221</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07400766483734066</v>
+        <v>0.0716166389072263</v>
       </c>
       <c r="C63">
-        <v>2964.411258959348</v>
+        <v>3183.962089626961</v>
       </c>
       <c r="D63">
-        <v>4953.670258959348</v>
+        <v>5173.221089626961</v>
       </c>
       <c r="E63">
         <v>-730.8410000000003</v>
@@ -6453,45 +6453,45 @@
         <v>797.3</v>
       </c>
       <c r="M63">
-        <v>191.7665700951215</v>
+        <v>176.7569832951215</v>
       </c>
       <c r="N63">
-        <v>605.5334299048785</v>
+        <v>620.5430167048785</v>
       </c>
       <c r="O63">
-        <v>151.3833574762196</v>
+        <v>155.1357541762196</v>
       </c>
       <c r="P63">
-        <v>454.1500724286589</v>
+        <v>465.4072625286589</v>
       </c>
       <c r="Q63">
-        <v>1206.450072428659</v>
+        <v>1217.707262528659</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1118279813185418</v>
+        <v>0.1117971456002999</v>
       </c>
       <c r="T63">
         <v>1.286407208172353</v>
       </c>
       <c r="U63">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.157658968424567</v>
+        <v>4.510712873328414</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0739719780678724</v>
+        <v>0.07270448761247815</v>
       </c>
       <c r="C64">
-        <v>2920.246932345242</v>
+        <v>3033.912315802784</v>
       </c>
       <c r="D64">
-        <v>4956.824932345242</v>
+        <v>5070.490315802784</v>
       </c>
       <c r="E64">
         <v>-683.5220000000004</v>
@@ -6535,37 +6535,37 @@
         <v>797.3</v>
       </c>
       <c r="M64">
-        <v>194.9102843589759</v>
+        <v>186.9890837589759</v>
       </c>
       <c r="N64">
-        <v>602.3897156410241</v>
+        <v>610.310916241024</v>
       </c>
       <c r="O64">
-        <v>150.597428910256</v>
+        <v>152.577729060256</v>
       </c>
       <c r="P64">
-        <v>451.7922867307681</v>
+        <v>457.733187180768</v>
       </c>
       <c r="Q64">
-        <v>1204.092286730768</v>
+        <v>1210.033187180768</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1133656613678791</v>
+        <v>0.1133341075378942</v>
       </c>
       <c r="T64">
         <v>1.316365457081816</v>
       </c>
       <c r="U64">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.090599952804815</v>
+        <v>4.263885270584559</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07393629129840415</v>
+        <v>0.07264858631773001</v>
       </c>
       <c r="C65">
-        <v>2876.086626307982</v>
+        <v>2991.772796854156</v>
       </c>
       <c r="D65">
-        <v>4959.983626307981</v>
+        <v>5075.669796854156</v>
       </c>
       <c r="E65">
         <v>-636.2030000000004</v>
@@ -6617,37 +6617,37 @@
         <v>797.3</v>
       </c>
       <c r="M65">
-        <v>198.0539986228304</v>
+        <v>190.0050367228304</v>
       </c>
       <c r="N65">
-        <v>599.2460013771696</v>
+        <v>607.2949632771696</v>
       </c>
       <c r="O65">
-        <v>149.8115003442924</v>
+        <v>151.8237408192924</v>
       </c>
       <c r="P65">
-        <v>449.4345010328772</v>
+        <v>455.4712224578772</v>
       </c>
       <c r="Q65">
-        <v>1201.734501032877</v>
+        <v>1207.771222457877</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1149864592577211</v>
+        <v>0.1149541484991423</v>
       </c>
       <c r="T65">
         <v>1.347943070797196</v>
       </c>
       <c r="U65">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.025669794823786</v>
+        <v>4.196204552003852</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.0751966045289359</v>
+        <v>0.07259268502298184</v>
       </c>
       <c r="C66">
-        <v>2719.600943042785</v>
+        <v>2949.643870354775</v>
       </c>
       <c r="D66">
-        <v>4850.816943042785</v>
+        <v>5080.859870354775</v>
       </c>
       <c r="E66">
         <v>-588.8840000000005</v>
@@ -6699,45 +6699,45 @@
         <v>797.3</v>
       </c>
       <c r="M66">
-        <v>209.3744360866848</v>
+        <v>193.0209896866848</v>
       </c>
       <c r="N66">
-        <v>587.9255639133152</v>
+        <v>604.2790103133151</v>
       </c>
       <c r="O66">
-        <v>146.9813909783288</v>
+        <v>151.0697525783288</v>
       </c>
       <c r="P66">
-        <v>440.9441729349863</v>
+        <v>453.2092577349863</v>
       </c>
       <c r="Q66">
-        <v>1193.244172934986</v>
+        <v>1205.509257734986</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1166973014747765</v>
+        <v>0.1166641917360152</v>
       </c>
       <c r="T66">
         <v>1.381274996385653</v>
       </c>
       <c r="U66">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.808010256180001</v>
+        <v>4.130638855878792</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07518116775946765</v>
+        <v>0.07253678372823369</v>
       </c>
       <c r="C67">
-        <v>2673.589979276913</v>
+        <v>2907.525568831494</v>
       </c>
       <c r="D67">
-        <v>4852.124979276913</v>
+        <v>5086.060568831494</v>
       </c>
       <c r="E67">
         <v>-541.5650000000005</v>
@@ -6781,45 +6781,45 @@
         <v>797.3</v>
       </c>
       <c r="M67">
-        <v>212.6459116505393</v>
+        <v>196.0369426505393</v>
       </c>
       <c r="N67">
-        <v>584.6540883494606</v>
+        <v>601.2630573494607</v>
       </c>
       <c r="O67">
-        <v>146.1635220873652</v>
+        <v>150.3157643373652</v>
       </c>
       <c r="P67">
-        <v>438.4905662620955</v>
+        <v>450.9472930120955</v>
       </c>
       <c r="Q67">
-        <v>1190.790566262095</v>
+        <v>1203.247293012095</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1185059061042351</v>
+        <v>0.1184719517292809</v>
       </c>
       <c r="T67">
         <v>1.416511603436307</v>
       </c>
       <c r="U67">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.749425483008001</v>
+        <v>4.06709056578835</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07516573098999937</v>
+        <v>0.07248088243348554</v>
       </c>
       <c r="C68">
-        <v>2627.57972113251</v>
+        <v>2865.417924944484</v>
       </c>
       <c r="D68">
-        <v>4853.43372113251</v>
+        <v>5091.271924944484</v>
       </c>
       <c r="E68">
         <v>-494.2460000000001</v>
@@ -6863,45 +6863,45 @@
         <v>797.3</v>
       </c>
       <c r="M68">
-        <v>215.9173872143938</v>
+        <v>199.0528956143937</v>
       </c>
       <c r="N68">
-        <v>581.3826127856062</v>
+        <v>598.2471043856062</v>
       </c>
       <c r="O68">
-        <v>145.3456531964015</v>
+        <v>149.5617760964016</v>
       </c>
       <c r="P68">
-        <v>436.0369595892046</v>
+        <v>448.6853282892047</v>
       </c>
       <c r="Q68">
-        <v>1188.336959589205</v>
+        <v>1200.985328289205</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1204208992413088</v>
+        <v>0.1203860505456799</v>
       </c>
       <c r="T68">
         <v>1.453820952078177</v>
       </c>
       <c r="U68">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.692616005992728</v>
+        <v>4.005467981458223</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07515029422053113</v>
+        <v>0.07418373113873739</v>
       </c>
       <c r="C69">
-        <v>2581.570169180695</v>
+        <v>2663.999257980596</v>
       </c>
       <c r="D69">
-        <v>4854.743169180695</v>
+        <v>4937.172257980596</v>
       </c>
       <c r="E69">
         <v>-446.9270000000001</v>
@@ -6945,37 +6945,37 @@
         <v>797.3</v>
       </c>
       <c r="M69">
-        <v>219.1888627782482</v>
+        <v>213.1651540782482</v>
       </c>
       <c r="N69">
-        <v>578.1111372217517</v>
+        <v>584.1348459217518</v>
       </c>
       <c r="O69">
-        <v>144.5277843054379</v>
+        <v>146.0337114804379</v>
       </c>
       <c r="P69">
-        <v>433.5833529163138</v>
+        <v>438.1011344413138</v>
       </c>
       <c r="Q69">
-        <v>1185.883352916314</v>
+        <v>1190.401134441314</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1224519525685083</v>
+        <v>0.1224161553509515</v>
       </c>
       <c r="T69">
         <v>1.493391473365008</v>
       </c>
       <c r="U69">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.637502334261493</v>
+        <v>3.740292373055161</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07513485745106288</v>
+        <v>0.07415407984398922</v>
       </c>
       <c r="C70">
-        <v>2535.561323993215</v>
+        <v>2619.2837139426</v>
       </c>
       <c r="D70">
-        <v>4856.053323993216</v>
+        <v>4939.7757139426</v>
       </c>
       <c r="E70">
         <v>-399.6080000000002</v>
@@ -7027,37 +7027,37 @@
         <v>797.3</v>
       </c>
       <c r="M70">
-        <v>222.4603383421027</v>
+        <v>216.3467235421027</v>
       </c>
       <c r="N70">
-        <v>574.8396616578973</v>
+        <v>580.9532764578973</v>
       </c>
       <c r="O70">
-        <v>143.7099154144743</v>
+        <v>145.2383191144743</v>
       </c>
       <c r="P70">
-        <v>431.129746243423</v>
+        <v>435.714957343423</v>
       </c>
       <c r="Q70">
-        <v>1183.429746243423</v>
+        <v>1188.014957343423</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1246099467286578</v>
+        <v>0.1245731417065526</v>
       </c>
       <c r="T70">
         <v>1.535435152232266</v>
       </c>
       <c r="U70">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.584009652875295</v>
+        <v>3.685288073451408</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07511942068159461</v>
+        <v>0.07412442854924106</v>
       </c>
       <c r="C71">
-        <v>2489.553186142432</v>
+        <v>2574.570917047553</v>
       </c>
       <c r="D71">
-        <v>4857.364186142432</v>
+        <v>4942.381917047554</v>
       </c>
       <c r="E71">
         <v>-352.2890000000002</v>
@@ -7109,37 +7109,37 @@
         <v>797.3</v>
       </c>
       <c r="M71">
-        <v>225.7318139059571</v>
+        <v>219.5282930059571</v>
       </c>
       <c r="N71">
-        <v>571.5681860940429</v>
+        <v>577.7717069940429</v>
       </c>
       <c r="O71">
-        <v>142.8920465235107</v>
+        <v>144.4429267485107</v>
       </c>
       <c r="P71">
-        <v>428.6761395705321</v>
+        <v>433.3287802455322</v>
       </c>
       <c r="Q71">
-        <v>1180.976139570532</v>
+        <v>1185.628780245532</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1269071663184943</v>
+        <v>0.1268692884721925</v>
       </c>
       <c r="T71">
         <v>1.580191326510315</v>
       </c>
       <c r="U71">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.532067483993044</v>
+        <v>3.631878101372403</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07757148391212637</v>
+        <v>0.07409477725449293</v>
       </c>
       <c r="C72">
-        <v>2242.517019856535</v>
+        <v>2529.860871645888</v>
       </c>
       <c r="D72">
-        <v>4657.647019856535</v>
+        <v>4944.990871645888</v>
       </c>
       <c r="E72">
         <v>-304.9700000000003</v>
@@ -7191,45 +7191,45 @@
         <v>797.3</v>
       </c>
       <c r="M72">
-        <v>244.5712404698116</v>
+        <v>222.7098624698116</v>
       </c>
       <c r="N72">
-        <v>552.7287595301884</v>
+        <v>574.5901375301884</v>
       </c>
       <c r="O72">
-        <v>138.1821898825471</v>
+        <v>143.6475343825471</v>
       </c>
       <c r="P72">
-        <v>414.5465696476413</v>
+        <v>430.9426031476413</v>
       </c>
       <c r="Q72">
-        <v>1166.846569647641</v>
+        <v>1183.242603147641</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1293575338809866</v>
+        <v>0.1293185116888751</v>
       </c>
       <c r="T72">
         <v>1.627931245740234</v>
       </c>
       <c r="U72">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.25999082503903</v>
+        <v>3.579994128495654</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07759129714265811</v>
+        <v>0.07406512595974477</v>
       </c>
       <c r="C73">
-        <v>2193.651125455445</v>
+        <v>2485.153582097237</v>
       </c>
       <c r="D73">
-        <v>4656.100125455445</v>
+        <v>4947.602582097236</v>
       </c>
       <c r="E73">
         <v>-257.6510000000007</v>
@@ -7273,45 +7273,45 @@
         <v>797.3</v>
       </c>
       <c r="M73">
-        <v>248.065115333666</v>
+        <v>225.891431933666</v>
       </c>
       <c r="N73">
-        <v>549.234884666334</v>
+        <v>571.4085680663339</v>
       </c>
       <c r="O73">
-        <v>137.3087211665835</v>
+        <v>142.8521420165835</v>
       </c>
       <c r="P73">
-        <v>411.9261634997505</v>
+        <v>428.5564260497505</v>
       </c>
       <c r="Q73">
-        <v>1164.22616349975</v>
+        <v>1180.856426049751</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1319768923098576</v>
+        <v>0.1319366468515357</v>
       </c>
       <c r="T73">
         <v>1.678963573192906</v>
       </c>
       <c r="U73">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.214075461306086</v>
+        <v>3.529571675981631</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07761111037318986</v>
+        <v>0.07554747466499662</v>
       </c>
       <c r="C74">
-        <v>2144.78625822014</v>
+        <v>2310.559668693903</v>
       </c>
       <c r="D74">
-        <v>4654.55425822014</v>
+        <v>4820.327668693903</v>
       </c>
       <c r="E74">
         <v>-210.3320000000008</v>
@@ -7355,37 +7355,37 @@
         <v>797.3</v>
       </c>
       <c r="M74">
-        <v>251.5589901975204</v>
+        <v>238.6125117975204</v>
       </c>
       <c r="N74">
-        <v>545.7410098024795</v>
+        <v>558.6874882024796</v>
       </c>
       <c r="O74">
-        <v>136.4352524506199</v>
+        <v>139.6718720506199</v>
       </c>
       <c r="P74">
-        <v>409.3057573518597</v>
+        <v>419.0156161518597</v>
       </c>
       <c r="Q74">
-        <v>1161.60575735186</v>
+        <v>1171.31561615186</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1347833477693623</v>
+        <v>0.1347417916686721</v>
       </c>
       <c r="T74">
         <v>1.733641066892197</v>
       </c>
       <c r="U74">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.169435524343502</v>
+        <v>3.341400641541234</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07763092360372162</v>
+        <v>0.07553882337024846</v>
       </c>
       <c r="C75">
-        <v>2095.922417127874</v>
+        <v>2263.964471897847</v>
       </c>
       <c r="D75">
-        <v>4653.009417127874</v>
+        <v>4821.051471897847</v>
       </c>
       <c r="E75">
         <v>-163.0130000000004</v>
@@ -7437,37 +7437,37 @@
         <v>797.3</v>
       </c>
       <c r="M75">
-        <v>255.0528650613749</v>
+        <v>241.9265744613749</v>
       </c>
       <c r="N75">
-        <v>542.247134938625</v>
+        <v>555.373425538625</v>
       </c>
       <c r="O75">
-        <v>135.5617837346562</v>
+        <v>138.8433563846563</v>
       </c>
       <c r="P75">
-        <v>406.6853512039687</v>
+        <v>416.5300691539688</v>
       </c>
       <c r="Q75">
-        <v>1158.985351203969</v>
+        <v>1168.830069153969</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1377976888184599</v>
+        <v>0.1377547249907816</v>
       </c>
       <c r="T75">
         <v>1.792368745309954</v>
       </c>
       <c r="U75">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.126018599352494</v>
+        <v>3.295628030013271</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07765073683425334</v>
+        <v>0.07553017207550031</v>
       </c>
       <c r="C76">
-        <v>2047.059601157263</v>
+        <v>2217.369492501849</v>
       </c>
       <c r="D76">
-        <v>4651.465601157263</v>
+        <v>4821.775492501849</v>
       </c>
       <c r="E76">
         <v>-115.6940000000004</v>
@@ -7519,37 +7519,37 @@
         <v>797.3</v>
       </c>
       <c r="M76">
-        <v>258.5467399252294</v>
+        <v>245.2406371252293</v>
       </c>
       <c r="N76">
-        <v>538.7532600747707</v>
+        <v>552.0593628747706</v>
       </c>
       <c r="O76">
-        <v>134.6883150186927</v>
+        <v>138.0148407186927</v>
       </c>
       <c r="P76">
-        <v>404.064945056078</v>
+        <v>414.044522156078</v>
       </c>
       <c r="Q76">
-        <v>1156.364945056078</v>
+        <v>1166.344522156078</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1410439022559497</v>
+        <v>0.1409994224145919</v>
       </c>
       <c r="T76">
         <v>1.855613937452154</v>
       </c>
       <c r="U76">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.08377510476665</v>
+        <v>3.251092516094173</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.0776705500647851</v>
+        <v>0.07552152078075217</v>
       </c>
       <c r="C77">
-        <v>1998.19780928827</v>
+        <v>2170.774730603868</v>
       </c>
       <c r="D77">
-        <v>4649.922809288269</v>
+        <v>4822.499730603868</v>
       </c>
       <c r="E77">
         <v>-68.37500000000045</v>
@@ -7601,37 +7601,37 @@
         <v>797.3</v>
       </c>
       <c r="M77">
-        <v>262.0406147890838</v>
+        <v>248.5546997890838</v>
       </c>
       <c r="N77">
-        <v>535.2593852109162</v>
+        <v>548.7453002109162</v>
       </c>
       <c r="O77">
-        <v>133.8148463027291</v>
+        <v>137.186325052729</v>
       </c>
       <c r="P77">
-        <v>401.4445389081872</v>
+        <v>411.5589751581871</v>
       </c>
       <c r="Q77">
-        <v>1153.744538908187</v>
+        <v>1163.858975158187</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1445498127684386</v>
+        <v>0.1445036956323069</v>
       </c>
       <c r="T77">
         <v>1.923918744965731</v>
       </c>
       <c r="U77">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.042658103369762</v>
+        <v>3.207744615879584</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07769036329531684</v>
+        <v>0.075512869486004</v>
       </c>
       <c r="C78">
-        <v>1949.337040502216</v>
+        <v>2124.180186301928</v>
       </c>
       <c r="D78">
-        <v>4648.381040502216</v>
+        <v>4823.224186301928</v>
       </c>
       <c r="E78">
         <v>-21.05600000000049</v>
@@ -7683,37 +7683,37 @@
         <v>797.3</v>
       </c>
       <c r="M78">
-        <v>265.5344896529382</v>
+        <v>251.8687624529382</v>
       </c>
       <c r="N78">
-        <v>531.7655103470618</v>
+        <v>545.4312375470618</v>
       </c>
       <c r="O78">
-        <v>132.9413775867654</v>
+        <v>136.3578093867654</v>
       </c>
       <c r="P78">
-        <v>398.8241327602963</v>
+        <v>409.0734281602963</v>
       </c>
       <c r="Q78">
-        <v>1151.124132760296</v>
+        <v>1161.373428160296</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1483478824903017</v>
+        <v>0.1482999916181649</v>
       </c>
       <c r="T78">
         <v>1.997915619772105</v>
       </c>
       <c r="U78">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.002623128325423</v>
+        <v>3.165537449881169</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08308092652584859</v>
+        <v>0.07550421819125586</v>
       </c>
       <c r="C79">
-        <v>1517.387194960751</v>
+        <v>2077.585859694105</v>
       </c>
       <c r="D79">
-        <v>4263.750194960751</v>
+        <v>4823.948859694105</v>
       </c>
       <c r="E79">
         <v>26.26299999999947</v>
@@ -7765,45 +7765,45 @@
         <v>797.3</v>
       </c>
       <c r="M79">
-        <v>302.9135004167927</v>
+        <v>255.1828251167927</v>
       </c>
       <c r="N79">
-        <v>494.3864995832073</v>
+        <v>542.1171748832073</v>
       </c>
       <c r="O79">
-        <v>123.5966248958018</v>
+        <v>135.5292937208018</v>
       </c>
       <c r="P79">
-        <v>370.7898746874055</v>
+        <v>406.5878811624055</v>
       </c>
       <c r="Q79">
-        <v>1123.089874687405</v>
+        <v>1158.887881162405</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1524762191445006</v>
+        <v>0.1524264002984453</v>
       </c>
       <c r="T79">
         <v>2.078347005431208</v>
       </c>
       <c r="U79">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.632104541075119</v>
+        <v>3.124426573908686</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08317048975638033</v>
+        <v>0.07549556689650769</v>
       </c>
       <c r="C80">
-        <v>1464.214459523695</v>
+        <v>2030.99175087854</v>
       </c>
       <c r="D80">
-        <v>4257.896459523696</v>
+        <v>4824.67375087854</v>
       </c>
       <c r="E80">
         <v>73.58199999999988</v>
@@ -7847,45 +7847,45 @@
         <v>797.3</v>
       </c>
       <c r="M80">
-        <v>306.8474419806471</v>
+        <v>258.4968877806472</v>
       </c>
       <c r="N80">
-        <v>490.4525580193528</v>
+        <v>538.8031122193528</v>
       </c>
       <c r="O80">
-        <v>122.6131395048382</v>
+        <v>134.7007780548382</v>
       </c>
       <c r="P80">
-        <v>367.8394185145146</v>
+        <v>404.1023341645146</v>
       </c>
       <c r="Q80">
-        <v>1120.139418514515</v>
+        <v>1156.402334164515</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1569798591308995</v>
+        <v>0.1569279370405693</v>
       </c>
       <c r="T80">
         <v>2.166090335241138</v>
       </c>
       <c r="U80">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.598359611061335</v>
+        <v>3.084369822961138</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08326005298691207</v>
+        <v>0.07548691560175955</v>
       </c>
       <c r="C81">
-        <v>1411.05777532658</v>
+        <v>1984.397859953426</v>
       </c>
       <c r="D81">
-        <v>4252.05877532658</v>
+        <v>4825.398859953426</v>
       </c>
       <c r="E81">
         <v>120.9009999999998</v>
@@ -7929,45 +7929,45 @@
         <v>797.3</v>
       </c>
       <c r="M81">
-        <v>310.7813835445016</v>
+        <v>261.8109504445016</v>
       </c>
       <c r="N81">
-        <v>486.5186164554983</v>
+        <v>535.4890495554984</v>
       </c>
       <c r="O81">
-        <v>121.6296541138746</v>
+        <v>133.8722623888746</v>
       </c>
       <c r="P81">
-        <v>364.8889623416237</v>
+        <v>401.6167871666238</v>
       </c>
       <c r="Q81">
-        <v>1117.188962341624</v>
+        <v>1153.916787166624</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1619124172112411</v>
+        <v>0.1618581915676576</v>
       </c>
       <c r="T81">
         <v>2.262190172652013</v>
       </c>
       <c r="U81">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.565468983073217</v>
+        <v>3.045327166974289</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08334961621744381</v>
+        <v>0.07547826430701139</v>
       </c>
       <c r="C82">
-        <v>1357.917076439821</v>
+        <v>1937.804187017024</v>
       </c>
       <c r="D82">
-        <v>4246.237076439821</v>
+        <v>4826.124187017024</v>
       </c>
       <c r="E82">
         <v>168.2199999999998</v>
@@ -8011,45 +8011,45 @@
         <v>797.3</v>
       </c>
       <c r="M82">
-        <v>314.7153251083561</v>
+        <v>265.1250131083561</v>
       </c>
       <c r="N82">
-        <v>482.5846748916439</v>
+        <v>532.1749868916438</v>
       </c>
       <c r="O82">
-        <v>120.646168722911</v>
+        <v>133.043746722911</v>
       </c>
       <c r="P82">
-        <v>361.9385061687329</v>
+        <v>399.1312401687329</v>
       </c>
       <c r="Q82">
-        <v>1114.238506168733</v>
+        <v>1151.431240168733</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1673382310996168</v>
+        <v>0.1672814715474547</v>
       </c>
       <c r="T82">
         <v>2.367899993803977</v>
       </c>
       <c r="U82">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.533400620784802</v>
+        <v>3.007260577387109</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08343917944797558</v>
+        <v>0.08020811301226324</v>
       </c>
       <c r="C83">
-        <v>1304.792297294413</v>
+        <v>1523.992136073482</v>
       </c>
       <c r="D83">
-        <v>4240.431297294414</v>
+        <v>4459.631136073482</v>
       </c>
       <c r="E83">
         <v>215.5389999999998</v>
@@ -8093,37 +8093,37 @@
         <v>797.3</v>
       </c>
       <c r="M83">
-        <v>318.6492666722105</v>
+        <v>298.3352199722106</v>
       </c>
       <c r="N83">
-        <v>478.6507333277895</v>
+        <v>498.9647800277894</v>
       </c>
       <c r="O83">
-        <v>119.6626833319474</v>
+        <v>124.7411950069474</v>
       </c>
       <c r="P83">
-        <v>358.9880499958421</v>
+        <v>374.2235850208421</v>
       </c>
       <c r="Q83">
-        <v>1111.288049995842</v>
+        <v>1126.523585020842</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1733351832920322</v>
+        <v>0.1732756231040725</v>
       </c>
       <c r="T83">
         <v>2.484737164550884</v>
       </c>
       <c r="U83">
-        <v>0.08313661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.06235246249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.502124069910916</v>
+        <v>2.672497065798223</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08641924267850731</v>
+        <v>0.08025796171751509</v>
       </c>
       <c r="C84">
-        <v>1072.954514707303</v>
+        <v>1473.106774431629</v>
       </c>
       <c r="D84">
-        <v>4055.912514707302</v>
+        <v>4456.064774431629</v>
       </c>
       <c r="E84">
         <v>262.8579999999997</v>
@@ -8175,45 +8175,45 @@
         <v>797.3</v>
       </c>
       <c r="M84">
-        <v>340.8199508360649</v>
+        <v>302.018370836065</v>
       </c>
       <c r="N84">
-        <v>456.480049163935</v>
+        <v>495.281629163935</v>
       </c>
       <c r="O84">
-        <v>114.1200122909838</v>
+        <v>123.8204072909837</v>
       </c>
       <c r="P84">
-        <v>342.3600368729512</v>
+        <v>371.4612218729512</v>
       </c>
       <c r="Q84">
-        <v>1094.660036872951</v>
+        <v>1123.761221872951</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1799984635058269</v>
+        <v>0.1799357915003146</v>
       </c>
       <c r="T84">
         <v>2.614556243158558</v>
       </c>
       <c r="U84">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.339358356352509</v>
+        <v>2.639905638166537</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08654405590903906</v>
+        <v>0.08030781042276694</v>
       </c>
       <c r="C85">
-        <v>1018.257092626316</v>
+        <v>1422.227112262124</v>
       </c>
       <c r="D85">
-        <v>4048.534092626316</v>
+        <v>4452.504112262124</v>
       </c>
       <c r="E85">
         <v>310.1769999999997</v>
@@ -8257,45 +8257,45 @@
         <v>797.3</v>
       </c>
       <c r="M85">
-        <v>344.9762916999194</v>
+        <v>305.7015216999195</v>
       </c>
       <c r="N85">
-        <v>452.3237083000806</v>
+        <v>491.5984783000805</v>
       </c>
       <c r="O85">
-        <v>113.0809270750201</v>
+        <v>122.8996195750201</v>
       </c>
       <c r="P85">
-        <v>339.2427812250604</v>
+        <v>368.6988587250604</v>
       </c>
       <c r="Q85">
-        <v>1091.54278122506</v>
+        <v>1120.99885872506</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1874456590388917</v>
+        <v>0.1873795091196439</v>
       </c>
       <c r="T85">
         <v>2.759648154543606</v>
       </c>
       <c r="U85">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>2.311173315914528</v>
+        <v>2.608099546140434</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.08666886913957081</v>
+        <v>0.08035765912801879</v>
       </c>
       <c r="C86">
-        <v>963.5864671066638</v>
+        <v>1371.353135913218</v>
       </c>
       <c r="D86">
-        <v>4041.182467106663</v>
+        <v>4448.949135913218</v>
       </c>
       <c r="E86">
         <v>357.4959999999992</v>
@@ -8339,45 +8339,45 @@
         <v>797.3</v>
       </c>
       <c r="M86">
-        <v>349.1326325637738</v>
+        <v>309.3846725637738</v>
       </c>
       <c r="N86">
-        <v>448.1673674362262</v>
+        <v>487.9153274362261</v>
       </c>
       <c r="O86">
-        <v>112.0418418590565</v>
+        <v>121.9788318590565</v>
       </c>
       <c r="P86">
-        <v>336.1255255771696</v>
+        <v>365.9364955771696</v>
       </c>
       <c r="Q86">
-        <v>1088.42552557717</v>
+        <v>1118.23649557717</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1958237540135895</v>
+        <v>0.1957536914413893</v>
       </c>
       <c r="T86">
         <v>2.922876554851783</v>
       </c>
       <c r="U86">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.283659347867927</v>
+        <v>2.577050742019715</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.08679368237010256</v>
+        <v>0.08040750783327064</v>
       </c>
       <c r="C87">
-        <v>908.9424924354516</v>
+        <v>1320.484831776726</v>
       </c>
       <c r="D87">
-        <v>4033.857492435452</v>
+        <v>4445.399831776726</v>
       </c>
       <c r="E87">
         <v>404.8149999999996</v>
@@ -8421,45 +8421,45 @@
         <v>797.3</v>
       </c>
       <c r="M87">
-        <v>353.2889734276283</v>
+        <v>313.0678234276284</v>
       </c>
       <c r="N87">
-        <v>444.0110265723717</v>
+        <v>484.2321765723716</v>
       </c>
       <c r="O87">
-        <v>111.0027566430929</v>
+        <v>121.0580441430929</v>
       </c>
       <c r="P87">
-        <v>333.0082699292788</v>
+        <v>363.1741324292787</v>
       </c>
       <c r="Q87">
-        <v>1085.308269929279</v>
+        <v>1115.474132429279</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2053189283182471</v>
+        <v>0.2052444314060343</v>
       </c>
       <c r="T87">
         <v>3.107868741867719</v>
       </c>
       <c r="U87">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.256792767304774</v>
+        <v>2.546732497995953</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.08691849560063429</v>
+        <v>0.08045735653852248</v>
       </c>
       <c r="C88">
-        <v>854.325023954339</v>
+        <v>1269.622186287857</v>
       </c>
       <c r="D88">
-        <v>4026.559023954339</v>
+        <v>4441.856186287857</v>
       </c>
       <c r="E88">
         <v>452.1339999999996</v>
@@ -8503,45 +8503,45 @@
         <v>797.3</v>
       </c>
       <c r="M88">
-        <v>357.4453142914827</v>
+        <v>316.7509742914828</v>
       </c>
       <c r="N88">
-        <v>439.8546857085173</v>
+        <v>480.5490257085171</v>
       </c>
       <c r="O88">
-        <v>109.9636714271293</v>
+        <v>120.1372564271293</v>
       </c>
       <c r="P88">
-        <v>329.8910142813879</v>
+        <v>360.4117692813879</v>
       </c>
       <c r="Q88">
-        <v>1082.191014281388</v>
+        <v>1112.711769281388</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2161705560949985</v>
+        <v>0.2160909913656284</v>
       </c>
       <c r="T88">
         <v>3.319288384171645</v>
       </c>
       <c r="U88">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.230550990940765</v>
+        <v>2.517119329414605</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.08704330883116604</v>
+        <v>0.08305195524377432</v>
       </c>
       <c r="C89">
-        <v>799.7339180500157</v>
+        <v>1045.347447420814</v>
       </c>
       <c r="D89">
-        <v>4019.286918050015</v>
+        <v>4264.900447420814</v>
       </c>
       <c r="E89">
         <v>499.4529999999995</v>
@@ -8585,37 +8585,37 @@
         <v>797.3</v>
       </c>
       <c r="M89">
-        <v>361.6016551553372</v>
+        <v>336.4894618553372</v>
       </c>
       <c r="N89">
-        <v>435.6983448446628</v>
+        <v>460.8105381446628</v>
       </c>
       <c r="O89">
-        <v>108.9245862111657</v>
+        <v>115.2026345361657</v>
       </c>
       <c r="P89">
-        <v>326.7737586334971</v>
+        <v>345.6079036084971</v>
       </c>
       <c r="Q89">
-        <v>1079.073758633497</v>
+        <v>1097.907903608497</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2286916650681733</v>
+        <v>0.2286062528574678</v>
       </c>
       <c r="T89">
         <v>3.56323412529156</v>
       </c>
       <c r="U89">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.204912473803515</v>
+        <v>2.369464991871791</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.08716812206169777</v>
+        <v>0.08313105394902617</v>
       </c>
       <c r="C90">
-        <v>745.1690321447859</v>
+        <v>992.8549873494285</v>
       </c>
       <c r="D90">
-        <v>4012.041032144786</v>
+        <v>4259.726987349429</v>
       </c>
       <c r="E90">
         <v>546.7719999999999</v>
@@ -8667,37 +8667,37 @@
         <v>797.3</v>
       </c>
       <c r="M90">
-        <v>365.7579960191916</v>
+        <v>340.3571568191917</v>
       </c>
       <c r="N90">
-        <v>431.5420039808083</v>
+        <v>456.9428431808083</v>
       </c>
       <c r="O90">
-        <v>107.8855009952021</v>
+        <v>114.2357107952021</v>
       </c>
       <c r="P90">
-        <v>323.6565029856063</v>
+        <v>342.7071323856062</v>
       </c>
       <c r="Q90">
-        <v>1075.956502985606</v>
+        <v>1095.007132385606</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2432996255368773</v>
+        <v>0.2432073912646139</v>
       </c>
       <c r="T90">
         <v>3.847837489931462</v>
       </c>
       <c r="U90">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.179856650237566</v>
+        <v>2.342539253327793</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.08729293529222952</v>
+        <v>0.083210152654278</v>
       </c>
       <c r="C91">
-        <v>690.6302246872474</v>
+        <v>940.3750632152178</v>
       </c>
       <c r="D91">
-        <v>4004.821224687247</v>
+        <v>4254.566063215218</v>
       </c>
       <c r="E91">
         <v>594.0909999999994</v>
@@ -8749,37 +8749,37 @@
         <v>797.3</v>
       </c>
       <c r="M91">
-        <v>369.9143368830461</v>
+        <v>344.2248517830461</v>
       </c>
       <c r="N91">
-        <v>427.3856631169539</v>
+        <v>453.0751482169538</v>
       </c>
       <c r="O91">
-        <v>106.8464157792385</v>
+        <v>113.2687870542385</v>
       </c>
       <c r="P91">
-        <v>320.5392473377154</v>
+        <v>339.8063611627153</v>
       </c>
       <c r="Q91">
-        <v>1072.839247337715</v>
+        <v>1092.106361162715</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2605635788180728</v>
+        <v>0.2604632821094228</v>
       </c>
       <c r="T91">
         <v>4.184186920869527</v>
       </c>
       <c r="U91">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.155363878886582</v>
+        <v>2.316218587560066</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.08741774852276127</v>
+        <v>0.08328925135952985</v>
       </c>
       <c r="C92">
-        <v>636.117355143072</v>
+        <v>887.9076295091108</v>
       </c>
       <c r="D92">
-        <v>3997.627355143072</v>
+        <v>4249.417629509111</v>
       </c>
       <c r="E92">
         <v>641.4099999999999</v>
@@ -8831,37 +8831,37 @@
         <v>797.3</v>
       </c>
       <c r="M92">
-        <v>374.0706777469006</v>
+        <v>348.0925467469006</v>
       </c>
       <c r="N92">
-        <v>423.2293222530994</v>
+        <v>449.2074532530994</v>
       </c>
       <c r="O92">
-        <v>105.8073305632748</v>
+        <v>112.3018633132749</v>
       </c>
       <c r="P92">
-        <v>317.4219916898246</v>
+        <v>336.9055899398246</v>
       </c>
       <c r="Q92">
-        <v>1069.721991689825</v>
+        <v>1089.205589939824</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2812803227555076</v>
+        <v>0.2811703511231934</v>
       </c>
       <c r="T92">
         <v>4.587806237995205</v>
       </c>
       <c r="U92">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.131415391343397</v>
+        <v>2.290482825476065</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.08754256175329302</v>
+        <v>0.0833683500647817</v>
       </c>
       <c r="C93">
-        <v>581.6302839858945</v>
+        <v>835.4526409420587</v>
       </c>
       <c r="D93">
-        <v>3990.459283985894</v>
+        <v>4244.281640942058</v>
       </c>
       <c r="E93">
         <v>688.7289999999994</v>
@@ -8913,37 +8913,37 @@
         <v>797.3</v>
       </c>
       <c r="M93">
-        <v>378.227018610755</v>
+        <v>351.960241710755</v>
       </c>
       <c r="N93">
-        <v>419.072981389245</v>
+        <v>445.339758289245</v>
       </c>
       <c r="O93">
-        <v>104.7682453473113</v>
+        <v>111.3349395723112</v>
       </c>
       <c r="P93">
-        <v>314.3047360419338</v>
+        <v>334.0048187169338</v>
       </c>
       <c r="Q93">
-        <v>1066.604736041934</v>
+        <v>1086.304818716934</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3066007875679278</v>
+        <v>0.3064789910289132</v>
       </c>
       <c r="T93">
         <v>5.081118736704368</v>
       </c>
       <c r="U93">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.107993244185778</v>
+        <v>2.265312684536767</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.08766737498382476</v>
+        <v>0.08344744877003354</v>
       </c>
       <c r="C94">
-        <v>527.1688726882812</v>
+        <v>783.0100524437012</v>
       </c>
       <c r="D94">
-        <v>3983.316872688281</v>
+        <v>4239.158052443701</v>
       </c>
       <c r="E94">
         <v>736.0479999999998</v>
@@ -8995,37 +8995,37 @@
         <v>797.3</v>
       </c>
       <c r="M94">
-        <v>382.3833594746094</v>
+        <v>355.8279366746095</v>
       </c>
       <c r="N94">
-        <v>414.9166405253905</v>
+        <v>441.4720633253905</v>
       </c>
       <c r="O94">
-        <v>103.7291601313476</v>
+        <v>110.3680158313476</v>
       </c>
       <c r="P94">
-        <v>311.1874803940429</v>
+        <v>331.1040474940428</v>
       </c>
       <c r="Q94">
-        <v>1063.487480394043</v>
+        <v>1083.404047494043</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3382513685834531</v>
+        <v>0.3381147909110629</v>
       </c>
       <c r="T94">
         <v>5.697759360090822</v>
       </c>
       <c r="U94">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V94">
         <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.08508027414028</v>
+        <v>2.240689720574411</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.08779218821435651</v>
+        <v>0.0835265474752854</v>
       </c>
       <c r="C95">
-        <v>472.7329837128182</v>
+        <v>730.5798191610411</v>
       </c>
       <c r="D95">
-        <v>3976.199983712818</v>
+        <v>4234.046819161041</v>
       </c>
       <c r="E95">
         <v>783.3669999999993</v>
@@ -9077,37 +9077,37 @@
         <v>797.3</v>
       </c>
       <c r="M95">
-        <v>386.5397003384638</v>
+        <v>359.6956316384639</v>
       </c>
       <c r="N95">
-        <v>410.7602996615361</v>
+        <v>437.604368361536</v>
       </c>
       <c r="O95">
-        <v>102.690074915384</v>
+        <v>109.401092090384</v>
       </c>
       <c r="P95">
-        <v>308.0702247461521</v>
+        <v>328.203276271152</v>
       </c>
       <c r="Q95">
-        <v>1060.370224746152</v>
+        <v>1080.503276271152</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3789449727462713</v>
+        <v>0.3787893907595412</v>
       </c>
       <c r="T95">
         <v>6.490583018730547</v>
       </c>
       <c r="U95">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V95">
         <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.062660056138772</v>
+        <v>2.216596282718772</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08791700144488825</v>
+        <v>0.08360564618053724</v>
       </c>
       <c r="C96">
-        <v>418.3224805032714</v>
+        <v>678.1618964571462</v>
       </c>
       <c r="D96">
-        <v>3969.108480503271</v>
+        <v>4228.947896457146</v>
       </c>
       <c r="E96">
         <v>830.6859999999997</v>
@@ -9159,37 +9159,37 @@
         <v>797.3</v>
       </c>
       <c r="M96">
-        <v>390.6960412023183</v>
+        <v>363.5633266023183</v>
       </c>
       <c r="N96">
-        <v>406.6039587976816</v>
+        <v>433.7366733976816</v>
       </c>
       <c r="O96">
-        <v>101.6509896994204</v>
+        <v>108.4341683494204</v>
       </c>
       <c r="P96">
-        <v>304.9529690982612</v>
+        <v>325.3025050482612</v>
       </c>
       <c r="Q96">
-        <v>1057.252969098261</v>
+        <v>1077.602505048261</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4332031116300288</v>
+        <v>0.4330221905575121</v>
       </c>
       <c r="T96">
         <v>7.547681230250181</v>
       </c>
       <c r="U96">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.040716864052189</v>
+        <v>2.193015471200487</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08804181467541999</v>
+        <v>0.08368474488578909</v>
       </c>
       <c r="C97">
-        <v>363.9372274758589</v>
+        <v>625.7562399098415</v>
       </c>
       <c r="D97">
-        <v>3962.042227475859</v>
+        <v>4223.861239909842</v>
       </c>
       <c r="E97">
         <v>878.0050000000001</v>
@@ -9241,37 +9241,37 @@
         <v>797.3</v>
       </c>
       <c r="M97">
-        <v>394.8523820661728</v>
+        <v>367.4310215661728</v>
       </c>
       <c r="N97">
-        <v>402.4476179338271</v>
+        <v>429.8689784338271</v>
       </c>
       <c r="O97">
-        <v>100.6119044834568</v>
+        <v>107.4672446084568</v>
       </c>
       <c r="P97">
-        <v>301.8357134503703</v>
+        <v>322.4017338253703</v>
       </c>
       <c r="Q97">
-        <v>1054.13571345037</v>
+        <v>1074.70173382537</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5091645060672897</v>
+        <v>0.5089481102746716</v>
       </c>
       <c r="T97">
         <v>9.027618726377673</v>
       </c>
       <c r="U97">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V97">
         <v>0.25</v>
       </c>
       <c r="W97">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.019235633904271</v>
+        <v>2.16993109781943</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.09990262790595175</v>
+        <v>0.08376384359104094</v>
       </c>
       <c r="C98">
-        <v>-256.6892824596689</v>
+        <v>573.3628053104248</v>
       </c>
       <c r="D98">
-        <v>3388.734717540331</v>
+        <v>4218.786805310425</v>
       </c>
       <c r="E98">
         <v>925.3239999999996</v>
@@ -9323,45 +9323,45 @@
         <v>797.3</v>
       </c>
       <c r="M98">
-        <v>473.0534941300273</v>
+        <v>371.2987165300273</v>
       </c>
       <c r="N98">
-        <v>324.2465058699727</v>
+        <v>426.0012834699727</v>
       </c>
       <c r="O98">
-        <v>81.06162646749317</v>
+        <v>106.5003208674932</v>
       </c>
       <c r="P98">
-        <v>243.1848794024795</v>
+        <v>319.5009626024795</v>
       </c>
       <c r="Q98">
-        <v>995.4848794024795</v>
+        <v>1071.80096260248</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6231065977231792</v>
+        <v>0.6228369898504091</v>
       </c>
       <c r="T98">
         <v>11.24752497056888</v>
       </c>
       <c r="U98">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V98">
         <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.685433063899635</v>
+        <v>2.14732764888381</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1001496911364835</v>
+        <v>0.08384294229629277</v>
       </c>
       <c r="C99">
-        <v>-314.1916800359731</v>
+        <v>520.9815486623829</v>
       </c>
       <c r="D99">
-        <v>3378.551319964026</v>
+        <v>4213.724548662382</v>
       </c>
       <c r="E99">
         <v>972.6429999999991</v>
@@ -9405,45 +9405,45 @@
         <v>797.3</v>
       </c>
       <c r="M99">
-        <v>477.9811346938817</v>
+        <v>375.1664114938817</v>
       </c>
       <c r="N99">
-        <v>319.3188653061183</v>
+        <v>422.1335885061183</v>
       </c>
       <c r="O99">
-        <v>79.82971632652956</v>
+        <v>105.5333971265296</v>
       </c>
       <c r="P99">
-        <v>239.4891489795887</v>
+        <v>316.6001913795887</v>
       </c>
       <c r="Q99">
-        <v>991.7891489795886</v>
+        <v>1068.900191379589</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8130100838163302</v>
+        <v>0.8126517891433068</v>
       </c>
       <c r="T99">
         <v>14.94736871088759</v>
       </c>
       <c r="U99">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V99">
         <v>0.25</v>
       </c>
       <c r="W99">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.668057465302732</v>
+        <v>2.12519025044171</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1003967543670152</v>
+        <v>0.08392204100154463</v>
       </c>
       <c r="C100">
-        <v>-371.6330572624593</v>
+        <v>468.6124261801178</v>
       </c>
       <c r="D100">
-        <v>3368.42894273754</v>
+        <v>4208.674426180118</v>
       </c>
       <c r="E100">
         <v>1019.962</v>
@@ -9487,45 +9487,45 @@
         <v>797.3</v>
       </c>
       <c r="M100">
-        <v>482.9087752577362</v>
+        <v>379.0341064577362</v>
       </c>
       <c r="N100">
-        <v>314.3912247422638</v>
+        <v>418.2658935422638</v>
       </c>
       <c r="O100">
-        <v>78.59780618556594</v>
+        <v>104.5664733855659</v>
       </c>
       <c r="P100">
-        <v>235.7934185566978</v>
+        <v>313.6994201566978</v>
       </c>
       <c r="Q100">
-        <v>988.0934185566978</v>
+        <v>1065.999420156698</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.192817056002633</v>
+        <v>1.192281387729103</v>
       </c>
       <c r="T100">
         <v>22.34705619152501</v>
       </c>
       <c r="U100">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V100">
         <v>0.25</v>
       </c>
       <c r="W100">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.651036470758826</v>
+        <v>2.103504635641284</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.100643817597547</v>
+        <v>0.08400113970679648</v>
       </c>
       <c r="C101">
-        <v>-429.0139609645676</v>
+        <v>416.2553942876921</v>
       </c>
       <c r="D101">
-        <v>3358.367039035431</v>
+        <v>4203.636394287691</v>
       </c>
       <c r="E101">
         <v>1067.280999999999</v>
@@ -9569,45 +9569,45 @@
         <v>797.3</v>
       </c>
       <c r="M101">
-        <v>487.8364158215905</v>
+        <v>382.9018014215906</v>
       </c>
       <c r="N101">
-        <v>309.4635841784094</v>
+        <v>414.3981985784094</v>
       </c>
       <c r="O101">
-        <v>77.36589604460235</v>
+        <v>103.5995496446023</v>
       </c>
       <c r="P101">
-        <v>232.0976881338071</v>
+        <v>310.798648933807</v>
       </c>
       <c r="Q101">
-        <v>984.397688133807</v>
+        <v>1063.098648933807</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.332237972561539</v>
+        <v>2.331170183486489</v>
       </c>
       <c r="T101">
         <v>44.54611863343727</v>
       </c>
       <c r="U101">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V101">
         <v>0.25</v>
       </c>
       <c r="W101">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y101">
-        <v>1.634359334690556</v>
+        <v>2.08225711406915</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/france/france_cable_tv.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07617036788686367</v>
+        <v>0.07605821659211551</v>
       </c>
       <c r="C2">
-        <v>5665.978885845398</v>
+        <v>5627.859651101419</v>
       </c>
       <c r="D2">
-        <v>4768.778885845398</v>
+        <v>4777.97865110142</v>
       </c>
       <c r="E2">
-        <v>-3617.3</v>
+        <v>-3569.981</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>47.319</v>
       </c>
       <c r="G2">
         <v>897.2</v>
@@ -1451,28 +1451,28 @@
         <v>797.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.661060463854451</v>
       </c>
       <c r="N2">
-        <v>797.3</v>
+        <v>794.6389395361455</v>
       </c>
       <c r="O2">
-        <v>199.325</v>
+        <v>198.6597348840364</v>
       </c>
       <c r="P2">
-        <v>597.9749999999999</v>
+        <v>595.979204652109</v>
       </c>
       <c r="Q2">
-        <v>1350.275</v>
+        <v>1348.279204652109</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07617036788686367</v>
+        <v>0.07640044643146111</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5964596575301683</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>299.6173934526611</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07605821659211551</v>
+        <v>0.07594606529736736</v>
       </c>
       <c r="C3">
-        <v>5627.859651101419</v>
+        <v>5589.77598071245</v>
       </c>
       <c r="D3">
-        <v>4777.97865110142</v>
+        <v>4787.21398071245</v>
       </c>
       <c r="E3">
-        <v>-3569.981</v>
+        <v>-3522.662</v>
       </c>
       <c r="F3">
-        <v>47.319</v>
+        <v>94.63799999999999</v>
       </c>
       <c r="G3">
         <v>897.2</v>
@@ -1533,28 +1533,28 @@
         <v>797.3</v>
       </c>
       <c r="M3">
-        <v>2.661060463854451</v>
+        <v>5.322120927708902</v>
       </c>
       <c r="N3">
-        <v>794.6389395361455</v>
+        <v>791.9778790722911</v>
       </c>
       <c r="O3">
-        <v>198.6597348840364</v>
+        <v>197.9944697680728</v>
       </c>
       <c r="P3">
-        <v>595.979204652109</v>
+        <v>593.9834093042183</v>
       </c>
       <c r="Q3">
-        <v>1348.279204652109</v>
+        <v>1346.283409304218</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07640044643146111</v>
+        <v>0.07663522045656056</v>
       </c>
       <c r="T3">
-        <v>0.5964596575301683</v>
+        <v>0.6010358402640196</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>299.6173934526611</v>
+        <v>149.8086967263306</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07594606529736736</v>
+        <v>0.0758339140026192</v>
       </c>
       <c r="C4">
-        <v>5589.77598071245</v>
+        <v>5551.728081304334</v>
       </c>
       <c r="D4">
-        <v>4787.21398071245</v>
+        <v>4796.485081304334</v>
       </c>
       <c r="E4">
-        <v>-3522.662</v>
+        <v>-3475.343</v>
       </c>
       <c r="F4">
-        <v>94.63799999999999</v>
+        <v>141.957</v>
       </c>
       <c r="G4">
         <v>897.2</v>
@@ -1615,28 +1615,28 @@
         <v>797.3</v>
       </c>
       <c r="M4">
-        <v>5.322120927708902</v>
+        <v>7.983181391563352</v>
       </c>
       <c r="N4">
-        <v>791.9778790722911</v>
+        <v>789.3168186084366</v>
       </c>
       <c r="O4">
-        <v>197.9944697680728</v>
+        <v>197.3292046521092</v>
       </c>
       <c r="P4">
-        <v>593.9834093042183</v>
+        <v>591.9876139563274</v>
       </c>
       <c r="Q4">
-        <v>1346.283409304218</v>
+        <v>1344.287613956327</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07663522045656056</v>
+        <v>0.07687483518320844</v>
       </c>
       <c r="T4">
-        <v>0.6010358402640196</v>
+        <v>0.6057063772810429</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>149.8086967263306</v>
+        <v>99.87246448422039</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0758339140026192</v>
+        <v>0.07572176270787105</v>
       </c>
       <c r="C5">
-        <v>5551.728081304334</v>
+        <v>5513.716161106659</v>
       </c>
       <c r="D5">
-        <v>4796.485081304334</v>
+        <v>4805.792161106659</v>
       </c>
       <c r="E5">
-        <v>-3475.343</v>
+        <v>-3428.024</v>
       </c>
       <c r="F5">
-        <v>141.957</v>
+        <v>189.276</v>
       </c>
       <c r="G5">
         <v>897.2</v>
@@ -1697,28 +1697,28 @@
         <v>797.3</v>
       </c>
       <c r="M5">
-        <v>7.983181391563352</v>
+        <v>10.6442418554178</v>
       </c>
       <c r="N5">
-        <v>789.3168186084366</v>
+        <v>786.6557581445821</v>
       </c>
       <c r="O5">
-        <v>197.3292046521092</v>
+        <v>196.6639395361455</v>
       </c>
       <c r="P5">
-        <v>591.9876139563274</v>
+        <v>589.9918186084366</v>
       </c>
       <c r="Q5">
-        <v>1344.287613956327</v>
+        <v>1342.291818608437</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07687483518320844</v>
+        <v>0.07711944188332816</v>
       </c>
       <c r="T5">
-        <v>0.6057063772810429</v>
+        <v>0.6104742171525877</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>99.87246448422039</v>
+        <v>74.90434836316528</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07572176270787105</v>
+        <v>0.0756096114131229</v>
       </c>
       <c r="C6">
-        <v>5513.716161106659</v>
+        <v>5475.740429968352</v>
       </c>
       <c r="D6">
-        <v>4805.792161106659</v>
+        <v>4815.135429968353</v>
       </c>
       <c r="E6">
-        <v>-3428.024</v>
+        <v>-3380.705</v>
       </c>
       <c r="F6">
-        <v>189.276</v>
+        <v>236.595</v>
       </c>
       <c r="G6">
         <v>897.2</v>
@@ -1779,28 +1779,28 @@
         <v>797.3</v>
       </c>
       <c r="M6">
-        <v>10.6442418554178</v>
+        <v>13.30530231927226</v>
       </c>
       <c r="N6">
-        <v>786.6557581445821</v>
+        <v>783.9946976807277</v>
       </c>
       <c r="O6">
-        <v>196.6639395361455</v>
+        <v>195.9986744201819</v>
       </c>
       <c r="P6">
-        <v>589.9918186084366</v>
+        <v>587.9960232605457</v>
       </c>
       <c r="Q6">
-        <v>1342.291818608437</v>
+        <v>1340.296023260546</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07711944188332816</v>
+        <v>0.07736919819818723</v>
       </c>
       <c r="T6">
-        <v>0.6104742171525877</v>
+        <v>0.6153424326003755</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>74.90434836316528</v>
+        <v>59.92347869053221</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0756096114131229</v>
+        <v>0.07549746011837476</v>
       </c>
       <c r="C7">
-        <v>5475.740429968352</v>
+        <v>5437.80109937344</v>
       </c>
       <c r="D7">
-        <v>4815.135429968353</v>
+        <v>4824.51509937344</v>
       </c>
       <c r="E7">
-        <v>-3380.705</v>
+        <v>-3333.386</v>
       </c>
       <c r="F7">
-        <v>236.595</v>
+        <v>283.914</v>
       </c>
       <c r="G7">
         <v>897.2</v>
@@ -1861,28 +1861,28 @@
         <v>797.3</v>
       </c>
       <c r="M7">
-        <v>13.30530231927226</v>
+        <v>15.9663627831267</v>
       </c>
       <c r="N7">
-        <v>783.9946976807277</v>
+        <v>781.3336372168733</v>
       </c>
       <c r="O7">
-        <v>195.9986744201819</v>
+        <v>195.3334093042183</v>
       </c>
       <c r="P7">
-        <v>587.9960232605457</v>
+        <v>586.000227912655</v>
       </c>
       <c r="Q7">
-        <v>1340.296023260546</v>
+        <v>1338.300227912655</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07736919819818723</v>
+        <v>0.07762426847719225</v>
       </c>
       <c r="T7">
-        <v>0.6153424326003755</v>
+        <v>0.6203142271002439</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.92347869053221</v>
+        <v>49.93623224211019</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07549746011837474</v>
+        <v>0.07538530882362658</v>
       </c>
       <c r="C8">
-        <v>5437.801099373441</v>
+        <v>5399.898382457014</v>
       </c>
       <c r="D8">
-        <v>4824.515099373441</v>
+        <v>4833.931382457014</v>
       </c>
       <c r="E8">
-        <v>-3333.386</v>
+        <v>-3286.067</v>
       </c>
       <c r="F8">
-        <v>283.914</v>
+        <v>331.2329999999999</v>
       </c>
       <c r="G8">
         <v>897.2</v>
@@ -1943,28 +1943,28 @@
         <v>797.3</v>
       </c>
       <c r="M8">
-        <v>15.9663627831267</v>
+        <v>18.62742324698116</v>
       </c>
       <c r="N8">
-        <v>781.3336372168733</v>
+        <v>778.6725767530188</v>
       </c>
       <c r="O8">
-        <v>195.3334093042183</v>
+        <v>194.6681441882547</v>
       </c>
       <c r="P8">
-        <v>586.000227912655</v>
+        <v>584.0044325647641</v>
       </c>
       <c r="Q8">
-        <v>1338.300227912655</v>
+        <v>1336.304432564764</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07762426847719225</v>
+        <v>0.07788482413854145</v>
       </c>
       <c r="T8">
-        <v>0.6203142271002439</v>
+        <v>0.6253929419119373</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.93623224211019</v>
+        <v>42.80248477895159</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07538530882362658</v>
+        <v>0.07527315752887845</v>
       </c>
       <c r="C9">
-        <v>5399.898382457014</v>
+        <v>5362.03249402137</v>
       </c>
       <c r="D9">
-        <v>4833.931382457014</v>
+        <v>4843.384494021369</v>
       </c>
       <c r="E9">
-        <v>-3286.067</v>
+        <v>-3238.748</v>
       </c>
       <c r="F9">
-        <v>331.233</v>
+        <v>378.552</v>
       </c>
       <c r="G9">
         <v>897.2</v>
@@ -2025,28 +2025,28 @@
         <v>797.3</v>
       </c>
       <c r="M9">
-        <v>18.62742324698116</v>
+        <v>21.28848371083561</v>
       </c>
       <c r="N9">
-        <v>778.6725767530188</v>
+        <v>776.0115162891643</v>
       </c>
       <c r="O9">
-        <v>194.6681441882547</v>
+        <v>194.0028790722911</v>
       </c>
       <c r="P9">
-        <v>584.0044325647641</v>
+        <v>582.0086372168732</v>
       </c>
       <c r="Q9">
-        <v>1336.304432564764</v>
+        <v>1334.308637216873</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07788482413854145</v>
+        <v>0.07815104405339826</v>
       </c>
       <c r="T9">
-        <v>0.6253929419119373</v>
+        <v>0.6305820635673633</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.80248477895158</v>
+        <v>37.45217418158264</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07527315752887845</v>
+        <v>0.07516100623413029</v>
       </c>
       <c r="C10">
-        <v>5362.03249402137</v>
+        <v>5324.203650552344</v>
       </c>
       <c r="D10">
-        <v>4843.384494021369</v>
+        <v>4852.874650552344</v>
       </c>
       <c r="E10">
-        <v>-3238.748</v>
+        <v>-3191.429</v>
       </c>
       <c r="F10">
-        <v>378.552</v>
+        <v>425.8709999999999</v>
       </c>
       <c r="G10">
         <v>897.2</v>
@@ -2107,28 +2107,28 @@
         <v>797.3</v>
       </c>
       <c r="M10">
-        <v>21.28848371083561</v>
+        <v>23.94954417469005</v>
       </c>
       <c r="N10">
-        <v>776.0115162891643</v>
+        <v>773.35045582531</v>
       </c>
       <c r="O10">
-        <v>194.0028790722911</v>
+        <v>193.3376139563275</v>
       </c>
       <c r="P10">
-        <v>582.0086372168732</v>
+        <v>580.0128418689825</v>
       </c>
       <c r="Q10">
-        <v>1334.308637216873</v>
+        <v>1332.312841868983</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07815104405339826</v>
+        <v>0.07842311495539477</v>
       </c>
       <c r="T10">
-        <v>0.6305820635673633</v>
+        <v>0.6358852318525788</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.45217418158264</v>
+        <v>33.29082149474014</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07516100623413029</v>
+        <v>0.07504885493938213</v>
       </c>
       <c r="C11">
-        <v>5324.203650552344</v>
+        <v>5286.41207023584</v>
       </c>
       <c r="D11">
-        <v>4852.874650552344</v>
+        <v>4862.402070235839</v>
       </c>
       <c r="E11">
-        <v>-3191.429</v>
+        <v>-3144.11</v>
       </c>
       <c r="F11">
-        <v>425.8709999999999</v>
+        <v>473.1899999999999</v>
       </c>
       <c r="G11">
         <v>897.2</v>
@@ -2189,28 +2189,28 @@
         <v>797.3</v>
       </c>
       <c r="M11">
-        <v>23.94954417469005</v>
+        <v>26.61060463854451</v>
       </c>
       <c r="N11">
-        <v>773.35045582531</v>
+        <v>770.6893953614555</v>
       </c>
       <c r="O11">
-        <v>193.3376139563275</v>
+        <v>192.6723488403639</v>
       </c>
       <c r="P11">
-        <v>580.0128418689825</v>
+        <v>578.0170465210916</v>
       </c>
       <c r="Q11">
-        <v>1332.312841868983</v>
+        <v>1330.317046521091</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07842311495539477</v>
+        <v>0.07870123187743563</v>
       </c>
       <c r="T11">
-        <v>0.6358852318525788</v>
+        <v>0.6413062483219102</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.29082149474014</v>
+        <v>29.96173934526611</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07504885493938213</v>
+        <v>0.07493670364463398</v>
       </c>
       <c r="C12">
-        <v>5286.41207023584</v>
+        <v>5248.657972974542</v>
       </c>
       <c r="D12">
-        <v>4862.402070235839</v>
+        <v>4871.966972974542</v>
       </c>
       <c r="E12">
-        <v>-3144.11</v>
+        <v>-3096.791</v>
       </c>
       <c r="F12">
-        <v>473.19</v>
+        <v>520.509</v>
       </c>
       <c r="G12">
         <v>897.2</v>
@@ -2271,28 +2271,28 @@
         <v>797.3</v>
       </c>
       <c r="M12">
-        <v>26.61060463854451</v>
+        <v>29.27166510239896</v>
       </c>
       <c r="N12">
-        <v>770.6893953614555</v>
+        <v>768.028334897601</v>
       </c>
       <c r="O12">
-        <v>192.6723488403639</v>
+        <v>192.0070837244002</v>
       </c>
       <c r="P12">
-        <v>578.0170465210916</v>
+        <v>576.0212511732008</v>
       </c>
       <c r="Q12">
-        <v>1330.317046521091</v>
+        <v>1328.321251173201</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07870123187743563</v>
+        <v>0.07898559861794935</v>
       </c>
       <c r="T12">
-        <v>0.6413062483219102</v>
+        <v>0.6468490853860582</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.96173934526611</v>
+        <v>27.23794485933283</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07493670364463398</v>
+        <v>0.07482455234988583</v>
       </c>
       <c r="C13">
-        <v>5248.657972974542</v>
+        <v>5210.941580404848</v>
       </c>
       <c r="D13">
-        <v>4871.966972974542</v>
+        <v>4881.569580404848</v>
       </c>
       <c r="E13">
-        <v>-3096.791</v>
+        <v>-3049.472</v>
       </c>
       <c r="F13">
-        <v>520.509</v>
+        <v>567.828</v>
       </c>
       <c r="G13">
         <v>897.2</v>
@@ -2353,28 +2353,28 @@
         <v>797.3</v>
       </c>
       <c r="M13">
-        <v>29.27166510239896</v>
+        <v>31.93272556625341</v>
       </c>
       <c r="N13">
-        <v>768.028334897601</v>
+        <v>765.3672744337465</v>
       </c>
       <c r="O13">
-        <v>192.0070837244002</v>
+        <v>191.3418186084366</v>
       </c>
       <c r="P13">
-        <v>576.0212511732008</v>
+        <v>574.0254558253099</v>
       </c>
       <c r="Q13">
-        <v>1328.321251173201</v>
+        <v>1326.32545582531</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07898559861794935</v>
+        <v>0.07927642823892928</v>
       </c>
       <c r="T13">
-        <v>0.6468490853860582</v>
+        <v>0.6525178960198458</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.23794485933283</v>
+        <v>24.96811612105509</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07482455234988583</v>
+        <v>0.07471240105513767</v>
       </c>
       <c r="C14">
-        <v>5210.941580404848</v>
+        <v>5173.263115913978</v>
       </c>
       <c r="D14">
-        <v>4881.569580404848</v>
+        <v>4891.210115913978</v>
       </c>
       <c r="E14">
-        <v>-3049.472</v>
+        <v>-3002.153</v>
       </c>
       <c r="F14">
-        <v>567.828</v>
+        <v>615.1469999999999</v>
       </c>
       <c r="G14">
         <v>897.2</v>
@@ -2435,28 +2435,28 @@
         <v>797.3</v>
       </c>
       <c r="M14">
-        <v>31.93272556625341</v>
+        <v>34.59378603010786</v>
       </c>
       <c r="N14">
-        <v>765.3672744337465</v>
+        <v>762.7062139698921</v>
       </c>
       <c r="O14">
-        <v>191.3418186084366</v>
+        <v>190.676553492473</v>
       </c>
       <c r="P14">
-        <v>574.0254558253099</v>
+        <v>572.0296604774192</v>
       </c>
       <c r="Q14">
-        <v>1326.32545582531</v>
+        <v>1324.329660477419</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07927642823892928</v>
+        <v>0.07957394359832252</v>
       </c>
       <c r="T14">
-        <v>0.6525178960198458</v>
+        <v>0.6583170241394676</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.96811612105509</v>
+        <v>23.04749180405086</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07471240105513767</v>
+        <v>0.07460024976038952</v>
       </c>
       <c r="C15">
-        <v>5173.263115913978</v>
+        <v>5135.622804657296</v>
       </c>
       <c r="D15">
-        <v>4891.210115913978</v>
+        <v>4900.888804657297</v>
       </c>
       <c r="E15">
-        <v>-3002.153</v>
+        <v>-2954.834</v>
       </c>
       <c r="F15">
-        <v>615.1469999999999</v>
+        <v>662.466</v>
       </c>
       <c r="G15">
         <v>897.2</v>
@@ -2517,28 +2517,28 @@
         <v>797.3</v>
       </c>
       <c r="M15">
-        <v>34.59378603010786</v>
+        <v>37.25484649396232</v>
       </c>
       <c r="N15">
-        <v>762.7062139698921</v>
+        <v>760.0451535060377</v>
       </c>
       <c r="O15">
-        <v>190.676553492473</v>
+        <v>190.0112883765094</v>
       </c>
       <c r="P15">
-        <v>572.0296604774192</v>
+        <v>570.0338651295283</v>
       </c>
       <c r="Q15">
-        <v>1324.329660477419</v>
+        <v>1322.333865129528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07957394359832252</v>
+        <v>0.07987837791956215</v>
       </c>
       <c r="T15">
-        <v>0.6583170241394676</v>
+        <v>0.6642510157037318</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.04749180405086</v>
+        <v>21.40124238947579</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07460024976038952</v>
+        <v>0.07448809846564136</v>
       </c>
       <c r="C16">
-        <v>5135.622804657296</v>
+        <v>5098.020873575849</v>
       </c>
       <c r="D16">
-        <v>4900.888804657297</v>
+        <v>4910.605873575849</v>
       </c>
       <c r="E16">
-        <v>-2954.834</v>
+        <v>-2907.515</v>
       </c>
       <c r="F16">
-        <v>662.466</v>
+        <v>709.7850000000001</v>
       </c>
       <c r="G16">
         <v>897.2</v>
@@ -2599,28 +2599,28 @@
         <v>797.3</v>
       </c>
       <c r="M16">
-        <v>37.25484649396232</v>
+        <v>39.91590695781677</v>
       </c>
       <c r="N16">
-        <v>760.0451535060377</v>
+        <v>757.3840930421832</v>
       </c>
       <c r="O16">
-        <v>190.0112883765094</v>
+        <v>189.3460232605458</v>
       </c>
       <c r="P16">
-        <v>570.0338651295283</v>
+        <v>568.0380697816374</v>
       </c>
       <c r="Q16">
-        <v>1322.333865129528</v>
+        <v>1320.338069781637</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07987837791956215</v>
+        <v>0.0801899754013015</v>
       </c>
       <c r="T16">
-        <v>0.6642510157037318</v>
+        <v>0.6703246305989198</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.40124238947579</v>
+        <v>19.97449289684407</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07448809846564136</v>
+        <v>0.07437594717089321</v>
       </c>
       <c r="C17">
-        <v>5098.020873575849</v>
+        <v>5060.457551414091</v>
       </c>
       <c r="D17">
-        <v>4910.605873575849</v>
+        <v>4920.361551414091</v>
       </c>
       <c r="E17">
-        <v>-2907.515</v>
+        <v>-2860.196</v>
       </c>
       <c r="F17">
-        <v>709.785</v>
+        <v>757.1039999999999</v>
       </c>
       <c r="G17">
         <v>897.2</v>
@@ -2681,28 +2681,28 @@
         <v>797.3</v>
       </c>
       <c r="M17">
-        <v>39.91590695781677</v>
+        <v>42.57696742167121</v>
       </c>
       <c r="N17">
-        <v>757.3840930421832</v>
+        <v>754.7230325783287</v>
       </c>
       <c r="O17">
-        <v>189.3460232605458</v>
+        <v>188.6807581445822</v>
       </c>
       <c r="P17">
-        <v>568.0380697816374</v>
+        <v>566.0422744337466</v>
       </c>
       <c r="Q17">
-        <v>1320.338069781637</v>
+        <v>1318.342274433747</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0801899754013015</v>
+        <v>0.08050899187070133</v>
       </c>
       <c r="T17">
-        <v>0.6703246305989198</v>
+        <v>0.6765428553725646</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.97449289684407</v>
+        <v>18.72608709079132</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07437594717089321</v>
+        <v>0.07426379587614507</v>
       </c>
       <c r="C18">
-        <v>5060.457551414091</v>
+        <v>5022.933068737843</v>
       </c>
       <c r="D18">
-        <v>4920.361551414091</v>
+        <v>4930.156068737843</v>
       </c>
       <c r="E18">
-        <v>-2860.196</v>
+        <v>-2812.877</v>
       </c>
       <c r="F18">
-        <v>757.1039999999999</v>
+        <v>804.423</v>
       </c>
       <c r="G18">
         <v>897.2</v>
@@ -2763,28 +2763,28 @@
         <v>797.3</v>
       </c>
       <c r="M18">
-        <v>42.57696742167121</v>
+        <v>45.23802788552567</v>
       </c>
       <c r="N18">
-        <v>754.7230325783287</v>
+        <v>752.0619721144743</v>
       </c>
       <c r="O18">
-        <v>188.6807581445822</v>
+        <v>188.0154930286186</v>
       </c>
       <c r="P18">
-        <v>566.0422744337466</v>
+        <v>564.0464790858557</v>
       </c>
       <c r="Q18">
-        <v>1318.342274433747</v>
+        <v>1316.346479085856</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08050899187070133</v>
+        <v>0.08083569548394212</v>
       </c>
       <c r="T18">
-        <v>0.6765428553725646</v>
+        <v>0.6829109168877433</v>
       </c>
       <c r="U18">
         <v>0.0562366166625341</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.72608709079132</v>
+        <v>17.62455255603889</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07426379587614507</v>
+        <v>0.07415164458139691</v>
       </c>
       <c r="C19">
-        <v>5022.933068737843</v>
+        <v>4985.447657952456</v>
       </c>
       <c r="D19">
-        <v>4930.156068737843</v>
+        <v>4939.989657952457</v>
       </c>
       <c r="E19">
-        <v>-2812.877</v>
+        <v>-2765.558</v>
       </c>
       <c r="F19">
-        <v>804.423</v>
+        <v>851.7420000000001</v>
       </c>
       <c r="G19">
         <v>897.2</v>
@@ -2845,28 +2845,28 @@
         <v>797.3</v>
       </c>
       <c r="M19">
-        <v>45.23802788552567</v>
+        <v>47.89908834938012</v>
       </c>
       <c r="N19">
-        <v>752.0619721144743</v>
+        <v>749.4009116506198</v>
       </c>
       <c r="O19">
-        <v>188.0154930286186</v>
+        <v>187.350227912655</v>
       </c>
       <c r="P19">
-        <v>564.0464790858557</v>
+        <v>562.0506837379648</v>
       </c>
       <c r="Q19">
-        <v>1316.346479085856</v>
+        <v>1314.350683737965</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08083569548394212</v>
+        <v>0.08117036747799367</v>
       </c>
       <c r="T19">
-        <v>0.6829109168877433</v>
+        <v>0.6894342969764626</v>
       </c>
       <c r="U19">
         <v>0.0562366166625341</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.62455255603889</v>
+        <v>16.64541074737006</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07415164458139692</v>
+        <v>0.07403949328664874</v>
       </c>
       <c r="C20">
-        <v>4985.447657952454</v>
+        <v>4948.001553321185</v>
       </c>
       <c r="D20">
-        <v>4939.989657952455</v>
+        <v>4949.862553321185</v>
       </c>
       <c r="E20">
-        <v>-2765.558</v>
+        <v>-2718.239</v>
       </c>
       <c r="F20">
-        <v>851.7419999999998</v>
+        <v>899.0609999999999</v>
       </c>
       <c r="G20">
         <v>897.2</v>
@@ -2927,28 +2927,28 @@
         <v>797.3</v>
       </c>
       <c r="M20">
-        <v>47.89908834938011</v>
+        <v>50.56014881323457</v>
       </c>
       <c r="N20">
-        <v>749.4009116506198</v>
+        <v>746.7398511867653</v>
       </c>
       <c r="O20">
-        <v>187.350227912655</v>
+        <v>186.6849627966913</v>
       </c>
       <c r="P20">
-        <v>562.0506837379648</v>
+        <v>560.054888390074</v>
       </c>
       <c r="Q20">
-        <v>1314.350683737965</v>
+        <v>1312.354888390074</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08117036747799367</v>
+        <v>0.08151330297807116</v>
       </c>
       <c r="T20">
-        <v>0.6894342969764626</v>
+        <v>0.6961187481784838</v>
       </c>
       <c r="U20">
         <v>0.0562366166625341</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.64541074737006</v>
+        <v>15.76933649750848</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07403949328664874</v>
+        <v>0.0739273419919006</v>
       </c>
       <c r="C21">
-        <v>4948.001553321185</v>
+        <v>4910.594990983799</v>
       </c>
       <c r="D21">
-        <v>4949.862553321185</v>
+        <v>4959.774990983799</v>
       </c>
       <c r="E21">
-        <v>-2718.239</v>
+        <v>-2670.92</v>
       </c>
       <c r="F21">
-        <v>899.0609999999999</v>
+        <v>946.38</v>
       </c>
       <c r="G21">
         <v>897.2</v>
@@ -3009,28 +3009,28 @@
         <v>797.3</v>
       </c>
       <c r="M21">
-        <v>50.56014881323457</v>
+        <v>53.22120927708902</v>
       </c>
       <c r="N21">
-        <v>746.7398511867653</v>
+        <v>744.078790722911</v>
       </c>
       <c r="O21">
-        <v>186.6849627966913</v>
+        <v>186.0196976807277</v>
       </c>
       <c r="P21">
-        <v>560.054888390074</v>
+        <v>558.0590930421832</v>
       </c>
       <c r="Q21">
-        <v>1312.354888390074</v>
+        <v>1310.359093042183</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08151330297807116</v>
+        <v>0.0818648118656506</v>
       </c>
       <c r="T21">
-        <v>0.6961187481784838</v>
+        <v>0.7029703106605555</v>
       </c>
       <c r="U21">
         <v>0.0562366166625341</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.76933649750848</v>
+        <v>14.98086967263306</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0739273419919006</v>
+        <v>0.07381519069715245</v>
       </c>
       <c r="C22">
-        <v>4910.594990983799</v>
+        <v>4873.228208975412</v>
       </c>
       <c r="D22">
-        <v>4959.774990983799</v>
+        <v>4969.727208975411</v>
       </c>
       <c r="E22">
-        <v>-2670.92</v>
+        <v>-2623.601</v>
       </c>
       <c r="F22">
-        <v>946.38</v>
+        <v>993.6990000000001</v>
       </c>
       <c r="G22">
         <v>897.2</v>
@@ -3091,28 +3091,28 @@
         <v>797.3</v>
       </c>
       <c r="M22">
-        <v>53.22120927708902</v>
+        <v>55.88226974094348</v>
       </c>
       <c r="N22">
-        <v>744.078790722911</v>
+        <v>741.4177302590565</v>
       </c>
       <c r="O22">
-        <v>186.0196976807277</v>
+        <v>185.3544325647641</v>
       </c>
       <c r="P22">
-        <v>558.0590930421832</v>
+        <v>556.0632976942924</v>
       </c>
       <c r="Q22">
-        <v>1310.359093042183</v>
+        <v>1308.363297694292</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0818648118656506</v>
+        <v>0.08222521971240927</v>
       </c>
       <c r="T22">
-        <v>0.7029703106605555</v>
+        <v>0.7099953304206543</v>
       </c>
       <c r="U22">
         <v>0.0562366166625341</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.98086967263306</v>
+        <v>14.26749492631719</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07381519069715245</v>
+        <v>0.07370303940240429</v>
       </c>
       <c r="C23">
-        <v>4873.228208975412</v>
+        <v>4835.901447245526</v>
       </c>
       <c r="D23">
-        <v>4969.727208975411</v>
+        <v>4979.719447245526</v>
       </c>
       <c r="E23">
-        <v>-2623.601000000001</v>
+        <v>-2576.282</v>
       </c>
       <c r="F23">
-        <v>993.6989999999998</v>
+        <v>1041.018</v>
       </c>
       <c r="G23">
         <v>897.2</v>
@@ -3173,28 +3173,28 @@
         <v>797.3</v>
       </c>
       <c r="M23">
-        <v>55.88226974094346</v>
+        <v>58.54333020479793</v>
       </c>
       <c r="N23">
-        <v>741.4177302590565</v>
+        <v>738.756669795202</v>
       </c>
       <c r="O23">
-        <v>185.3544325647641</v>
+        <v>184.6891674488005</v>
       </c>
       <c r="P23">
-        <v>556.0632976942924</v>
+        <v>554.0675023464015</v>
       </c>
       <c r="Q23">
-        <v>1308.363297694292</v>
+        <v>1306.367502346402</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08222521971240927</v>
+        <v>0.0825948687860079</v>
       </c>
       <c r="T23">
-        <v>0.7099953304206543</v>
+        <v>0.7172004788925505</v>
       </c>
       <c r="U23">
         <v>0.0562366166625341</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.2674949263172</v>
+        <v>13.61897242966641</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07370303940240429</v>
+        <v>0.07359088810765614</v>
       </c>
       <c r="C24">
-        <v>4835.901447245526</v>
+        <v>4798.614947677321</v>
       </c>
       <c r="D24">
-        <v>4979.719447245526</v>
+        <v>4989.75194767732</v>
       </c>
       <c r="E24">
-        <v>-2576.282</v>
+        <v>-2528.963</v>
       </c>
       <c r="F24">
-        <v>1041.018</v>
+        <v>1088.337</v>
       </c>
       <c r="G24">
         <v>897.2</v>
@@ -3255,28 +3255,28 @@
         <v>797.3</v>
       </c>
       <c r="M24">
-        <v>58.54333020479793</v>
+        <v>61.20439066865237</v>
       </c>
       <c r="N24">
-        <v>738.756669795202</v>
+        <v>736.0956093313475</v>
       </c>
       <c r="O24">
-        <v>184.6891674488005</v>
+        <v>184.0239023328369</v>
       </c>
       <c r="P24">
-        <v>554.0675023464015</v>
+        <v>552.0717069985106</v>
       </c>
       <c r="Q24">
-        <v>1306.367502346402</v>
+        <v>1304.37170699851</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0825948687860079</v>
+        <v>0.08297411913424546</v>
       </c>
       <c r="T24">
-        <v>0.7172004788925505</v>
+        <v>0.7245927740780025</v>
       </c>
       <c r="U24">
         <v>0.0562366166625341</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.61897242966641</v>
+        <v>13.02684319359396</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07359088810765614</v>
+        <v>0.073748736812908</v>
       </c>
       <c r="C25">
-        <v>4798.614947677321</v>
+        <v>4737.187141465646</v>
       </c>
       <c r="D25">
-        <v>4989.75194767732</v>
+        <v>4975.643141465646</v>
       </c>
       <c r="E25">
-        <v>-2528.963</v>
+        <v>-2481.644</v>
       </c>
       <c r="F25">
-        <v>1088.337</v>
+        <v>1135.656</v>
       </c>
       <c r="G25">
         <v>897.2</v>
@@ -3337,45 +3337,45 @@
         <v>797.3</v>
       </c>
       <c r="M25">
-        <v>61.20439066865237</v>
+        <v>65.56893513250682</v>
       </c>
       <c r="N25">
-        <v>736.0956093313475</v>
+        <v>731.7310648674932</v>
       </c>
       <c r="O25">
-        <v>184.0239023328369</v>
+        <v>182.9327662168733</v>
       </c>
       <c r="P25">
-        <v>552.0717069985106</v>
+        <v>548.7982986506199</v>
       </c>
       <c r="Q25">
-        <v>1304.37170699851</v>
+        <v>1301.09829865062</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08297411913424546</v>
+        <v>0.08336334975480507</v>
       </c>
       <c r="T25">
-        <v>0.7245927740780025</v>
+        <v>0.7321796033472823</v>
       </c>
       <c r="U25">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.02684319359396</v>
+        <v>12.15972164850251</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.073748736812908</v>
+        <v>0.07364783551815983</v>
       </c>
       <c r="C26">
-        <v>4737.187141465646</v>
+        <v>4698.877667176215</v>
       </c>
       <c r="D26">
-        <v>4975.643141465646</v>
+        <v>4984.652667176216</v>
       </c>
       <c r="E26">
-        <v>-2481.644</v>
+        <v>-2434.325</v>
       </c>
       <c r="F26">
-        <v>1135.656</v>
+        <v>1182.975</v>
       </c>
       <c r="G26">
         <v>897.2</v>
@@ -3419,28 +3419,28 @@
         <v>797.3</v>
       </c>
       <c r="M26">
-        <v>65.56893513250682</v>
+        <v>68.30097409636126</v>
       </c>
       <c r="N26">
-        <v>731.7310648674932</v>
+        <v>728.9990259036387</v>
       </c>
       <c r="O26">
-        <v>182.9327662168733</v>
+        <v>182.2497564759097</v>
       </c>
       <c r="P26">
-        <v>548.7982986506199</v>
+        <v>546.749269427729</v>
       </c>
       <c r="Q26">
-        <v>1301.09829865062</v>
+        <v>1299.049269427729</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08336334975480507</v>
+        <v>0.08376295985857959</v>
       </c>
       <c r="T26">
-        <v>0.7321796033472823</v>
+        <v>0.7399687480637427</v>
       </c>
       <c r="U26">
         <v>0.05773661666253409</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.15972164850251</v>
+        <v>11.67333278256241</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07364783551815983</v>
+        <v>0.07354693422341167</v>
       </c>
       <c r="C27">
-        <v>4698.877667176215</v>
+        <v>4660.600879635923</v>
       </c>
       <c r="D27">
-        <v>4984.652667176216</v>
+        <v>4993.694879635923</v>
       </c>
       <c r="E27">
-        <v>-2434.325</v>
+        <v>-2387.006</v>
       </c>
       <c r="F27">
-        <v>1182.975</v>
+        <v>1230.294</v>
       </c>
       <c r="G27">
         <v>897.2</v>
@@ -3501,28 +3501,28 @@
         <v>797.3</v>
       </c>
       <c r="M27">
-        <v>68.30097409636126</v>
+        <v>71.03301306021571</v>
       </c>
       <c r="N27">
-        <v>728.9990259036387</v>
+        <v>726.2669869397843</v>
       </c>
       <c r="O27">
-        <v>182.2497564759097</v>
+        <v>181.5667467349461</v>
       </c>
       <c r="P27">
-        <v>546.749269427729</v>
+        <v>544.7002402048382</v>
       </c>
       <c r="Q27">
-        <v>1299.049269427729</v>
+        <v>1297.000240204838</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08376295985857959</v>
+        <v>0.08417337023542909</v>
       </c>
       <c r="T27">
-        <v>0.7399687480637427</v>
+        <v>0.7479684102049723</v>
       </c>
       <c r="U27">
         <v>0.05773661666253409</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.67333278256241</v>
+        <v>11.22435844477155</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07354693422341167</v>
+        <v>0.07344603292866353</v>
       </c>
       <c r="C28">
-        <v>4660.600879635923</v>
+        <v>4622.356957050354</v>
       </c>
       <c r="D28">
-        <v>4993.694879635923</v>
+        <v>5002.769957050355</v>
       </c>
       <c r="E28">
-        <v>-2387.006</v>
+        <v>-2339.687</v>
       </c>
       <c r="F28">
-        <v>1230.294</v>
+        <v>1277.613</v>
       </c>
       <c r="G28">
         <v>897.2</v>
@@ -3583,28 +3583,28 @@
         <v>797.3</v>
       </c>
       <c r="M28">
-        <v>71.03301306021571</v>
+        <v>73.76505202407017</v>
       </c>
       <c r="N28">
-        <v>726.2669869397843</v>
+        <v>723.5349479759298</v>
       </c>
       <c r="O28">
-        <v>181.5667467349461</v>
+        <v>180.8837369939824</v>
       </c>
       <c r="P28">
-        <v>544.7002402048382</v>
+        <v>542.6512109819473</v>
       </c>
       <c r="Q28">
-        <v>1297.000240204838</v>
+        <v>1294.951210981947</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08417337023542909</v>
+        <v>0.0845950247321923</v>
       </c>
       <c r="T28">
-        <v>0.7479684102049723</v>
+        <v>0.7561872411719891</v>
       </c>
       <c r="U28">
         <v>0.05773661666253409</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.22435844477155</v>
+        <v>10.80864146533556</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07344603292866353</v>
+        <v>0.07334513163391537</v>
       </c>
       <c r="C29">
-        <v>4622.356957050354</v>
+        <v>4584.146078922879</v>
       </c>
       <c r="D29">
-        <v>5002.769957050355</v>
+        <v>5011.878078922879</v>
       </c>
       <c r="E29">
-        <v>-2339.687</v>
+        <v>-2292.368</v>
       </c>
       <c r="F29">
-        <v>1277.613</v>
+        <v>1324.932</v>
       </c>
       <c r="G29">
         <v>897.2</v>
@@ -3665,28 +3665,28 @@
         <v>797.3</v>
       </c>
       <c r="M29">
-        <v>73.76505202407017</v>
+        <v>76.49709098792462</v>
       </c>
       <c r="N29">
-        <v>723.5349479759298</v>
+        <v>720.8029090120754</v>
       </c>
       <c r="O29">
-        <v>180.8837369939824</v>
+        <v>180.2007272530188</v>
       </c>
       <c r="P29">
-        <v>542.6512109819473</v>
+        <v>540.6021817590565</v>
       </c>
       <c r="Q29">
-        <v>1294.951210981947</v>
+        <v>1292.902181759056</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0845950247321923</v>
+        <v>0.08502839185386557</v>
       </c>
       <c r="T29">
-        <v>0.7561872411719891</v>
+        <v>0.7646343729992008</v>
       </c>
       <c r="U29">
         <v>0.05773661666253409</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.80864146533556</v>
+        <v>10.42261855585929</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07334513163391537</v>
+        <v>0.07324423033916722</v>
       </c>
       <c r="C30">
-        <v>4584.146078922879</v>
+        <v>4545.96842606647</v>
       </c>
       <c r="D30">
-        <v>5011.878078922879</v>
+        <v>5021.01942606647</v>
       </c>
       <c r="E30">
-        <v>-2292.368</v>
+        <v>-2245.049</v>
       </c>
       <c r="F30">
-        <v>1324.932</v>
+        <v>1372.251</v>
       </c>
       <c r="G30">
         <v>897.2</v>
@@ -3747,28 +3747,28 @@
         <v>797.3</v>
       </c>
       <c r="M30">
-        <v>76.49709098792462</v>
+        <v>79.22912995177907</v>
       </c>
       <c r="N30">
-        <v>720.8029090120754</v>
+        <v>718.0708700482209</v>
       </c>
       <c r="O30">
-        <v>180.2007272530188</v>
+        <v>179.5177175120552</v>
       </c>
       <c r="P30">
-        <v>540.6021817590565</v>
+        <v>538.5531525361656</v>
       </c>
       <c r="Q30">
-        <v>1292.902181759056</v>
+        <v>1290.853152536165</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08502839185386557</v>
+        <v>0.08547396650009303</v>
       </c>
       <c r="T30">
-        <v>0.7646343729992008</v>
+        <v>0.7733194522018267</v>
       </c>
       <c r="U30">
         <v>0.05773661666253409</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.42261855585929</v>
+        <v>10.06321791600208</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07324423033916722</v>
+        <v>0.07352582904441905</v>
       </c>
       <c r="C31">
-        <v>4545.968426066471</v>
+        <v>4473.220358406777</v>
       </c>
       <c r="D31">
-        <v>5021.01942606647</v>
+        <v>4995.590358406777</v>
       </c>
       <c r="E31">
-        <v>-2245.049</v>
+        <v>-2197.73</v>
       </c>
       <c r="F31">
-        <v>1372.251</v>
+        <v>1419.57</v>
       </c>
       <c r="G31">
         <v>897.2</v>
@@ -3829,45 +3829,45 @@
         <v>797.3</v>
       </c>
       <c r="M31">
-        <v>79.22912995177906</v>
+        <v>84.37443791563352</v>
       </c>
       <c r="N31">
-        <v>718.0708700482209</v>
+        <v>712.9255620843664</v>
       </c>
       <c r="O31">
-        <v>179.5177175120552</v>
+        <v>178.2313905210916</v>
       </c>
       <c r="P31">
-        <v>538.5531525361656</v>
+        <v>534.6941715632748</v>
       </c>
       <c r="Q31">
-        <v>1290.853152536165</v>
+        <v>1286.994171563275</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08547396650009303</v>
+        <v>0.08593227185049841</v>
       </c>
       <c r="T31">
-        <v>0.7733194522018267</v>
+        <v>0.7822526765245279</v>
       </c>
       <c r="U31">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>10.06321791600208</v>
+        <v>9.449544431895649</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07352582904441905</v>
+        <v>0.0734376777496709</v>
       </c>
       <c r="C32">
-        <v>4473.220358406777</v>
+        <v>4433.83390203812</v>
       </c>
       <c r="D32">
-        <v>4995.590358406777</v>
+        <v>5003.52290203812</v>
       </c>
       <c r="E32">
-        <v>-2197.73</v>
+        <v>-2150.411</v>
       </c>
       <c r="F32">
-        <v>1419.57</v>
+        <v>1466.889</v>
       </c>
       <c r="G32">
         <v>897.2</v>
@@ -3911,28 +3911,28 @@
         <v>797.3</v>
       </c>
       <c r="M32">
-        <v>84.37443791563352</v>
+        <v>87.18691917948797</v>
       </c>
       <c r="N32">
-        <v>712.9255620843664</v>
+        <v>710.113080820512</v>
       </c>
       <c r="O32">
-        <v>178.2313905210916</v>
+        <v>177.528270205128</v>
       </c>
       <c r="P32">
-        <v>534.6941715632748</v>
+        <v>532.584810615384</v>
       </c>
       <c r="Q32">
-        <v>1286.994171563275</v>
+        <v>1284.884810615384</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08593227185049841</v>
+        <v>0.08640386141395903</v>
       </c>
       <c r="T32">
-        <v>0.7822526765245279</v>
+        <v>0.7914448348855682</v>
       </c>
       <c r="U32">
         <v>0.05943661666253409</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.449544431895649</v>
+        <v>9.144720417963532</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0734376777496709</v>
+        <v>0.07334952645492275</v>
       </c>
       <c r="C33">
-        <v>4433.83390203812</v>
+        <v>4394.472678053399</v>
       </c>
       <c r="D33">
-        <v>5003.52290203812</v>
+        <v>5011.480678053399</v>
       </c>
       <c r="E33">
-        <v>-2150.411</v>
+        <v>-2103.092000000001</v>
       </c>
       <c r="F33">
-        <v>1466.889</v>
+        <v>1514.208</v>
       </c>
       <c r="G33">
         <v>897.2</v>
@@ -3993,28 +3993,28 @@
         <v>797.3</v>
       </c>
       <c r="M33">
-        <v>87.18691917948797</v>
+        <v>89.99940044334242</v>
       </c>
       <c r="N33">
-        <v>710.113080820512</v>
+        <v>707.3005995566575</v>
       </c>
       <c r="O33">
-        <v>177.528270205128</v>
+        <v>176.8251498891644</v>
       </c>
       <c r="P33">
-        <v>532.584810615384</v>
+        <v>530.4754496674932</v>
       </c>
       <c r="Q33">
-        <v>1284.884810615384</v>
+        <v>1282.775449667493</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08640386141395903</v>
+        <v>0.0868893212586979</v>
       </c>
       <c r="T33">
-        <v>0.7914448348855682</v>
+        <v>0.8009073508454626</v>
       </c>
       <c r="U33">
         <v>0.05943661666253409</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.144720417963532</v>
+        <v>8.858947904902172</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07334952645492275</v>
+        <v>0.0732613751601746</v>
       </c>
       <c r="C34">
-        <v>4394.472678053399</v>
+        <v>4355.136807035764</v>
       </c>
       <c r="D34">
-        <v>5011.480678053399</v>
+        <v>5019.463807035764</v>
       </c>
       <c r="E34">
-        <v>-2103.092000000001</v>
+        <v>-2055.773</v>
       </c>
       <c r="F34">
-        <v>1514.208</v>
+        <v>1561.527</v>
       </c>
       <c r="G34">
         <v>897.2</v>
@@ -4075,28 +4075,28 @@
         <v>797.3</v>
       </c>
       <c r="M34">
-        <v>89.99940044334242</v>
+        <v>92.81188170719687</v>
       </c>
       <c r="N34">
-        <v>707.3005995566575</v>
+        <v>704.4881182928031</v>
       </c>
       <c r="O34">
-        <v>176.8251498891644</v>
+        <v>176.1220295732008</v>
       </c>
       <c r="P34">
-        <v>530.4754496674932</v>
+        <v>528.3660887196023</v>
       </c>
       <c r="Q34">
-        <v>1282.775449667493</v>
+        <v>1280.666088719602</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0868893212586979</v>
+        <v>0.08738927244208569</v>
       </c>
       <c r="T34">
-        <v>0.8009073508454626</v>
+        <v>0.810652329968339</v>
       </c>
       <c r="U34">
         <v>0.05943661666253409</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.858947904902172</v>
+        <v>8.590494938086955</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0732613751601746</v>
+        <v>0.07317322386542643</v>
       </c>
       <c r="C35">
-        <v>4355.136807035764</v>
+        <v>4315.826410337935</v>
       </c>
       <c r="D35">
-        <v>5019.463807035764</v>
+        <v>5027.472410337935</v>
       </c>
       <c r="E35">
-        <v>-2055.773</v>
+        <v>-2008.454</v>
       </c>
       <c r="F35">
-        <v>1561.527</v>
+        <v>1608.846</v>
       </c>
       <c r="G35">
         <v>897.2</v>
@@ -4157,28 +4157,28 @@
         <v>797.3</v>
       </c>
       <c r="M35">
-        <v>92.81188170719687</v>
+        <v>95.62436297105133</v>
       </c>
       <c r="N35">
-        <v>704.4881182928031</v>
+        <v>701.6756370289486</v>
       </c>
       <c r="O35">
-        <v>176.1220295732008</v>
+        <v>175.4189092572371</v>
       </c>
       <c r="P35">
-        <v>528.3660887196023</v>
+        <v>526.2567277717114</v>
       </c>
       <c r="Q35">
-        <v>1280.666088719602</v>
+        <v>1278.556727771711</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08738927244208569</v>
+        <v>0.08790437366133372</v>
       </c>
       <c r="T35">
-        <v>0.810652329968339</v>
+        <v>0.8206926114888783</v>
       </c>
       <c r="U35">
         <v>0.05943661666253409</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.590494938086955</v>
+        <v>8.337833322260867</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07317322386542643</v>
+        <v>0.0730850725706783</v>
       </c>
       <c r="C36">
-        <v>4315.826410337935</v>
+        <v>4276.541610088336</v>
       </c>
       <c r="D36">
-        <v>5027.472410337935</v>
+        <v>5035.506610088336</v>
       </c>
       <c r="E36">
-        <v>-2008.454</v>
+        <v>-1961.135</v>
       </c>
       <c r="F36">
-        <v>1608.846</v>
+        <v>1656.165</v>
       </c>
       <c r="G36">
         <v>897.2</v>
@@ -4239,28 +4239,28 @@
         <v>797.3</v>
       </c>
       <c r="M36">
-        <v>95.62436297105133</v>
+        <v>98.43684423490578</v>
       </c>
       <c r="N36">
-        <v>701.6756370289486</v>
+        <v>698.8631557650942</v>
       </c>
       <c r="O36">
-        <v>175.4189092572371</v>
+        <v>174.7157889412736</v>
       </c>
       <c r="P36">
-        <v>526.2567277717114</v>
+        <v>524.1473668238207</v>
       </c>
       <c r="Q36">
-        <v>1278.556727771711</v>
+        <v>1276.447366823821</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08790437366133372</v>
+        <v>0.0884353241488663</v>
       </c>
       <c r="T36">
-        <v>0.8206926114888783</v>
+        <v>0.8310418247485111</v>
       </c>
       <c r="U36">
         <v>0.05943661666253409</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.337833322260867</v>
+        <v>8.099609513053416</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0730850725706783</v>
+        <v>0.07299692127593013</v>
       </c>
       <c r="C37">
-        <v>4276.541610088336</v>
+        <v>4237.28252919733</v>
       </c>
       <c r="D37">
-        <v>5035.506610088336</v>
+        <v>5043.566529197331</v>
       </c>
       <c r="E37">
-        <v>-1961.135</v>
+        <v>-1913.816</v>
       </c>
       <c r="F37">
-        <v>1656.165</v>
+        <v>1703.484</v>
       </c>
       <c r="G37">
         <v>897.2</v>
@@ -4321,28 +4321,28 @@
         <v>797.3</v>
       </c>
       <c r="M37">
-        <v>98.43684423490578</v>
+        <v>101.2493254987602</v>
       </c>
       <c r="N37">
-        <v>698.8631557650942</v>
+        <v>696.0506745012397</v>
       </c>
       <c r="O37">
-        <v>174.7157889412736</v>
+        <v>174.0126686253099</v>
       </c>
       <c r="P37">
-        <v>524.1473668238207</v>
+        <v>522.0380058759297</v>
       </c>
       <c r="Q37">
-        <v>1276.447366823821</v>
+        <v>1274.33800587593</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0884353241488663</v>
+        <v>0.08898286683913428</v>
       </c>
       <c r="T37">
-        <v>0.8310418247485111</v>
+        <v>0.8417144509225073</v>
       </c>
       <c r="U37">
         <v>0.05943661666253409</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.099609513053416</v>
+        <v>7.87462035991304</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07299692127593015</v>
+        <v>0.07290876998118198</v>
       </c>
       <c r="C38">
-        <v>4237.282529197329</v>
+        <v>4198.049291363461</v>
       </c>
       <c r="D38">
-        <v>5043.566529197329</v>
+        <v>5051.652291363461</v>
       </c>
       <c r="E38">
-        <v>-1913.816</v>
+        <v>-1866.497</v>
       </c>
       <c r="F38">
-        <v>1703.484</v>
+        <v>1750.803</v>
       </c>
       <c r="G38">
         <v>897.2</v>
@@ -4403,28 +4403,28 @@
         <v>797.3</v>
       </c>
       <c r="M38">
-        <v>101.2493254987602</v>
+        <v>104.0618067626147</v>
       </c>
       <c r="N38">
-        <v>696.0506745012398</v>
+        <v>693.2381932373853</v>
       </c>
       <c r="O38">
-        <v>174.0126686253099</v>
+        <v>173.3095483093463</v>
       </c>
       <c r="P38">
-        <v>522.0380058759298</v>
+        <v>519.9286449280389</v>
       </c>
       <c r="Q38">
-        <v>1274.33800587593</v>
+        <v>1272.228644928039</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08898286683913428</v>
+        <v>0.08954779183702979</v>
       </c>
       <c r="T38">
-        <v>0.8417144509225073</v>
+        <v>0.8527258906258367</v>
       </c>
       <c r="U38">
         <v>0.05943661666253409</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.874620359913043</v>
+        <v>7.661792782618095</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07290876998118198</v>
+        <v>0.07304861868643384</v>
       </c>
       <c r="C39">
-        <v>4198.049291363461</v>
+        <v>4137.914564716175</v>
       </c>
       <c r="D39">
-        <v>5051.652291363461</v>
+        <v>5038.836564716175</v>
       </c>
       <c r="E39">
-        <v>-1866.497</v>
+        <v>-1819.178</v>
       </c>
       <c r="F39">
-        <v>1750.803</v>
+        <v>1798.122</v>
       </c>
       <c r="G39">
         <v>897.2</v>
@@ -4485,45 +4485,45 @@
         <v>797.3</v>
       </c>
       <c r="M39">
-        <v>104.0618067626147</v>
+        <v>108.3127856264691</v>
       </c>
       <c r="N39">
-        <v>693.2381932373853</v>
+        <v>688.9872143735308</v>
       </c>
       <c r="O39">
-        <v>173.3095483093463</v>
+        <v>172.2468035933827</v>
       </c>
       <c r="P39">
-        <v>519.9286449280389</v>
+        <v>516.7404107801481</v>
       </c>
       <c r="Q39">
-        <v>1272.228644928039</v>
+        <v>1269.040410780148</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08954779183702979</v>
+        <v>0.09013094022195423</v>
       </c>
       <c r="T39">
-        <v>0.8527258906258367</v>
+        <v>0.8640925380615317</v>
       </c>
       <c r="U39">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.661792782618095</v>
+        <v>7.361088493740654</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07304861868643384</v>
+        <v>0.07296646739168568</v>
       </c>
       <c r="C40">
-        <v>4137.914564716175</v>
+        <v>4098.116012846031</v>
       </c>
       <c r="D40">
-        <v>5038.836564716175</v>
+        <v>5046.357012846031</v>
       </c>
       <c r="E40">
-        <v>-1819.178</v>
+        <v>-1771.859</v>
       </c>
       <c r="F40">
-        <v>1798.122</v>
+        <v>1845.441</v>
       </c>
       <c r="G40">
         <v>897.2</v>
@@ -4567,28 +4567,28 @@
         <v>797.3</v>
       </c>
       <c r="M40">
-        <v>108.3127856264691</v>
+        <v>111.1631220903236</v>
       </c>
       <c r="N40">
-        <v>688.9872143735308</v>
+        <v>686.1368779096764</v>
       </c>
       <c r="O40">
-        <v>172.2468035933827</v>
+        <v>171.5342194774191</v>
       </c>
       <c r="P40">
-        <v>516.7404107801481</v>
+        <v>514.6026584322573</v>
       </c>
       <c r="Q40">
-        <v>1269.040410780148</v>
+        <v>1266.902658432257</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09013094022195423</v>
+        <v>0.09073320822605649</v>
       </c>
       <c r="T40">
-        <v>0.8640925380615317</v>
+        <v>0.8758318624623315</v>
       </c>
       <c r="U40">
         <v>0.0602366166625341</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.361088493740654</v>
+        <v>7.172342634926791</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07296646739168568</v>
+        <v>0.07288431609693753</v>
       </c>
       <c r="C41">
-        <v>4098.116012846031</v>
+        <v>4058.339943021841</v>
       </c>
       <c r="D41">
-        <v>5046.357012846031</v>
+        <v>5053.899943021841</v>
       </c>
       <c r="E41">
-        <v>-1771.859</v>
+        <v>-1724.54</v>
       </c>
       <c r="F41">
-        <v>1845.441</v>
+        <v>1892.76</v>
       </c>
       <c r="G41">
         <v>897.2</v>
@@ -4649,28 +4649,28 @@
         <v>797.3</v>
       </c>
       <c r="M41">
-        <v>111.1631220903236</v>
+        <v>114.013458554178</v>
       </c>
       <c r="N41">
-        <v>686.1368779096764</v>
+        <v>683.286541445822</v>
       </c>
       <c r="O41">
-        <v>171.5342194774191</v>
+        <v>170.8216353614555</v>
       </c>
       <c r="P41">
-        <v>514.6026584322573</v>
+        <v>512.4649060843665</v>
       </c>
       <c r="Q41">
-        <v>1266.902658432257</v>
+        <v>1264.764906084366</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09073320822605649</v>
+        <v>0.09135555183029551</v>
       </c>
       <c r="T41">
-        <v>0.8758318624623315</v>
+        <v>0.8879624976764912</v>
       </c>
       <c r="U41">
         <v>0.0602366166625341</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.172342634926791</v>
+        <v>6.993034069053621</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07288431609693753</v>
+        <v>0.07280216480218937</v>
       </c>
       <c r="C42">
-        <v>4058.339943021841</v>
+        <v>4018.586456208139</v>
       </c>
       <c r="D42">
-        <v>5053.899943021841</v>
+        <v>5061.465456208139</v>
       </c>
       <c r="E42">
-        <v>-1724.54</v>
+        <v>-1677.221</v>
       </c>
       <c r="F42">
-        <v>1892.76</v>
+        <v>1940.079</v>
       </c>
       <c r="G42">
         <v>897.2</v>
@@ -4731,28 +4731,28 @@
         <v>797.3</v>
       </c>
       <c r="M42">
-        <v>114.013458554178</v>
+        <v>116.8637950180325</v>
       </c>
       <c r="N42">
-        <v>683.286541445822</v>
+        <v>680.4362049819674</v>
       </c>
       <c r="O42">
-        <v>170.8216353614555</v>
+        <v>170.1090512454919</v>
       </c>
       <c r="P42">
-        <v>512.4649060843665</v>
+        <v>510.3271537364756</v>
       </c>
       <c r="Q42">
-        <v>1264.764906084366</v>
+        <v>1262.627153736476</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09135555183029551</v>
+        <v>0.09199899182789856</v>
       </c>
       <c r="T42">
-        <v>0.8879624976764912</v>
+        <v>0.9005043408640123</v>
       </c>
       <c r="U42">
         <v>0.0602366166625341</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.993034069053621</v>
+        <v>6.822472262491337</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07280216480218937</v>
+        <v>0.07272001350744121</v>
       </c>
       <c r="C43">
-        <v>4018.586456208139</v>
+        <v>3978.855653974926</v>
       </c>
       <c r="D43">
-        <v>5061.465456208139</v>
+        <v>5069.053653974926</v>
       </c>
       <c r="E43">
-        <v>-1677.221</v>
+        <v>-1629.902</v>
       </c>
       <c r="F43">
-        <v>1940.079</v>
+        <v>1987.398</v>
       </c>
       <c r="G43">
         <v>897.2</v>
@@ -4813,28 +4813,28 @@
         <v>797.3</v>
       </c>
       <c r="M43">
-        <v>116.8637950180325</v>
+        <v>119.714131481887</v>
       </c>
       <c r="N43">
-        <v>680.4362049819674</v>
+        <v>677.585868518113</v>
       </c>
       <c r="O43">
-        <v>170.1090512454919</v>
+        <v>169.3964671295282</v>
       </c>
       <c r="P43">
-        <v>510.3271537364756</v>
+        <v>508.1894013885848</v>
       </c>
       <c r="Q43">
-        <v>1262.627153736476</v>
+        <v>1260.489401388585</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09199899182789856</v>
+        <v>0.09266461941162582</v>
       </c>
       <c r="T43">
-        <v>0.9005043408640123</v>
+        <v>0.9134786614028271</v>
       </c>
       <c r="U43">
         <v>0.0602366166625341</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.822472262491337</v>
+        <v>6.660032446717733</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07272001350744123</v>
+        <v>0.07263786221269307</v>
       </c>
       <c r="C44">
-        <v>3978.855653974926</v>
+        <v>3939.147638502214</v>
       </c>
       <c r="D44">
-        <v>5069.053653974926</v>
+        <v>5076.664638502214</v>
       </c>
       <c r="E44">
-        <v>-1629.902</v>
+        <v>-1582.583</v>
       </c>
       <c r="F44">
-        <v>1987.398</v>
+        <v>2034.717</v>
       </c>
       <c r="G44">
         <v>897.2</v>
@@ -4895,28 +4895,28 @@
         <v>797.3</v>
       </c>
       <c r="M44">
-        <v>119.7141314818869</v>
+        <v>122.5644679457414</v>
       </c>
       <c r="N44">
-        <v>677.585868518113</v>
+        <v>674.7355320542586</v>
       </c>
       <c r="O44">
-        <v>169.3964671295282</v>
+        <v>168.6838830135646</v>
       </c>
       <c r="P44">
-        <v>508.1894013885848</v>
+        <v>506.0516490406939</v>
       </c>
       <c r="Q44">
-        <v>1260.489401388585</v>
+        <v>1258.351649040694</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09266461941162582</v>
+        <v>0.0933536023491681</v>
       </c>
       <c r="T44">
-        <v>0.9134786614028271</v>
+        <v>0.9269082212587934</v>
       </c>
       <c r="U44">
         <v>0.0602366166625341</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.660032446717734</v>
+        <v>6.50514797121267</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07263786221269307</v>
+        <v>0.07255571091794492</v>
       </c>
       <c r="C45">
-        <v>3939.147638502214</v>
+        <v>3899.462512584618</v>
       </c>
       <c r="D45">
-        <v>5076.664638502214</v>
+        <v>5084.298512584618</v>
       </c>
       <c r="E45">
-        <v>-1582.583</v>
+        <v>-1535.264</v>
       </c>
       <c r="F45">
-        <v>2034.717</v>
+        <v>2082.036</v>
       </c>
       <c r="G45">
         <v>897.2</v>
@@ -4977,28 +4977,28 @@
         <v>797.3</v>
       </c>
       <c r="M45">
-        <v>122.5644679457414</v>
+        <v>125.4148044095958</v>
       </c>
       <c r="N45">
-        <v>674.7355320542586</v>
+        <v>671.8851955904041</v>
       </c>
       <c r="O45">
-        <v>168.6838830135646</v>
+        <v>167.971298897601</v>
       </c>
       <c r="P45">
-        <v>506.0516490406939</v>
+        <v>503.9138966928031</v>
       </c>
       <c r="Q45">
-        <v>1258.351649040694</v>
+        <v>1256.213896692803</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0933536023491681</v>
+        <v>0.09406719182019405</v>
       </c>
       <c r="T45">
-        <v>0.9269082212587934</v>
+        <v>0.9408174082524728</v>
       </c>
       <c r="U45">
         <v>0.0602366166625341</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.50514797121267</v>
+        <v>6.357303699139655</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07255571091794492</v>
+        <v>0.07247355962319676</v>
       </c>
       <c r="C46">
-        <v>3899.462512584618</v>
+        <v>3859.800379635979</v>
       </c>
       <c r="D46">
-        <v>5084.298512584618</v>
+        <v>5091.95537963598</v>
       </c>
       <c r="E46">
-        <v>-1535.264</v>
+        <v>-1487.945</v>
       </c>
       <c r="F46">
-        <v>2082.036</v>
+        <v>2129.355</v>
       </c>
       <c r="G46">
         <v>897.2</v>
@@ -5059,28 +5059,28 @@
         <v>797.3</v>
       </c>
       <c r="M46">
-        <v>125.4148044095958</v>
+        <v>128.2651408734503</v>
       </c>
       <c r="N46">
-        <v>671.8851955904041</v>
+        <v>669.0348591265497</v>
       </c>
       <c r="O46">
-        <v>167.971298897601</v>
+        <v>167.2587147816374</v>
       </c>
       <c r="P46">
-        <v>503.9138966928031</v>
+        <v>501.7761443449123</v>
       </c>
       <c r="Q46">
-        <v>1256.213896692803</v>
+        <v>1254.076144344912</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09406719182019405</v>
+        <v>0.09480672999925727</v>
       </c>
       <c r="T46">
-        <v>0.9408174082524728</v>
+        <v>0.955232383864104</v>
       </c>
       <c r="U46">
         <v>0.0602366166625341</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.357303699139655</v>
+        <v>6.216030283603218</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07247355962319676</v>
+        <v>0.0727364083284486</v>
       </c>
       <c r="C47">
-        <v>3859.800379635979</v>
+        <v>3788.063471055946</v>
       </c>
       <c r="D47">
-        <v>5091.95537963598</v>
+        <v>5067.537471055946</v>
       </c>
       <c r="E47">
-        <v>-1487.945</v>
+        <v>-1440.626</v>
       </c>
       <c r="F47">
-        <v>2129.355</v>
+        <v>2176.674</v>
       </c>
       <c r="G47">
         <v>897.2</v>
@@ -5141,45 +5141,45 @@
         <v>797.3</v>
       </c>
       <c r="M47">
-        <v>128.2651408734503</v>
+        <v>133.2921513373047</v>
       </c>
       <c r="N47">
-        <v>669.0348591265497</v>
+        <v>664.0078486626952</v>
       </c>
       <c r="O47">
-        <v>167.2587147816374</v>
+        <v>166.0019621656738</v>
       </c>
       <c r="P47">
-        <v>501.7761443449123</v>
+        <v>498.0058864970214</v>
       </c>
       <c r="Q47">
-        <v>1254.076144344912</v>
+        <v>1250.305886497021</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09480672999925727</v>
+        <v>0.09557365848124878</v>
       </c>
       <c r="T47">
-        <v>0.955232383864104</v>
+        <v>0.9701812474613514</v>
       </c>
       <c r="U47">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.216030283603218</v>
+        <v>5.981597505935505</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0727364083284486</v>
+        <v>0.07266175703370047</v>
       </c>
       <c r="C48">
-        <v>3788.063471055946</v>
+        <v>3747.655524124437</v>
       </c>
       <c r="D48">
-        <v>5067.537471055946</v>
+        <v>5074.448524124437</v>
       </c>
       <c r="E48">
-        <v>-1440.626</v>
+        <v>-1393.307</v>
       </c>
       <c r="F48">
-        <v>2176.674</v>
+        <v>2223.993</v>
       </c>
       <c r="G48">
         <v>897.2</v>
@@ -5223,28 +5223,28 @@
         <v>797.3</v>
       </c>
       <c r="M48">
-        <v>133.2921513373047</v>
+        <v>136.1898068011592</v>
       </c>
       <c r="N48">
-        <v>664.0078486626952</v>
+        <v>661.1101931988408</v>
       </c>
       <c r="O48">
-        <v>166.0019621656738</v>
+        <v>165.2775482997102</v>
       </c>
       <c r="P48">
-        <v>498.0058864970214</v>
+        <v>495.8326448991306</v>
       </c>
       <c r="Q48">
-        <v>1250.305886497021</v>
+        <v>1248.132644899131</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09557365848124878</v>
+        <v>0.09636952766067394</v>
       </c>
       <c r="T48">
-        <v>0.9701812474613514</v>
+        <v>0.9856942191188722</v>
       </c>
       <c r="U48">
         <v>0.0612366166625341</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.981597505935505</v>
+        <v>5.854329473894325</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07266175703370047</v>
+        <v>0.0725871057389523</v>
       </c>
       <c r="C49">
-        <v>3747.655524124437</v>
+        <v>3707.266453375667</v>
       </c>
       <c r="D49">
-        <v>5074.448524124437</v>
+        <v>5081.378453375667</v>
       </c>
       <c r="E49">
-        <v>-1393.307</v>
+        <v>-1345.988</v>
       </c>
       <c r="F49">
-        <v>2223.993</v>
+        <v>2271.312</v>
       </c>
       <c r="G49">
         <v>897.2</v>
@@ -5305,28 +5305,28 @@
         <v>797.3</v>
       </c>
       <c r="M49">
-        <v>136.1898068011592</v>
+        <v>139.0874622650136</v>
       </c>
       <c r="N49">
-        <v>661.1101931988408</v>
+        <v>658.2125377349863</v>
       </c>
       <c r="O49">
-        <v>165.2775482997102</v>
+        <v>164.5531344337466</v>
       </c>
       <c r="P49">
-        <v>495.8326448991306</v>
+        <v>493.6594033012398</v>
       </c>
       <c r="Q49">
-        <v>1248.132644899131</v>
+        <v>1245.95940330124</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09636952766067394</v>
+        <v>0.09719600719315388</v>
       </c>
       <c r="T49">
-        <v>0.9856942191188722</v>
+        <v>1.001803843532451</v>
       </c>
       <c r="U49">
         <v>0.0612366166625341</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.854329473894325</v>
+        <v>5.732364276521526</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07258710573895229</v>
+        <v>0.07251245444420415</v>
       </c>
       <c r="C50">
-        <v>3707.266453375668</v>
+        <v>3666.896336250263</v>
       </c>
       <c r="D50">
-        <v>5081.378453375668</v>
+        <v>5088.327336250263</v>
       </c>
       <c r="E50">
-        <v>-1345.988</v>
+        <v>-1298.669</v>
       </c>
       <c r="F50">
-        <v>2271.312</v>
+        <v>2318.631</v>
       </c>
       <c r="G50">
         <v>897.2</v>
@@ -5387,28 +5387,28 @@
         <v>797.3</v>
       </c>
       <c r="M50">
-        <v>139.0874622650136</v>
+        <v>141.9851177288681</v>
       </c>
       <c r="N50">
-        <v>658.2125377349863</v>
+        <v>655.3148822711319</v>
       </c>
       <c r="O50">
-        <v>164.5531344337466</v>
+        <v>163.828720567783</v>
       </c>
       <c r="P50">
-        <v>493.6594033012398</v>
+        <v>491.4861617033489</v>
       </c>
       <c r="Q50">
-        <v>1245.95940330124</v>
+        <v>1243.786161703349</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09719600719315388</v>
+        <v>0.09805489768769189</v>
       </c>
       <c r="T50">
-        <v>1.001803843532451</v>
+        <v>1.018545217923034</v>
       </c>
       <c r="U50">
         <v>0.0612366166625341</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.732364276521526</v>
+        <v>5.615377250470067</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07251245444420415</v>
+        <v>0.072437803149456</v>
       </c>
       <c r="C51">
-        <v>3666.896336250263</v>
+        <v>3626.545250613044</v>
       </c>
       <c r="D51">
-        <v>5088.327336250263</v>
+        <v>5095.295250613044</v>
       </c>
       <c r="E51">
-        <v>-1298.669</v>
+        <v>-1251.35</v>
       </c>
       <c r="F51">
-        <v>2318.631</v>
+        <v>2365.95</v>
       </c>
       <c r="G51">
         <v>897.2</v>
@@ -5469,28 +5469,28 @@
         <v>797.3</v>
       </c>
       <c r="M51">
-        <v>141.9851177288681</v>
+        <v>144.8827731927225</v>
       </c>
       <c r="N51">
-        <v>655.3148822711319</v>
+        <v>652.4172268072774</v>
       </c>
       <c r="O51">
-        <v>163.828720567783</v>
+        <v>163.1043067018194</v>
       </c>
       <c r="P51">
-        <v>491.4861617033489</v>
+        <v>489.312920105458</v>
       </c>
       <c r="Q51">
-        <v>1243.786161703349</v>
+        <v>1241.612920105458</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09805489768769189</v>
+        <v>0.09894814380201142</v>
       </c>
       <c r="T51">
-        <v>1.018545217923034</v>
+        <v>1.03595624728924</v>
       </c>
       <c r="U51">
         <v>0.0612366166625341</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.615377250470067</v>
+        <v>5.503069705460665</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.072437803149456</v>
+        <v>0.07236315185470785</v>
       </c>
       <c r="C52">
-        <v>3626.545250613044</v>
+        <v>3586.213274755919</v>
       </c>
       <c r="D52">
-        <v>5095.295250613044</v>
+        <v>5102.282274755918</v>
       </c>
       <c r="E52">
-        <v>-1251.35</v>
+        <v>-1204.031</v>
       </c>
       <c r="F52">
-        <v>2365.95</v>
+        <v>2413.269</v>
       </c>
       <c r="G52">
         <v>897.2</v>
@@ -5551,28 +5551,28 @@
         <v>797.3</v>
       </c>
       <c r="M52">
-        <v>144.8827731927225</v>
+        <v>147.780428656577</v>
       </c>
       <c r="N52">
-        <v>652.4172268072774</v>
+        <v>649.519571343423</v>
       </c>
       <c r="O52">
-        <v>163.1043067018194</v>
+        <v>162.3798928358557</v>
       </c>
       <c r="P52">
-        <v>489.312920105458</v>
+        <v>487.1396785075672</v>
       </c>
       <c r="Q52">
-        <v>1241.612920105458</v>
+        <v>1239.439678507567</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09894814380201142</v>
+        <v>0.0998778489414052</v>
       </c>
       <c r="T52">
-        <v>1.03595624728924</v>
+        <v>1.054077930915291</v>
       </c>
       <c r="U52">
         <v>0.0612366166625341</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.503069705460665</v>
+        <v>5.395166377902613</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07236315185470785</v>
+        <v>0.07228850055995968</v>
       </c>
       <c r="C53">
-        <v>3586.213274755919</v>
+        <v>3545.900487400828</v>
       </c>
       <c r="D53">
-        <v>5102.282274755918</v>
+        <v>5109.288487400828</v>
       </c>
       <c r="E53">
-        <v>-1204.031</v>
+        <v>-1156.712</v>
       </c>
       <c r="F53">
-        <v>2413.269</v>
+        <v>2460.588</v>
       </c>
       <c r="G53">
         <v>897.2</v>
@@ -5633,28 +5633,28 @@
         <v>797.3</v>
       </c>
       <c r="M53">
-        <v>147.780428656577</v>
+        <v>150.6780841204314</v>
       </c>
       <c r="N53">
-        <v>649.519571343423</v>
+        <v>646.6219158795685</v>
       </c>
       <c r="O53">
-        <v>162.3798928358557</v>
+        <v>161.6554789698921</v>
       </c>
       <c r="P53">
-        <v>487.1396785075672</v>
+        <v>484.9664369096764</v>
       </c>
       <c r="Q53">
-        <v>1239.439678507567</v>
+        <v>1237.266436909676</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0998778489414052</v>
+        <v>0.1008462917949404</v>
       </c>
       <c r="T53">
-        <v>1.054077930915291</v>
+        <v>1.072954684692427</v>
       </c>
       <c r="U53">
         <v>0.0612366166625341</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.395166377902613</v>
+        <v>5.291413178327563</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07228850055995968</v>
+        <v>0.07221384926521153</v>
       </c>
       <c r="C54">
-        <v>3545.900487400828</v>
+        <v>3505.606967702688</v>
       </c>
       <c r="D54">
-        <v>5109.288487400828</v>
+        <v>5116.313967702688</v>
       </c>
       <c r="E54">
-        <v>-1156.712</v>
+        <v>-1109.393</v>
       </c>
       <c r="F54">
-        <v>2460.588</v>
+        <v>2507.907</v>
       </c>
       <c r="G54">
         <v>897.2</v>
@@ -5715,28 +5715,28 @@
         <v>797.3</v>
       </c>
       <c r="M54">
-        <v>150.6780841204314</v>
+        <v>153.5757395842859</v>
       </c>
       <c r="N54">
-        <v>646.6219158795685</v>
+        <v>643.7242604157141</v>
       </c>
       <c r="O54">
-        <v>161.6554789698921</v>
+        <v>160.9310651039285</v>
       </c>
       <c r="P54">
-        <v>484.9664369096764</v>
+        <v>482.7931953117856</v>
       </c>
       <c r="Q54">
-        <v>1237.266436909676</v>
+        <v>1235.093195311786</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1008462917949404</v>
+        <v>0.1018559449826686</v>
       </c>
       <c r="T54">
-        <v>1.072954684692427</v>
+        <v>1.092634704587739</v>
       </c>
       <c r="U54">
         <v>0.0612366166625341</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.291413178327563</v>
+        <v>5.191575193830816</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07221384926521153</v>
+        <v>0.07213919797046338</v>
       </c>
       <c r="C55">
-        <v>3505.606967702688</v>
+        <v>3465.33279525239</v>
       </c>
       <c r="D55">
-        <v>5116.313967702688</v>
+        <v>5123.35879525239</v>
       </c>
       <c r="E55">
-        <v>-1109.393</v>
+        <v>-1062.074</v>
       </c>
       <c r="F55">
-        <v>2507.907</v>
+        <v>2555.226</v>
       </c>
       <c r="G55">
         <v>897.2</v>
@@ -5797,28 +5797,28 @@
         <v>797.3</v>
       </c>
       <c r="M55">
-        <v>153.5757395842859</v>
+        <v>156.4733950481404</v>
       </c>
       <c r="N55">
-        <v>643.7242604157141</v>
+        <v>640.8266049518596</v>
       </c>
       <c r="O55">
-        <v>160.9310651039285</v>
+        <v>160.2066512379649</v>
       </c>
       <c r="P55">
-        <v>482.7931953117856</v>
+        <v>480.6199537138947</v>
       </c>
       <c r="Q55">
-        <v>1235.093195311786</v>
+        <v>1232.919953713895</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1018559449826686</v>
+        <v>0.1029094961350806</v>
       </c>
       <c r="T55">
-        <v>1.092634704587739</v>
+        <v>1.113170377521978</v>
       </c>
       <c r="U55">
         <v>0.0612366166625341</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.191575193830816</v>
+        <v>5.095434912463578</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07213919797046338</v>
+        <v>0.07206454667571524</v>
       </c>
       <c r="C56">
-        <v>3465.33279525239</v>
+        <v>3425.078050079786</v>
       </c>
       <c r="D56">
-        <v>5123.35879525239</v>
+        <v>5130.423050079787</v>
       </c>
       <c r="E56">
-        <v>-1062.074</v>
+        <v>-1014.755</v>
       </c>
       <c r="F56">
-        <v>2555.226</v>
+        <v>2602.545</v>
       </c>
       <c r="G56">
         <v>897.2</v>
@@ -5879,28 +5879,28 @@
         <v>797.3</v>
       </c>
       <c r="M56">
-        <v>156.4733950481404</v>
+        <v>159.3710505119948</v>
       </c>
       <c r="N56">
-        <v>640.8266049518596</v>
+        <v>637.9289494880052</v>
       </c>
       <c r="O56">
-        <v>160.2066512379649</v>
+        <v>159.4822373720013</v>
       </c>
       <c r="P56">
-        <v>480.6199537138947</v>
+        <v>478.4467121160039</v>
       </c>
       <c r="Q56">
-        <v>1232.919953713895</v>
+        <v>1230.746712116004</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1029094961350806</v>
+        <v>0.1040098717831554</v>
       </c>
       <c r="T56">
-        <v>1.113170377521978</v>
+        <v>1.134618747031072</v>
       </c>
       <c r="U56">
         <v>0.0612366166625341</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.095434912463578</v>
+        <v>5.002790641327877</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07206454667571524</v>
+        <v>0.07198989538096708</v>
       </c>
       <c r="C57">
-        <v>3425.078050079786</v>
+        <v>3384.842812656738</v>
       </c>
       <c r="D57">
-        <v>5130.423050079787</v>
+        <v>5137.506812656738</v>
       </c>
       <c r="E57">
-        <v>-1014.755</v>
+        <v>-967.4360000000001</v>
       </c>
       <c r="F57">
-        <v>2602.545</v>
+        <v>2649.864</v>
       </c>
       <c r="G57">
         <v>897.2</v>
@@ -5961,28 +5961,28 @@
         <v>797.3</v>
       </c>
       <c r="M57">
-        <v>159.3710505119948</v>
+        <v>162.2687059758493</v>
       </c>
       <c r="N57">
-        <v>637.9289494880052</v>
+        <v>635.0312940241507</v>
       </c>
       <c r="O57">
-        <v>159.4822373720013</v>
+        <v>158.7578235060377</v>
       </c>
       <c r="P57">
-        <v>478.4467121160039</v>
+        <v>476.2734705181131</v>
       </c>
       <c r="Q57">
-        <v>1230.746712116004</v>
+        <v>1228.573470518113</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1040098717831554</v>
+        <v>0.1051602645061426</v>
       </c>
       <c r="T57">
-        <v>1.134618747031072</v>
+        <v>1.157042042426943</v>
       </c>
       <c r="U57">
         <v>0.0612366166625341</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.002790641327877</v>
+        <v>4.913455094161308</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07198989538096708</v>
+        <v>0.07191524408621891</v>
       </c>
       <c r="C58">
-        <v>3384.842812656738</v>
+        <v>3344.627163900156</v>
       </c>
       <c r="D58">
-        <v>5137.506812656738</v>
+        <v>5144.610163900156</v>
       </c>
       <c r="E58">
-        <v>-967.4360000000001</v>
+        <v>-920.1170000000002</v>
       </c>
       <c r="F58">
-        <v>2649.864</v>
+        <v>2697.183</v>
       </c>
       <c r="G58">
         <v>897.2</v>
@@ -6043,28 +6043,28 @@
         <v>797.3</v>
       </c>
       <c r="M58">
-        <v>162.2687059758493</v>
+        <v>165.1663614397037</v>
       </c>
       <c r="N58">
-        <v>635.0312940241507</v>
+        <v>632.1336385602963</v>
       </c>
       <c r="O58">
-        <v>158.7578235060377</v>
+        <v>158.0334096400741</v>
       </c>
       <c r="P58">
-        <v>476.2734705181131</v>
+        <v>474.1002289202222</v>
       </c>
       <c r="Q58">
-        <v>1228.573470518113</v>
+        <v>1226.400228920222</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1051602645061426</v>
+        <v>0.1063641638674084</v>
       </c>
       <c r="T58">
-        <v>1.157042042426943</v>
+        <v>1.180508281794715</v>
       </c>
       <c r="U58">
         <v>0.0612366166625341</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.913455094161308</v>
+        <v>4.827254127597074</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07191524408621891</v>
+        <v>0.07184059279147077</v>
       </c>
       <c r="C59">
-        <v>3344.627163900156</v>
+        <v>3304.431185175087</v>
       </c>
       <c r="D59">
-        <v>5144.610163900156</v>
+        <v>5151.733185175087</v>
       </c>
       <c r="E59">
-        <v>-920.1170000000002</v>
+        <v>-872.7980000000002</v>
       </c>
       <c r="F59">
-        <v>2697.183</v>
+        <v>2744.502</v>
       </c>
       <c r="G59">
         <v>897.2</v>
@@ -6125,28 +6125,28 @@
         <v>797.3</v>
       </c>
       <c r="M59">
-        <v>165.1663614397037</v>
+        <v>168.0640169035582</v>
       </c>
       <c r="N59">
-        <v>632.1336385602963</v>
+        <v>629.2359830964418</v>
       </c>
       <c r="O59">
-        <v>158.0334096400741</v>
+        <v>157.3089957741105</v>
       </c>
       <c r="P59">
-        <v>474.1002289202222</v>
+        <v>471.9269873223313</v>
       </c>
       <c r="Q59">
-        <v>1226.400228920222</v>
+        <v>1224.226987322331</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1063641638674084</v>
+        <v>0.1076253917696868</v>
       </c>
       <c r="T59">
-        <v>1.180508281794715</v>
+        <v>1.205091961132381</v>
       </c>
       <c r="U59">
         <v>0.0612366166625341</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.827254127597074</v>
+        <v>4.744025608155745</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07184059279147077</v>
+        <v>0.07176594149672261</v>
       </c>
       <c r="C60">
-        <v>3304.431185175087</v>
+        <v>3264.25495829783</v>
       </c>
       <c r="D60">
-        <v>5151.733185175087</v>
+        <v>5158.87595829783</v>
       </c>
       <c r="E60">
-        <v>-872.7980000000007</v>
+        <v>-825.4790000000007</v>
       </c>
       <c r="F60">
-        <v>2744.501999999999</v>
+        <v>2791.820999999999</v>
       </c>
       <c r="G60">
         <v>897.2</v>
@@ -6207,28 +6207,28 @@
         <v>797.3</v>
       </c>
       <c r="M60">
-        <v>168.0640169035581</v>
+        <v>170.9616723674126</v>
       </c>
       <c r="N60">
-        <v>629.2359830964418</v>
+        <v>626.3383276325874</v>
       </c>
       <c r="O60">
-        <v>157.3089957741105</v>
+        <v>156.5845819081468</v>
       </c>
       <c r="P60">
-        <v>471.9269873223313</v>
+        <v>469.7537457244405</v>
       </c>
       <c r="Q60">
-        <v>1224.226987322331</v>
+        <v>1222.05374572444</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1076253917696867</v>
+        <v>0.1089481429842714</v>
       </c>
       <c r="T60">
-        <v>1.205091961132381</v>
+        <v>1.230874844340177</v>
       </c>
       <c r="U60">
         <v>0.0612366166625341</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.744025608155747</v>
+        <v>4.663618394458191</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07176594149672261</v>
+        <v>0.07169129020197446</v>
       </c>
       <c r="C61">
-        <v>3264.25495829783</v>
+        <v>3224.098565539052</v>
       </c>
       <c r="D61">
-        <v>5158.87595829783</v>
+        <v>5166.038565539052</v>
       </c>
       <c r="E61">
-        <v>-825.4790000000007</v>
+        <v>-778.1600000000003</v>
       </c>
       <c r="F61">
-        <v>2791.820999999999</v>
+        <v>2839.14</v>
       </c>
       <c r="G61">
         <v>897.2</v>
@@ -6289,28 +6289,28 @@
         <v>797.3</v>
       </c>
       <c r="M61">
-        <v>170.9616723674126</v>
+        <v>173.8593278312671</v>
       </c>
       <c r="N61">
-        <v>626.3383276325874</v>
+        <v>623.4406721687329</v>
       </c>
       <c r="O61">
-        <v>156.5845819081468</v>
+        <v>155.8601680421832</v>
       </c>
       <c r="P61">
-        <v>469.7537457244405</v>
+        <v>467.5805041265497</v>
       </c>
       <c r="Q61">
-        <v>1222.05374572444</v>
+        <v>1219.88050412655</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1089481429842714</v>
+        <v>0.1103370317595853</v>
       </c>
       <c r="T61">
-        <v>1.230874844340177</v>
+        <v>1.257946871708362</v>
       </c>
       <c r="U61">
         <v>0.0612366166625341</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.663618394458191</v>
+        <v>4.585891421217221</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07169129020197446</v>
+        <v>0.0716166389072263</v>
       </c>
       <c r="C62">
-        <v>3224.098565539052</v>
+        <v>3183.962089626961</v>
       </c>
       <c r="D62">
-        <v>5166.038565539052</v>
+        <v>5173.221089626961</v>
       </c>
       <c r="E62">
-        <v>-778.1600000000003</v>
+        <v>-730.8410000000003</v>
       </c>
       <c r="F62">
-        <v>2839.14</v>
+        <v>2886.459</v>
       </c>
       <c r="G62">
         <v>897.2</v>
@@ -6371,28 +6371,28 @@
         <v>797.3</v>
       </c>
       <c r="M62">
-        <v>173.8593278312671</v>
+        <v>176.7569832951215</v>
       </c>
       <c r="N62">
-        <v>623.4406721687329</v>
+        <v>620.5430167048785</v>
       </c>
       <c r="O62">
-        <v>155.8601680421832</v>
+        <v>155.1357541762196</v>
       </c>
       <c r="P62">
-        <v>467.5805041265497</v>
+        <v>465.4072625286589</v>
       </c>
       <c r="Q62">
-        <v>1219.88050412655</v>
+        <v>1217.707262528659</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1103370317595853</v>
+        <v>0.1117971456002999</v>
       </c>
       <c r="T62">
-        <v>1.257946871708362</v>
+        <v>1.286407208172353</v>
       </c>
       <c r="U62">
         <v>0.0612366166625341</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.585891421217221</v>
+        <v>4.510712873328414</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0716166389072263</v>
+        <v>0.07270448761247815</v>
       </c>
       <c r="C63">
-        <v>3183.962089626961</v>
+        <v>3033.912315802784</v>
       </c>
       <c r="D63">
-        <v>5173.221089626961</v>
+        <v>5070.490315802784</v>
       </c>
       <c r="E63">
-        <v>-730.8410000000003</v>
+        <v>-683.5220000000004</v>
       </c>
       <c r="F63">
-        <v>2886.459</v>
+        <v>2933.778</v>
       </c>
       <c r="G63">
         <v>897.2</v>
@@ -6453,45 +6453,45 @@
         <v>797.3</v>
       </c>
       <c r="M63">
-        <v>176.7569832951215</v>
+        <v>186.9890837589759</v>
       </c>
       <c r="N63">
-        <v>620.5430167048785</v>
+        <v>610.310916241024</v>
       </c>
       <c r="O63">
-        <v>155.1357541762196</v>
+        <v>152.577729060256</v>
       </c>
       <c r="P63">
-        <v>465.4072625286589</v>
+        <v>457.733187180768</v>
       </c>
       <c r="Q63">
-        <v>1217.707262528659</v>
+        <v>1210.033187180768</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1117971456002999</v>
+        <v>0.1133341075378942</v>
       </c>
       <c r="T63">
-        <v>1.286407208172353</v>
+        <v>1.316365457081816</v>
       </c>
       <c r="U63">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.510712873328414</v>
+        <v>4.263885270584559</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07270448761247815</v>
+        <v>0.07264858631773001</v>
       </c>
       <c r="C64">
-        <v>3033.912315802784</v>
+        <v>2991.772796854156</v>
       </c>
       <c r="D64">
-        <v>5070.490315802784</v>
+        <v>5075.669796854156</v>
       </c>
       <c r="E64">
-        <v>-683.5220000000004</v>
+        <v>-636.2030000000004</v>
       </c>
       <c r="F64">
-        <v>2933.778</v>
+        <v>2981.097</v>
       </c>
       <c r="G64">
         <v>897.2</v>
@@ -6535,28 +6535,28 @@
         <v>797.3</v>
       </c>
       <c r="M64">
-        <v>186.9890837589759</v>
+        <v>190.0050367228304</v>
       </c>
       <c r="N64">
-        <v>610.310916241024</v>
+        <v>607.2949632771696</v>
       </c>
       <c r="O64">
-        <v>152.577729060256</v>
+        <v>151.8237408192924</v>
       </c>
       <c r="P64">
-        <v>457.733187180768</v>
+        <v>455.4712224578772</v>
       </c>
       <c r="Q64">
-        <v>1210.033187180768</v>
+        <v>1207.771222457877</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1133341075378942</v>
+        <v>0.1149541484991423</v>
       </c>
       <c r="T64">
-        <v>1.316365457081816</v>
+        <v>1.347943070797196</v>
       </c>
       <c r="U64">
         <v>0.06373661666253409</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.263885270584559</v>
+        <v>4.196204552003852</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07264858631773001</v>
+        <v>0.07259268502298184</v>
       </c>
       <c r="C65">
-        <v>2991.772796854156</v>
+        <v>2949.643870354775</v>
       </c>
       <c r="D65">
-        <v>5075.669796854156</v>
+        <v>5080.859870354775</v>
       </c>
       <c r="E65">
-        <v>-636.2030000000004</v>
+        <v>-588.8840000000005</v>
       </c>
       <c r="F65">
-        <v>2981.097</v>
+        <v>3028.416</v>
       </c>
       <c r="G65">
         <v>897.2</v>
@@ -6617,28 +6617,28 @@
         <v>797.3</v>
       </c>
       <c r="M65">
-        <v>190.0050367228304</v>
+        <v>193.0209896866848</v>
       </c>
       <c r="N65">
-        <v>607.2949632771696</v>
+        <v>604.2790103133151</v>
       </c>
       <c r="O65">
-        <v>151.8237408192924</v>
+        <v>151.0697525783288</v>
       </c>
       <c r="P65">
-        <v>455.4712224578772</v>
+        <v>453.2092577349863</v>
       </c>
       <c r="Q65">
-        <v>1207.771222457877</v>
+        <v>1205.509257734986</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1149541484991423</v>
+        <v>0.1166641917360152</v>
       </c>
       <c r="T65">
-        <v>1.347943070797196</v>
+        <v>1.381274996385653</v>
       </c>
       <c r="U65">
         <v>0.06373661666253409</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.196204552003852</v>
+        <v>4.130638855878792</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07259268502298184</v>
+        <v>0.07253678372823369</v>
       </c>
       <c r="C66">
-        <v>2949.643870354775</v>
+        <v>2907.525568831494</v>
       </c>
       <c r="D66">
-        <v>5080.859870354775</v>
+        <v>5086.060568831494</v>
       </c>
       <c r="E66">
-        <v>-588.8840000000005</v>
+        <v>-541.5650000000005</v>
       </c>
       <c r="F66">
-        <v>3028.416</v>
+        <v>3075.735</v>
       </c>
       <c r="G66">
         <v>897.2</v>
@@ -6699,28 +6699,28 @@
         <v>797.3</v>
       </c>
       <c r="M66">
-        <v>193.0209896866848</v>
+        <v>196.0369426505393</v>
       </c>
       <c r="N66">
-        <v>604.2790103133151</v>
+        <v>601.2630573494607</v>
       </c>
       <c r="O66">
-        <v>151.0697525783288</v>
+        <v>150.3157643373652</v>
       </c>
       <c r="P66">
-        <v>453.2092577349863</v>
+        <v>450.9472930120955</v>
       </c>
       <c r="Q66">
-        <v>1205.509257734986</v>
+        <v>1203.247293012095</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1166641917360152</v>
+        <v>0.1184719517292809</v>
       </c>
       <c r="T66">
-        <v>1.381274996385653</v>
+        <v>1.416511603436307</v>
       </c>
       <c r="U66">
         <v>0.06373661666253409</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.130638855878792</v>
+        <v>4.06709056578835</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07253678372823369</v>
+        <v>0.07248088243348554</v>
       </c>
       <c r="C67">
-        <v>2907.525568831494</v>
+        <v>2865.417924944484</v>
       </c>
       <c r="D67">
-        <v>5086.060568831494</v>
+        <v>5091.271924944484</v>
       </c>
       <c r="E67">
-        <v>-541.5650000000005</v>
+        <v>-494.2460000000001</v>
       </c>
       <c r="F67">
-        <v>3075.735</v>
+        <v>3123.054</v>
       </c>
       <c r="G67">
         <v>897.2</v>
@@ -6781,28 +6781,28 @@
         <v>797.3</v>
       </c>
       <c r="M67">
-        <v>196.0369426505393</v>
+        <v>199.0528956143937</v>
       </c>
       <c r="N67">
-        <v>601.2630573494607</v>
+        <v>598.2471043856062</v>
       </c>
       <c r="O67">
-        <v>150.3157643373652</v>
+        <v>149.5617760964016</v>
       </c>
       <c r="P67">
-        <v>450.9472930120955</v>
+        <v>448.6853282892047</v>
       </c>
       <c r="Q67">
-        <v>1203.247293012095</v>
+        <v>1200.985328289205</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1184719517292809</v>
+        <v>0.1203860505456799</v>
       </c>
       <c r="T67">
-        <v>1.416511603436307</v>
+        <v>1.453820952078177</v>
       </c>
       <c r="U67">
         <v>0.06373661666253409</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.06709056578835</v>
+        <v>4.005467981458223</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07248088243348554</v>
+        <v>0.07418373113873739</v>
       </c>
       <c r="C68">
-        <v>2865.417924944484</v>
+        <v>2663.999257980596</v>
       </c>
       <c r="D68">
-        <v>5091.271924944484</v>
+        <v>4937.172257980596</v>
       </c>
       <c r="E68">
-        <v>-494.2460000000001</v>
+        <v>-446.9270000000001</v>
       </c>
       <c r="F68">
-        <v>3123.054</v>
+        <v>3170.373</v>
       </c>
       <c r="G68">
         <v>897.2</v>
@@ -6863,45 +6863,45 @@
         <v>797.3</v>
       </c>
       <c r="M68">
-        <v>199.0528956143937</v>
+        <v>213.1651540782482</v>
       </c>
       <c r="N68">
-        <v>598.2471043856062</v>
+        <v>584.1348459217518</v>
       </c>
       <c r="O68">
-        <v>149.5617760964016</v>
+        <v>146.0337114804379</v>
       </c>
       <c r="P68">
-        <v>448.6853282892047</v>
+        <v>438.1011344413138</v>
       </c>
       <c r="Q68">
-        <v>1200.985328289205</v>
+        <v>1190.401134441314</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1203860505456799</v>
+        <v>0.1224161553509515</v>
       </c>
       <c r="T68">
-        <v>1.453820952078177</v>
+        <v>1.493391473365008</v>
       </c>
       <c r="U68">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.005467981458223</v>
+        <v>3.740292373055161</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07418373113873739</v>
+        <v>0.07415407984398922</v>
       </c>
       <c r="C69">
-        <v>2663.999257980596</v>
+        <v>2619.2837139426</v>
       </c>
       <c r="D69">
-        <v>4937.172257980596</v>
+        <v>4939.7757139426</v>
       </c>
       <c r="E69">
-        <v>-446.9270000000001</v>
+        <v>-399.6080000000002</v>
       </c>
       <c r="F69">
-        <v>3170.373</v>
+        <v>3217.692</v>
       </c>
       <c r="G69">
         <v>897.2</v>
@@ -6945,28 +6945,28 @@
         <v>797.3</v>
       </c>
       <c r="M69">
-        <v>213.1651540782482</v>
+        <v>216.3467235421027</v>
       </c>
       <c r="N69">
-        <v>584.1348459217518</v>
+        <v>580.9532764578973</v>
       </c>
       <c r="O69">
-        <v>146.0337114804379</v>
+        <v>145.2383191144743</v>
       </c>
       <c r="P69">
-        <v>438.1011344413138</v>
+        <v>435.714957343423</v>
       </c>
       <c r="Q69">
-        <v>1190.401134441314</v>
+        <v>1188.014957343423</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1224161553509515</v>
+        <v>0.1245731417065526</v>
       </c>
       <c r="T69">
-        <v>1.493391473365008</v>
+        <v>1.535435152232266</v>
       </c>
       <c r="U69">
         <v>0.0672366166625341</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.740292373055161</v>
+        <v>3.685288073451408</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07415407984398922</v>
+        <v>0.07412442854924106</v>
       </c>
       <c r="C70">
-        <v>2619.2837139426</v>
+        <v>2574.570917047553</v>
       </c>
       <c r="D70">
-        <v>4939.7757139426</v>
+        <v>4942.381917047554</v>
       </c>
       <c r="E70">
-        <v>-399.6080000000002</v>
+        <v>-352.2890000000002</v>
       </c>
       <c r="F70">
-        <v>3217.692</v>
+        <v>3265.011</v>
       </c>
       <c r="G70">
         <v>897.2</v>
@@ -7027,28 +7027,28 @@
         <v>797.3</v>
       </c>
       <c r="M70">
-        <v>216.3467235421027</v>
+        <v>219.5282930059571</v>
       </c>
       <c r="N70">
-        <v>580.9532764578973</v>
+        <v>577.7717069940429</v>
       </c>
       <c r="O70">
-        <v>145.2383191144743</v>
+        <v>144.4429267485107</v>
       </c>
       <c r="P70">
-        <v>435.714957343423</v>
+        <v>433.3287802455322</v>
       </c>
       <c r="Q70">
-        <v>1188.014957343423</v>
+        <v>1185.628780245532</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1245731417065526</v>
+        <v>0.1268692884721925</v>
       </c>
       <c r="T70">
-        <v>1.535435152232266</v>
+        <v>1.580191326510315</v>
       </c>
       <c r="U70">
         <v>0.0672366166625341</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.685288073451408</v>
+        <v>3.631878101372403</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07412442854924106</v>
+        <v>0.07409477725449293</v>
       </c>
       <c r="C71">
-        <v>2574.570917047553</v>
+        <v>2529.860871645888</v>
       </c>
       <c r="D71">
-        <v>4942.381917047554</v>
+        <v>4944.990871645888</v>
       </c>
       <c r="E71">
-        <v>-352.2890000000002</v>
+        <v>-304.9700000000003</v>
       </c>
       <c r="F71">
-        <v>3265.011</v>
+        <v>3312.33</v>
       </c>
       <c r="G71">
         <v>897.2</v>
@@ -7109,28 +7109,28 @@
         <v>797.3</v>
       </c>
       <c r="M71">
-        <v>219.5282930059571</v>
+        <v>222.7098624698116</v>
       </c>
       <c r="N71">
-        <v>577.7717069940429</v>
+        <v>574.5901375301884</v>
       </c>
       <c r="O71">
-        <v>144.4429267485107</v>
+        <v>143.6475343825471</v>
       </c>
       <c r="P71">
-        <v>433.3287802455322</v>
+        <v>430.9426031476413</v>
       </c>
       <c r="Q71">
-        <v>1185.628780245532</v>
+        <v>1183.242603147641</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1268692884721925</v>
+        <v>0.1293185116888751</v>
       </c>
       <c r="T71">
-        <v>1.580191326510315</v>
+        <v>1.627931245740234</v>
       </c>
       <c r="U71">
         <v>0.0672366166625341</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.631878101372403</v>
+        <v>3.579994128495654</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07409477725449293</v>
+        <v>0.07406512595974477</v>
       </c>
       <c r="C72">
-        <v>2529.860871645888</v>
+        <v>2485.153582097236</v>
       </c>
       <c r="D72">
-        <v>4944.990871645888</v>
+        <v>4947.602582097236</v>
       </c>
       <c r="E72">
-        <v>-304.9700000000003</v>
+        <v>-257.6510000000003</v>
       </c>
       <c r="F72">
-        <v>3312.33</v>
+        <v>3359.649</v>
       </c>
       <c r="G72">
         <v>897.2</v>
@@ -7191,28 +7191,28 @@
         <v>797.3</v>
       </c>
       <c r="M72">
-        <v>222.7098624698116</v>
+        <v>225.891431933666</v>
       </c>
       <c r="N72">
-        <v>574.5901375301884</v>
+        <v>571.4085680663339</v>
       </c>
       <c r="O72">
-        <v>143.6475343825471</v>
+        <v>142.8521420165835</v>
       </c>
       <c r="P72">
-        <v>430.9426031476413</v>
+        <v>428.5564260497505</v>
       </c>
       <c r="Q72">
-        <v>1183.242603147641</v>
+        <v>1180.856426049751</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1293185116888751</v>
+        <v>0.1319366468515358</v>
       </c>
       <c r="T72">
-        <v>1.627931245740234</v>
+        <v>1.678963573192906</v>
       </c>
       <c r="U72">
         <v>0.0672366166625341</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.579994128495654</v>
+        <v>3.52957167598163</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07406512595974477</v>
+        <v>0.07554747466499662</v>
       </c>
       <c r="C73">
-        <v>2485.153582097237</v>
+        <v>2310.559668693903</v>
       </c>
       <c r="D73">
-        <v>4947.602582097236</v>
+        <v>4820.327668693903</v>
       </c>
       <c r="E73">
-        <v>-257.6510000000007</v>
+        <v>-210.3320000000008</v>
       </c>
       <c r="F73">
-        <v>3359.648999999999</v>
+        <v>3406.967999999999</v>
       </c>
       <c r="G73">
         <v>897.2</v>
@@ -7273,45 +7273,45 @@
         <v>797.3</v>
       </c>
       <c r="M73">
-        <v>225.891431933666</v>
+        <v>238.6125117975204</v>
       </c>
       <c r="N73">
-        <v>571.4085680663339</v>
+        <v>558.6874882024796</v>
       </c>
       <c r="O73">
-        <v>142.8521420165835</v>
+        <v>139.6718720506199</v>
       </c>
       <c r="P73">
-        <v>428.5564260497505</v>
+        <v>419.0156161518597</v>
       </c>
       <c r="Q73">
-        <v>1180.856426049751</v>
+        <v>1171.31561615186</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1319366468515357</v>
+        <v>0.1347417916686721</v>
       </c>
       <c r="T73">
-        <v>1.678963573192906</v>
+        <v>1.733641066892197</v>
       </c>
       <c r="U73">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.529571675981631</v>
+        <v>3.341400641541234</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07554747466499662</v>
+        <v>0.07553882337024846</v>
       </c>
       <c r="C74">
-        <v>2310.559668693903</v>
+        <v>2263.964471897847</v>
       </c>
       <c r="D74">
-        <v>4820.327668693903</v>
+        <v>4821.051471897847</v>
       </c>
       <c r="E74">
-        <v>-210.3320000000008</v>
+        <v>-163.0130000000004</v>
       </c>
       <c r="F74">
-        <v>3406.967999999999</v>
+        <v>3454.287</v>
       </c>
       <c r="G74">
         <v>897.2</v>
@@ -7355,28 +7355,28 @@
         <v>797.3</v>
       </c>
       <c r="M74">
-        <v>238.6125117975204</v>
+        <v>241.9265744613749</v>
       </c>
       <c r="N74">
-        <v>558.6874882024796</v>
+        <v>555.373425538625</v>
       </c>
       <c r="O74">
-        <v>139.6718720506199</v>
+        <v>138.8433563846563</v>
       </c>
       <c r="P74">
-        <v>419.0156161518597</v>
+        <v>416.5300691539688</v>
       </c>
       <c r="Q74">
-        <v>1171.31561615186</v>
+        <v>1168.830069153969</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1347417916686721</v>
+        <v>0.1377547249907816</v>
       </c>
       <c r="T74">
-        <v>1.733641066892197</v>
+        <v>1.792368745309954</v>
       </c>
       <c r="U74">
         <v>0.07003661666253409</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.341400641541234</v>
+        <v>3.295628030013271</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07553882337024846</v>
+        <v>0.07553017207550031</v>
       </c>
       <c r="C75">
-        <v>2263.964471897847</v>
+        <v>2217.369492501849</v>
       </c>
       <c r="D75">
-        <v>4821.051471897847</v>
+        <v>4821.775492501849</v>
       </c>
       <c r="E75">
-        <v>-163.0130000000004</v>
+        <v>-115.6940000000004</v>
       </c>
       <c r="F75">
-        <v>3454.287</v>
+        <v>3501.606</v>
       </c>
       <c r="G75">
         <v>897.2</v>
@@ -7437,28 +7437,28 @@
         <v>797.3</v>
       </c>
       <c r="M75">
-        <v>241.9265744613749</v>
+        <v>245.2406371252293</v>
       </c>
       <c r="N75">
-        <v>555.373425538625</v>
+        <v>552.0593628747706</v>
       </c>
       <c r="O75">
-        <v>138.8433563846563</v>
+        <v>138.0148407186927</v>
       </c>
       <c r="P75">
-        <v>416.5300691539688</v>
+        <v>414.044522156078</v>
       </c>
       <c r="Q75">
-        <v>1168.830069153969</v>
+        <v>1166.344522156078</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1377547249907816</v>
+        <v>0.1409994224145919</v>
       </c>
       <c r="T75">
-        <v>1.792368745309954</v>
+        <v>1.855613937452154</v>
       </c>
       <c r="U75">
         <v>0.07003661666253409</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.295628030013271</v>
+        <v>3.251092516094173</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07553017207550031</v>
+        <v>0.07552152078075217</v>
       </c>
       <c r="C76">
-        <v>2217.369492501849</v>
+        <v>2170.774730603868</v>
       </c>
       <c r="D76">
-        <v>4821.775492501849</v>
+        <v>4822.499730603868</v>
       </c>
       <c r="E76">
-        <v>-115.6940000000004</v>
+        <v>-68.37500000000045</v>
       </c>
       <c r="F76">
-        <v>3501.606</v>
+        <v>3548.925</v>
       </c>
       <c r="G76">
         <v>897.2</v>
@@ -7519,28 +7519,28 @@
         <v>797.3</v>
       </c>
       <c r="M76">
-        <v>245.2406371252293</v>
+        <v>248.5546997890838</v>
       </c>
       <c r="N76">
-        <v>552.0593628747706</v>
+        <v>548.7453002109162</v>
       </c>
       <c r="O76">
-        <v>138.0148407186927</v>
+        <v>137.186325052729</v>
       </c>
       <c r="P76">
-        <v>414.044522156078</v>
+        <v>411.5589751581871</v>
       </c>
       <c r="Q76">
-        <v>1166.344522156078</v>
+        <v>1163.858975158187</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1409994224145919</v>
+        <v>0.1445036956323069</v>
       </c>
       <c r="T76">
-        <v>1.855613937452154</v>
+        <v>1.923918744965731</v>
       </c>
       <c r="U76">
         <v>0.07003661666253409</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.251092516094173</v>
+        <v>3.207744615879584</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07552152078075217</v>
+        <v>0.075512869486004</v>
       </c>
       <c r="C77">
-        <v>2170.774730603868</v>
+        <v>2124.180186301928</v>
       </c>
       <c r="D77">
-        <v>4822.499730603868</v>
+        <v>4823.224186301928</v>
       </c>
       <c r="E77">
-        <v>-68.37500000000045</v>
+        <v>-21.05600000000049</v>
       </c>
       <c r="F77">
-        <v>3548.925</v>
+        <v>3596.244</v>
       </c>
       <c r="G77">
         <v>897.2</v>
@@ -7601,28 +7601,28 @@
         <v>797.3</v>
       </c>
       <c r="M77">
-        <v>248.5546997890838</v>
+        <v>251.8687624529382</v>
       </c>
       <c r="N77">
-        <v>548.7453002109162</v>
+        <v>545.4312375470618</v>
       </c>
       <c r="O77">
-        <v>137.186325052729</v>
+        <v>136.3578093867654</v>
       </c>
       <c r="P77">
-        <v>411.5589751581871</v>
+        <v>409.0734281602963</v>
       </c>
       <c r="Q77">
-        <v>1163.858975158187</v>
+        <v>1161.373428160296</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1445036956323069</v>
+        <v>0.1482999916181649</v>
       </c>
       <c r="T77">
-        <v>1.923918744965731</v>
+        <v>1.997915619772105</v>
       </c>
       <c r="U77">
         <v>0.07003661666253409</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.207744615879584</v>
+        <v>3.165537449881169</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.075512869486004</v>
+        <v>0.07550421819125586</v>
       </c>
       <c r="C78">
-        <v>2124.180186301928</v>
+        <v>2077.585859694105</v>
       </c>
       <c r="D78">
-        <v>4823.224186301928</v>
+        <v>4823.948859694105</v>
       </c>
       <c r="E78">
-        <v>-21.05600000000049</v>
+        <v>26.26299999999947</v>
       </c>
       <c r="F78">
-        <v>3596.244</v>
+        <v>3643.563</v>
       </c>
       <c r="G78">
         <v>897.2</v>
@@ -7683,28 +7683,28 @@
         <v>797.3</v>
       </c>
       <c r="M78">
-        <v>251.8687624529382</v>
+        <v>255.1828251167927</v>
       </c>
       <c r="N78">
-        <v>545.4312375470618</v>
+        <v>542.1171748832073</v>
       </c>
       <c r="O78">
-        <v>136.3578093867654</v>
+        <v>135.5292937208018</v>
       </c>
       <c r="P78">
-        <v>409.0734281602963</v>
+        <v>406.5878811624055</v>
       </c>
       <c r="Q78">
-        <v>1161.373428160296</v>
+        <v>1158.887881162405</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1482999916181649</v>
+        <v>0.1524264002984453</v>
       </c>
       <c r="T78">
-        <v>1.997915619772105</v>
+        <v>2.078347005431208</v>
       </c>
       <c r="U78">
         <v>0.07003661666253409</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.165537449881169</v>
+        <v>3.124426573908686</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07550421819125586</v>
+        <v>0.07549556689650769</v>
       </c>
       <c r="C79">
-        <v>2077.585859694105</v>
+        <v>2030.99175087854</v>
       </c>
       <c r="D79">
-        <v>4823.948859694105</v>
+        <v>4824.67375087854</v>
       </c>
       <c r="E79">
-        <v>26.26299999999947</v>
+        <v>73.58199999999988</v>
       </c>
       <c r="F79">
-        <v>3643.563</v>
+        <v>3690.882</v>
       </c>
       <c r="G79">
         <v>897.2</v>
@@ -7765,28 +7765,28 @@
         <v>797.3</v>
       </c>
       <c r="M79">
-        <v>255.1828251167927</v>
+        <v>258.4968877806472</v>
       </c>
       <c r="N79">
-        <v>542.1171748832073</v>
+        <v>538.8031122193528</v>
       </c>
       <c r="O79">
-        <v>135.5292937208018</v>
+        <v>134.7007780548382</v>
       </c>
       <c r="P79">
-        <v>406.5878811624055</v>
+        <v>404.1023341645146</v>
       </c>
       <c r="Q79">
-        <v>1158.887881162405</v>
+        <v>1156.402334164515</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1524264002984453</v>
+        <v>0.1569279370405693</v>
       </c>
       <c r="T79">
-        <v>2.078347005431208</v>
+        <v>2.166090335241138</v>
       </c>
       <c r="U79">
         <v>0.07003661666253409</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.124426573908686</v>
+        <v>3.084369822961138</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07549556689650769</v>
+        <v>0.07548691560175955</v>
       </c>
       <c r="C80">
-        <v>2030.99175087854</v>
+        <v>1984.397859953426</v>
       </c>
       <c r="D80">
-        <v>4824.67375087854</v>
+        <v>4825.398859953426</v>
       </c>
       <c r="E80">
-        <v>73.58199999999988</v>
+        <v>120.9009999999998</v>
       </c>
       <c r="F80">
-        <v>3690.882</v>
+        <v>3738.201</v>
       </c>
       <c r="G80">
         <v>897.2</v>
@@ -7847,28 +7847,28 @@
         <v>797.3</v>
       </c>
       <c r="M80">
-        <v>258.4968877806472</v>
+        <v>261.8109504445016</v>
       </c>
       <c r="N80">
-        <v>538.8031122193528</v>
+        <v>535.4890495554984</v>
       </c>
       <c r="O80">
-        <v>134.7007780548382</v>
+        <v>133.8722623888746</v>
       </c>
       <c r="P80">
-        <v>404.1023341645146</v>
+        <v>401.6167871666238</v>
       </c>
       <c r="Q80">
-        <v>1156.402334164515</v>
+        <v>1153.916787166624</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1569279370405693</v>
+        <v>0.1618581915676576</v>
       </c>
       <c r="T80">
-        <v>2.166090335241138</v>
+        <v>2.262190172652013</v>
       </c>
       <c r="U80">
         <v>0.07003661666253409</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.084369822961138</v>
+        <v>3.045327166974289</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07548691560175955</v>
+        <v>0.07547826430701139</v>
       </c>
       <c r="C81">
-        <v>1984.397859953426</v>
+        <v>1937.804187017024</v>
       </c>
       <c r="D81">
-        <v>4825.398859953426</v>
+        <v>4826.124187017024</v>
       </c>
       <c r="E81">
-        <v>120.9009999999998</v>
+        <v>168.2199999999998</v>
       </c>
       <c r="F81">
-        <v>3738.201</v>
+        <v>3785.52</v>
       </c>
       <c r="G81">
         <v>897.2</v>
@@ -7929,28 +7929,28 @@
         <v>797.3</v>
       </c>
       <c r="M81">
-        <v>261.8109504445016</v>
+        <v>265.1250131083561</v>
       </c>
       <c r="N81">
-        <v>535.4890495554984</v>
+        <v>532.1749868916438</v>
       </c>
       <c r="O81">
-        <v>133.8722623888746</v>
+        <v>133.043746722911</v>
       </c>
       <c r="P81">
-        <v>401.6167871666238</v>
+        <v>399.1312401687329</v>
       </c>
       <c r="Q81">
-        <v>1153.916787166624</v>
+        <v>1151.431240168733</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1618581915676576</v>
+        <v>0.1672814715474547</v>
       </c>
       <c r="T81">
-        <v>2.262190172652013</v>
+        <v>2.367899993803977</v>
       </c>
       <c r="U81">
         <v>0.07003661666253409</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.045327166974289</v>
+        <v>3.007260577387109</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07547826430701139</v>
+        <v>0.08020811301226324</v>
       </c>
       <c r="C82">
-        <v>1937.804187017024</v>
+        <v>1523.992136073482</v>
       </c>
       <c r="D82">
-        <v>4826.124187017024</v>
+        <v>4459.631136073482</v>
       </c>
       <c r="E82">
-        <v>168.2199999999998</v>
+        <v>215.5389999999998</v>
       </c>
       <c r="F82">
-        <v>3785.52</v>
+        <v>3832.839</v>
       </c>
       <c r="G82">
         <v>897.2</v>
@@ -8011,45 +8011,45 @@
         <v>797.3</v>
       </c>
       <c r="M82">
-        <v>265.1250131083561</v>
+        <v>298.3352199722106</v>
       </c>
       <c r="N82">
-        <v>532.1749868916438</v>
+        <v>498.9647800277894</v>
       </c>
       <c r="O82">
-        <v>133.043746722911</v>
+        <v>124.7411950069474</v>
       </c>
       <c r="P82">
-        <v>399.1312401687329</v>
+        <v>374.2235850208421</v>
       </c>
       <c r="Q82">
-        <v>1151.431240168733</v>
+        <v>1126.523585020842</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1672814715474547</v>
+        <v>0.1732756231040725</v>
       </c>
       <c r="T82">
-        <v>2.367899993803977</v>
+        <v>2.484737164550884</v>
       </c>
       <c r="U82">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.007260577387109</v>
+        <v>2.672497065798223</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08020811301226324</v>
+        <v>0.08025796171751509</v>
       </c>
       <c r="C83">
-        <v>1523.992136073482</v>
+        <v>1473.106774431629</v>
       </c>
       <c r="D83">
-        <v>4459.631136073482</v>
+        <v>4456.064774431629</v>
       </c>
       <c r="E83">
-        <v>215.5389999999998</v>
+        <v>262.8579999999997</v>
       </c>
       <c r="F83">
-        <v>3832.839</v>
+        <v>3880.158</v>
       </c>
       <c r="G83">
         <v>897.2</v>
@@ -8093,28 +8093,28 @@
         <v>797.3</v>
       </c>
       <c r="M83">
-        <v>298.3352199722106</v>
+        <v>302.018370836065</v>
       </c>
       <c r="N83">
-        <v>498.9647800277894</v>
+        <v>495.281629163935</v>
       </c>
       <c r="O83">
-        <v>124.7411950069474</v>
+        <v>123.8204072909837</v>
       </c>
       <c r="P83">
-        <v>374.2235850208421</v>
+        <v>371.4612218729512</v>
       </c>
       <c r="Q83">
-        <v>1126.523585020842</v>
+        <v>1123.761221872951</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1732756231040725</v>
+        <v>0.1799357915003146</v>
       </c>
       <c r="T83">
-        <v>2.484737164550884</v>
+        <v>2.614556243158558</v>
       </c>
       <c r="U83">
         <v>0.07783661666253411</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.672497065798223</v>
+        <v>2.639905638166537</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08025796171751509</v>
+        <v>0.08030781042276694</v>
       </c>
       <c r="C84">
-        <v>1473.106774431629</v>
+        <v>1422.227112262124</v>
       </c>
       <c r="D84">
-        <v>4456.064774431629</v>
+        <v>4452.504112262124</v>
       </c>
       <c r="E84">
-        <v>262.8579999999997</v>
+        <v>310.1769999999997</v>
       </c>
       <c r="F84">
-        <v>3880.158</v>
+        <v>3927.477</v>
       </c>
       <c r="G84">
         <v>897.2</v>
@@ -8175,28 +8175,28 @@
         <v>797.3</v>
       </c>
       <c r="M84">
-        <v>302.018370836065</v>
+        <v>305.7015216999195</v>
       </c>
       <c r="N84">
-        <v>495.281629163935</v>
+        <v>491.5984783000805</v>
       </c>
       <c r="O84">
-        <v>123.8204072909837</v>
+        <v>122.8996195750201</v>
       </c>
       <c r="P84">
-        <v>371.4612218729512</v>
+        <v>368.6988587250604</v>
       </c>
       <c r="Q84">
-        <v>1123.761221872951</v>
+        <v>1120.99885872506</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1799357915003146</v>
+        <v>0.1873795091196439</v>
       </c>
       <c r="T84">
-        <v>2.614556243158558</v>
+        <v>2.759648154543606</v>
       </c>
       <c r="U84">
         <v>0.07783661666253411</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.639905638166537</v>
+        <v>2.608099546140434</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08030781042276694</v>
+        <v>0.08035765912801879</v>
       </c>
       <c r="C85">
-        <v>1422.227112262124</v>
+        <v>1371.353135913218</v>
       </c>
       <c r="D85">
-        <v>4452.504112262124</v>
+        <v>4448.949135913218</v>
       </c>
       <c r="E85">
-        <v>310.1769999999997</v>
+        <v>357.4960000000001</v>
       </c>
       <c r="F85">
-        <v>3927.477</v>
+        <v>3974.796</v>
       </c>
       <c r="G85">
         <v>897.2</v>
@@ -8257,28 +8257,28 @@
         <v>797.3</v>
       </c>
       <c r="M85">
-        <v>305.7015216999195</v>
+        <v>309.384672563774</v>
       </c>
       <c r="N85">
-        <v>491.5984783000805</v>
+        <v>487.915327436226</v>
       </c>
       <c r="O85">
-        <v>122.8996195750201</v>
+        <v>121.9788318590565</v>
       </c>
       <c r="P85">
-        <v>368.6988587250604</v>
+        <v>365.9364955771695</v>
       </c>
       <c r="Q85">
-        <v>1120.99885872506</v>
+        <v>1118.23649557717</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1873795091196439</v>
+        <v>0.1957536914413894</v>
       </c>
       <c r="T85">
-        <v>2.759648154543606</v>
+        <v>2.922876554851785</v>
       </c>
       <c r="U85">
         <v>0.07783661666253411</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.608099546140434</v>
+        <v>2.577050742019714</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08035765912801879</v>
+        <v>0.08040750783327064</v>
       </c>
       <c r="C86">
-        <v>1371.353135913218</v>
+        <v>1320.484831776726</v>
       </c>
       <c r="D86">
-        <v>4448.949135913218</v>
+        <v>4445.399831776726</v>
       </c>
       <c r="E86">
-        <v>357.4959999999992</v>
+        <v>404.8149999999996</v>
       </c>
       <c r="F86">
-        <v>3974.795999999999</v>
+        <v>4022.115</v>
       </c>
       <c r="G86">
         <v>897.2</v>
@@ -8339,28 +8339,28 @@
         <v>797.3</v>
       </c>
       <c r="M86">
-        <v>309.3846725637738</v>
+        <v>313.0678234276284</v>
       </c>
       <c r="N86">
-        <v>487.9153274362261</v>
+        <v>484.2321765723716</v>
       </c>
       <c r="O86">
-        <v>121.9788318590565</v>
+        <v>121.0580441430929</v>
       </c>
       <c r="P86">
-        <v>365.9364955771696</v>
+        <v>363.1741324292787</v>
       </c>
       <c r="Q86">
-        <v>1118.23649557717</v>
+        <v>1115.474132429279</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1957536914413893</v>
+        <v>0.2052444314060343</v>
       </c>
       <c r="T86">
-        <v>2.922876554851783</v>
+        <v>3.107868741867719</v>
       </c>
       <c r="U86">
         <v>0.07783661666253411</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.577050742019715</v>
+        <v>2.546732497995953</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08040750783327064</v>
+        <v>0.08045735653852248</v>
       </c>
       <c r="C87">
-        <v>1320.484831776726</v>
+        <v>1269.622186287857</v>
       </c>
       <c r="D87">
-        <v>4445.399831776726</v>
+        <v>4441.856186287857</v>
       </c>
       <c r="E87">
-        <v>404.8149999999996</v>
+        <v>452.1339999999996</v>
       </c>
       <c r="F87">
-        <v>4022.115</v>
+        <v>4069.434</v>
       </c>
       <c r="G87">
         <v>897.2</v>
@@ -8421,28 +8421,28 @@
         <v>797.3</v>
       </c>
       <c r="M87">
-        <v>313.0678234276284</v>
+        <v>316.7509742914828</v>
       </c>
       <c r="N87">
-        <v>484.2321765723716</v>
+        <v>480.5490257085171</v>
       </c>
       <c r="O87">
-        <v>121.0580441430929</v>
+        <v>120.1372564271293</v>
       </c>
       <c r="P87">
-        <v>363.1741324292787</v>
+        <v>360.4117692813879</v>
       </c>
       <c r="Q87">
-        <v>1115.474132429279</v>
+        <v>1112.711769281388</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2052444314060343</v>
+        <v>0.2160909913656284</v>
       </c>
       <c r="T87">
-        <v>3.107868741867719</v>
+        <v>3.319288384171645</v>
       </c>
       <c r="U87">
         <v>0.07783661666253411</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.546732497995953</v>
+        <v>2.517119329414605</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08045735653852248</v>
+        <v>0.08305195524377432</v>
       </c>
       <c r="C88">
-        <v>1269.622186287857</v>
+        <v>1045.347447420814</v>
       </c>
       <c r="D88">
-        <v>4441.856186287857</v>
+        <v>4264.900447420814</v>
       </c>
       <c r="E88">
-        <v>452.1339999999996</v>
+        <v>499.4529999999995</v>
       </c>
       <c r="F88">
-        <v>4069.434</v>
+        <v>4116.753</v>
       </c>
       <c r="G88">
         <v>897.2</v>
@@ -8503,45 +8503,45 @@
         <v>797.3</v>
       </c>
       <c r="M88">
-        <v>316.7509742914828</v>
+        <v>336.4894618553372</v>
       </c>
       <c r="N88">
-        <v>480.5490257085171</v>
+        <v>460.8105381446628</v>
       </c>
       <c r="O88">
-        <v>120.1372564271293</v>
+        <v>115.2026345361657</v>
       </c>
       <c r="P88">
-        <v>360.4117692813879</v>
+        <v>345.6079036084971</v>
       </c>
       <c r="Q88">
-        <v>1112.711769281388</v>
+        <v>1097.907903608497</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2160909913656284</v>
+        <v>0.2286062528574678</v>
       </c>
       <c r="T88">
-        <v>3.319288384171645</v>
+        <v>3.56323412529156</v>
       </c>
       <c r="U88">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.517119329414605</v>
+        <v>2.369464991871791</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08305195524377432</v>
+        <v>0.08313105394902617</v>
       </c>
       <c r="C89">
-        <v>1045.347447420814</v>
+        <v>992.8549873494285</v>
       </c>
       <c r="D89">
-        <v>4264.900447420814</v>
+        <v>4259.726987349429</v>
       </c>
       <c r="E89">
-        <v>499.4529999999995</v>
+        <v>546.7719999999999</v>
       </c>
       <c r="F89">
-        <v>4116.753</v>
+        <v>4164.072</v>
       </c>
       <c r="G89">
         <v>897.2</v>
@@ -8585,28 +8585,28 @@
         <v>797.3</v>
       </c>
       <c r="M89">
-        <v>336.4894618553372</v>
+        <v>340.3571568191917</v>
       </c>
       <c r="N89">
-        <v>460.8105381446628</v>
+        <v>456.9428431808083</v>
       </c>
       <c r="O89">
-        <v>115.2026345361657</v>
+        <v>114.2357107952021</v>
       </c>
       <c r="P89">
-        <v>345.6079036084971</v>
+        <v>342.7071323856062</v>
       </c>
       <c r="Q89">
-        <v>1097.907903608497</v>
+        <v>1095.007132385606</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2286062528574678</v>
+        <v>0.2432073912646139</v>
       </c>
       <c r="T89">
-        <v>3.56323412529156</v>
+        <v>3.847837489931462</v>
       </c>
       <c r="U89">
         <v>0.0817366166625341</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.369464991871791</v>
+        <v>2.342539253327793</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08313105394902617</v>
+        <v>0.083210152654278</v>
       </c>
       <c r="C90">
-        <v>992.8549873494285</v>
+        <v>940.3750632152178</v>
       </c>
       <c r="D90">
-        <v>4259.726987349429</v>
+        <v>4254.566063215218</v>
       </c>
       <c r="E90">
-        <v>546.7719999999999</v>
+        <v>594.0909999999994</v>
       </c>
       <c r="F90">
-        <v>4164.072</v>
+        <v>4211.391</v>
       </c>
       <c r="G90">
         <v>897.2</v>
@@ -8667,28 +8667,28 @@
         <v>797.3</v>
       </c>
       <c r="M90">
-        <v>340.3571568191917</v>
+        <v>344.2248517830461</v>
       </c>
       <c r="N90">
-        <v>456.9428431808083</v>
+        <v>453.0751482169538</v>
       </c>
       <c r="O90">
-        <v>114.2357107952021</v>
+        <v>113.2687870542385</v>
       </c>
       <c r="P90">
-        <v>342.7071323856062</v>
+        <v>339.8063611627153</v>
       </c>
       <c r="Q90">
-        <v>1095.007132385606</v>
+        <v>1092.106361162715</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2432073912646139</v>
+        <v>0.2604632821094228</v>
       </c>
       <c r="T90">
-        <v>3.847837489931462</v>
+        <v>4.184186920869527</v>
       </c>
       <c r="U90">
         <v>0.0817366166625341</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.342539253327793</v>
+        <v>2.316218587560066</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.083210152654278</v>
+        <v>0.08328925135952985</v>
       </c>
       <c r="C91">
-        <v>940.3750632152178</v>
+        <v>887.9076295091108</v>
       </c>
       <c r="D91">
-        <v>4254.566063215218</v>
+        <v>4249.417629509111</v>
       </c>
       <c r="E91">
-        <v>594.0909999999994</v>
+        <v>641.4099999999999</v>
       </c>
       <c r="F91">
-        <v>4211.391</v>
+        <v>4258.71</v>
       </c>
       <c r="G91">
         <v>897.2</v>
@@ -8749,28 +8749,28 @@
         <v>797.3</v>
       </c>
       <c r="M91">
-        <v>344.2248517830461</v>
+        <v>348.0925467469006</v>
       </c>
       <c r="N91">
-        <v>453.0751482169538</v>
+        <v>449.2074532530994</v>
       </c>
       <c r="O91">
-        <v>113.2687870542385</v>
+        <v>112.3018633132749</v>
       </c>
       <c r="P91">
-        <v>339.8063611627153</v>
+        <v>336.9055899398246</v>
       </c>
       <c r="Q91">
-        <v>1092.106361162715</v>
+        <v>1089.205589939824</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2604632821094228</v>
+        <v>0.2811703511231934</v>
       </c>
       <c r="T91">
-        <v>4.184186920869527</v>
+        <v>4.587806237995205</v>
       </c>
       <c r="U91">
         <v>0.0817366166625341</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.316218587560066</v>
+        <v>2.290482825476065</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08328925135952985</v>
+        <v>0.0833683500647817</v>
       </c>
       <c r="C92">
-        <v>887.9076295091108</v>
+        <v>835.4526409420587</v>
       </c>
       <c r="D92">
-        <v>4249.417629509111</v>
+        <v>4244.281640942058</v>
       </c>
       <c r="E92">
-        <v>641.4099999999999</v>
+        <v>688.7289999999994</v>
       </c>
       <c r="F92">
-        <v>4258.71</v>
+        <v>4306.029</v>
       </c>
       <c r="G92">
         <v>897.2</v>
@@ -8831,28 +8831,28 @@
         <v>797.3</v>
       </c>
       <c r="M92">
-        <v>348.0925467469006</v>
+        <v>351.960241710755</v>
       </c>
       <c r="N92">
-        <v>449.2074532530994</v>
+        <v>445.339758289245</v>
       </c>
       <c r="O92">
-        <v>112.3018633132749</v>
+        <v>111.3349395723112</v>
       </c>
       <c r="P92">
-        <v>336.9055899398246</v>
+        <v>334.0048187169338</v>
       </c>
       <c r="Q92">
-        <v>1089.205589939824</v>
+        <v>1086.304818716934</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2811703511231934</v>
+        <v>0.3064789910289132</v>
       </c>
       <c r="T92">
-        <v>4.587806237995205</v>
+        <v>5.081118736704368</v>
       </c>
       <c r="U92">
         <v>0.0817366166625341</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.290482825476065</v>
+        <v>2.265312684536767</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0833683500647817</v>
+        <v>0.08344744877003354</v>
       </c>
       <c r="C93">
-        <v>835.4526409420587</v>
+        <v>783.0100524437012</v>
       </c>
       <c r="D93">
-        <v>4244.281640942058</v>
+        <v>4239.158052443701</v>
       </c>
       <c r="E93">
-        <v>688.7289999999994</v>
+        <v>736.0479999999998</v>
       </c>
       <c r="F93">
-        <v>4306.029</v>
+        <v>4353.348</v>
       </c>
       <c r="G93">
         <v>897.2</v>
@@ -8913,28 +8913,28 @@
         <v>797.3</v>
       </c>
       <c r="M93">
-        <v>351.960241710755</v>
+        <v>355.8279366746095</v>
       </c>
       <c r="N93">
-        <v>445.339758289245</v>
+        <v>441.4720633253905</v>
       </c>
       <c r="O93">
-        <v>111.3349395723112</v>
+        <v>110.3680158313476</v>
       </c>
       <c r="P93">
-        <v>334.0048187169338</v>
+        <v>331.1040474940428</v>
       </c>
       <c r="Q93">
-        <v>1086.304818716934</v>
+        <v>1083.404047494043</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3064789910289132</v>
+        <v>0.3381147909110629</v>
       </c>
       <c r="T93">
-        <v>5.081118736704368</v>
+        <v>5.697759360090822</v>
       </c>
       <c r="U93">
         <v>0.0817366166625341</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.265312684536767</v>
+        <v>2.240689720574411</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08344744877003354</v>
+        <v>0.0835265474752854</v>
       </c>
       <c r="C94">
-        <v>783.0100524437012</v>
+        <v>730.5798191610411</v>
       </c>
       <c r="D94">
-        <v>4239.158052443701</v>
+        <v>4234.046819161041</v>
       </c>
       <c r="E94">
-        <v>736.0479999999998</v>
+        <v>783.3669999999993</v>
       </c>
       <c r="F94">
-        <v>4353.348</v>
+        <v>4400.666999999999</v>
       </c>
       <c r="G94">
         <v>897.2</v>
@@ -8995,28 +8995,28 @@
         <v>797.3</v>
       </c>
       <c r="M94">
-        <v>355.8279366746095</v>
+        <v>359.6956316384639</v>
       </c>
       <c r="N94">
-        <v>441.4720633253905</v>
+        <v>437.604368361536</v>
       </c>
       <c r="O94">
-        <v>110.3680158313476</v>
+        <v>109.401092090384</v>
       </c>
       <c r="P94">
-        <v>331.1040474940428</v>
+        <v>328.203276271152</v>
       </c>
       <c r="Q94">
-        <v>1083.404047494043</v>
+        <v>1080.503276271152</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3381147909110629</v>
+        <v>0.3787893907595412</v>
       </c>
       <c r="T94">
-        <v>5.697759360090822</v>
+        <v>6.490583018730547</v>
       </c>
       <c r="U94">
         <v>0.0817366166625341</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.240689720574411</v>
+        <v>2.216596282718772</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0835265474752854</v>
+        <v>0.08360564618053724</v>
       </c>
       <c r="C95">
-        <v>730.5798191610411</v>
+        <v>678.1618964571462</v>
       </c>
       <c r="D95">
-        <v>4234.046819161041</v>
+        <v>4228.947896457146</v>
       </c>
       <c r="E95">
-        <v>783.3669999999993</v>
+        <v>830.6859999999997</v>
       </c>
       <c r="F95">
-        <v>4400.666999999999</v>
+        <v>4447.986</v>
       </c>
       <c r="G95">
         <v>897.2</v>
@@ -9077,28 +9077,28 @@
         <v>797.3</v>
       </c>
       <c r="M95">
-        <v>359.6956316384639</v>
+        <v>363.5633266023183</v>
       </c>
       <c r="N95">
-        <v>437.604368361536</v>
+        <v>433.7366733976816</v>
       </c>
       <c r="O95">
-        <v>109.401092090384</v>
+        <v>108.4341683494204</v>
       </c>
       <c r="P95">
-        <v>328.203276271152</v>
+        <v>325.3025050482612</v>
       </c>
       <c r="Q95">
-        <v>1080.503276271152</v>
+        <v>1077.602505048261</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3787893907595412</v>
+        <v>0.4330221905575121</v>
       </c>
       <c r="T95">
-        <v>6.490583018730547</v>
+        <v>7.547681230250181</v>
       </c>
       <c r="U95">
         <v>0.0817366166625341</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.216596282718772</v>
+        <v>2.193015471200487</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08360564618053724</v>
+        <v>0.08368474488578909</v>
       </c>
       <c r="C96">
-        <v>678.1618964571462</v>
+        <v>625.7562399098415</v>
       </c>
       <c r="D96">
-        <v>4228.947896457146</v>
+        <v>4223.861239909842</v>
       </c>
       <c r="E96">
-        <v>830.6859999999997</v>
+        <v>878.0050000000001</v>
       </c>
       <c r="F96">
-        <v>4447.986</v>
+        <v>4495.305</v>
       </c>
       <c r="G96">
         <v>897.2</v>
@@ -9159,28 +9159,28 @@
         <v>797.3</v>
       </c>
       <c r="M96">
-        <v>363.5633266023183</v>
+        <v>367.4310215661728</v>
       </c>
       <c r="N96">
-        <v>433.7366733976816</v>
+        <v>429.8689784338271</v>
       </c>
       <c r="O96">
-        <v>108.4341683494204</v>
+        <v>107.4672446084568</v>
       </c>
       <c r="P96">
-        <v>325.3025050482612</v>
+        <v>322.4017338253703</v>
       </c>
       <c r="Q96">
-        <v>1077.602505048261</v>
+        <v>1074.70173382537</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4330221905575121</v>
+        <v>0.5089481102746716</v>
       </c>
       <c r="T96">
-        <v>7.547681230250181</v>
+        <v>9.027618726377673</v>
       </c>
       <c r="U96">
         <v>0.0817366166625341</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.193015471200487</v>
+        <v>2.16993109781943</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08368474488578909</v>
+        <v>0.08376384359104094</v>
       </c>
       <c r="C97">
-        <v>625.7562399098415</v>
+        <v>573.3628053104248</v>
       </c>
       <c r="D97">
-        <v>4223.861239909842</v>
+        <v>4218.786805310425</v>
       </c>
       <c r="E97">
-        <v>878.0050000000001</v>
+        <v>925.3239999999996</v>
       </c>
       <c r="F97">
-        <v>4495.305</v>
+        <v>4542.624</v>
       </c>
       <c r="G97">
         <v>897.2</v>
@@ -9241,28 +9241,28 @@
         <v>797.3</v>
       </c>
       <c r="M97">
-        <v>367.4310215661728</v>
+        <v>371.2987165300273</v>
       </c>
       <c r="N97">
-        <v>429.8689784338271</v>
+        <v>426.0012834699727</v>
       </c>
       <c r="O97">
-        <v>107.4672446084568</v>
+        <v>106.5003208674932</v>
       </c>
       <c r="P97">
-        <v>322.4017338253703</v>
+        <v>319.5009626024795</v>
       </c>
       <c r="Q97">
-        <v>1074.70173382537</v>
+        <v>1071.80096260248</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5089481102746716</v>
+        <v>0.6228369898504107</v>
       </c>
       <c r="T97">
-        <v>9.027618726377673</v>
+        <v>11.24752497056891</v>
       </c>
       <c r="U97">
         <v>0.0817366166625341</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.16993109781943</v>
+        <v>2.14732764888381</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08376384359104094</v>
+        <v>0.08384294229629277</v>
       </c>
       <c r="C98">
-        <v>573.3628053104248</v>
+        <v>520.9815486623829</v>
       </c>
       <c r="D98">
-        <v>4218.786805310425</v>
+        <v>4213.724548662382</v>
       </c>
       <c r="E98">
-        <v>925.3239999999996</v>
+        <v>972.6429999999991</v>
       </c>
       <c r="F98">
-        <v>4542.624</v>
+        <v>4589.942999999999</v>
       </c>
       <c r="G98">
         <v>897.2</v>
@@ -9323,28 +9323,28 @@
         <v>797.3</v>
       </c>
       <c r="M98">
-        <v>371.2987165300273</v>
+        <v>375.1664114938817</v>
       </c>
       <c r="N98">
-        <v>426.0012834699727</v>
+        <v>422.1335885061183</v>
       </c>
       <c r="O98">
-        <v>106.5003208674932</v>
+        <v>105.5333971265296</v>
       </c>
       <c r="P98">
-        <v>319.5009626024795</v>
+        <v>316.6001913795887</v>
       </c>
       <c r="Q98">
-        <v>1071.80096260248</v>
+        <v>1068.900191379589</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6228369898504091</v>
+        <v>0.8126517891433068</v>
       </c>
       <c r="T98">
-        <v>11.24752497056888</v>
+        <v>14.94736871088759</v>
       </c>
       <c r="U98">
         <v>0.0817366166625341</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.14732764888381</v>
+        <v>2.12519025044171</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08384294229629277</v>
+        <v>0.08392204100154463</v>
       </c>
       <c r="C99">
-        <v>520.9815486623829</v>
+        <v>468.6124261801178</v>
       </c>
       <c r="D99">
-        <v>4213.724548662382</v>
+        <v>4208.674426180118</v>
       </c>
       <c r="E99">
-        <v>972.6429999999991</v>
+        <v>1019.962</v>
       </c>
       <c r="F99">
-        <v>4589.942999999999</v>
+        <v>4637.262</v>
       </c>
       <c r="G99">
         <v>897.2</v>
@@ -9405,28 +9405,28 @@
         <v>797.3</v>
       </c>
       <c r="M99">
-        <v>375.1664114938817</v>
+        <v>379.0341064577362</v>
       </c>
       <c r="N99">
-        <v>422.1335885061183</v>
+        <v>418.2658935422638</v>
       </c>
       <c r="O99">
-        <v>105.5333971265296</v>
+        <v>104.5664733855659</v>
       </c>
       <c r="P99">
-        <v>316.6001913795887</v>
+        <v>313.6994201566978</v>
       </c>
       <c r="Q99">
-        <v>1068.900191379589</v>
+        <v>1065.999420156698</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8126517891433068</v>
+        <v>1.192281387729103</v>
       </c>
       <c r="T99">
-        <v>14.94736871088759</v>
+        <v>22.34705619152501</v>
       </c>
       <c r="U99">
         <v>0.0817366166625341</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.12519025044171</v>
+        <v>2.103504635641284</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08392204100154463</v>
+        <v>0.08400113970679648</v>
       </c>
       <c r="C100">
-        <v>468.6124261801178</v>
+        <v>416.2553942876921</v>
       </c>
       <c r="D100">
-        <v>4208.674426180118</v>
+        <v>4203.636394287691</v>
       </c>
       <c r="E100">
-        <v>1019.962</v>
+        <v>1067.280999999999</v>
       </c>
       <c r="F100">
-        <v>4637.262</v>
+        <v>4684.580999999999</v>
       </c>
       <c r="G100">
         <v>897.2</v>
@@ -9487,28 +9487,28 @@
         <v>797.3</v>
       </c>
       <c r="M100">
-        <v>379.0341064577362</v>
+        <v>382.9018014215906</v>
       </c>
       <c r="N100">
-        <v>418.2658935422638</v>
+        <v>414.3981985784094</v>
       </c>
       <c r="O100">
-        <v>104.5664733855659</v>
+        <v>103.5995496446023</v>
       </c>
       <c r="P100">
-        <v>313.6994201566978</v>
+        <v>310.798648933807</v>
       </c>
       <c r="Q100">
-        <v>1065.999420156698</v>
+        <v>1063.098648933807</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.192281387729103</v>
+        <v>2.331170183486489</v>
       </c>
       <c r="T100">
-        <v>22.34705619152501</v>
+        <v>44.54611863343727</v>
       </c>
       <c r="U100">
         <v>0.0817366166625341</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.103504635641284</v>
+        <v>2.08225711406915</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08400113970679648</v>
-      </c>
-      <c r="C101">
-        <v>416.2553942876921</v>
-      </c>
-      <c r="D101">
-        <v>4203.636394287691</v>
-      </c>
-      <c r="E101">
-        <v>1067.280999999999</v>
-      </c>
-      <c r="F101">
-        <v>4684.580999999999</v>
-      </c>
-      <c r="G101">
-        <v>897.2</v>
-      </c>
-      <c r="H101">
-        <v>1114.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1549.6</v>
-      </c>
-      <c r="K101">
-        <v>752.3</v>
-      </c>
-      <c r="L101">
-        <v>797.3</v>
-      </c>
-      <c r="M101">
-        <v>382.9018014215906</v>
-      </c>
-      <c r="N101">
-        <v>414.3981985784094</v>
-      </c>
-      <c r="O101">
-        <v>103.5995496446023</v>
-      </c>
-      <c r="P101">
-        <v>310.798648933807</v>
-      </c>
-      <c r="Q101">
-        <v>1063.098648933807</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.331170183486489</v>
-      </c>
-      <c r="T101">
-        <v>44.54611863343727</v>
-      </c>
-      <c r="U101">
-        <v>0.0817366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.06130246249690057</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.08225711406915</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
